--- a/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
+++ b/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
@@ -6,33 +6,28 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3160" yWindow="2260" windowWidth="28240" windowHeight="17240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Шаблон (новая встреча)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="27.08.2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="20.08.2026" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="13.08.2026 (2)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="24.07.2026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06.082026" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="30.07.2026" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="27.08.2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="20.08.2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="13.08.2026 (2)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="24.07.2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="06.082026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="30.07.2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'27.08.2026'!$1:$2</definedName>
-  </definedNames>
+  <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd\.mm"/>
     <numFmt numFmtId="165" formatCode="dd\.mm\.yyyy"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="dd\.mm\.yyyy h:mm"/>
     <numFmt numFmtId="168" formatCode="0.0%"/>
-    <numFmt numFmtId="169" formatCode="#,##0&quot; клиент.&quot;"/>
-    <numFmt numFmtId="170" formatCode="#,##0&quot; ₽&quot;"/>
   </numFmts>
-  <fonts count="52">
+  <fonts count="34">
     <font>
       <name val="Arimo"/>
       <family val="2"/>
@@ -155,138 +150,30 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="16"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="001F4E79"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
+      <sz val="14"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00548235"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-      <sz val="18"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
       <sz val="12"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00548235"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="00000000"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="007F7F7F"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00548235"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C65911"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="001F4E79"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001F4E79"/>
-      <sz val="16"/>
-    </font>
   </fonts>
-  <fills count="43">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -377,22 +264,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
+        <fgColor rgb="00ECECEC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEF4FA"/>
+        <fgColor rgb="008BC34A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F69C7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6E3F0"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -402,111 +284,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00548235"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C65911"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005B9BD5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F9FC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00ED7D31"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8CBAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="009E480E"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2D5F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="007030A0"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D6F0FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="0000B0F0"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="68">
+  <borders count="63">
     <border>
       <left/>
       <right/>
@@ -1006,101 +793,25 @@
     </border>
     <border/>
     <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
+      <right style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
+      <right/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="00B0B0B0"/>
-      </left>
-      <right style="thin">
-        <color rgb="00B0B0B0"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00B0B0B0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00B0B0B0"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="809">
+  <cellXfs count="749">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
@@ -1860,15 +1571,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -2082,24 +1799,36 @@
     <xf numFmtId="1" fontId="8" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -2121,11 +1850,15 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -2176,11 +1909,15 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2299,7 +2036,9 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2456,7 +2195,9 @@
     <xf numFmtId="1" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -2481,7 +2222,9 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -2968,235 +2711,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="17" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="31" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="31" fillId="21" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="32" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="32" fillId="21" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="32" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="63" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="27" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="32" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="51" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="32" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="51" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="51" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="51" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="30" fillId="18" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="19" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="27" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="34" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="35" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="33" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="43" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="24" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="43" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="25" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="40" fillId="26" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="26" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="41" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="42" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="40" fillId="24" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="60" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="44" fillId="24" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="17" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="19" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="170" fontId="28" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="45" fillId="27" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="28" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="28" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="20" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="30" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="29" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="29" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="31" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="33" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="32" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="32" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="34" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="66" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="49" fillId="36" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="35" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="38" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="37" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="37" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="40" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="39" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="39" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="42" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="41" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="41" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="25" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="8" fillId="7" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -3208,6 +2770,34 @@
     <xf numFmtId="1" fontId="8" fillId="11" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="32" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="20" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="59" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="22" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="50" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
@@ -3242,27 +2832,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="51" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="33" fillId="18" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="34" fillId="21" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="169" fontId="35" fillId="22" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="33" fillId="23" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="42" fillId="0" borderId="60" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3541,286 +3110,2077 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:AE102"/>
+  <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8.762" customWidth="1" min="1" max="1"/>
+    <col width="49.902" customWidth="1" min="2" max="2"/>
+    <col width="35.613" customWidth="1" min="3" max="3"/>
+    <col width="35.184" customWidth="1" min="4" max="4"/>
+    <col width="24.141" customWidth="1" min="5" max="5"/>
+    <col width="29.543" customWidth="1" min="6" max="6"/>
+    <col width="34.801" customWidth="1" min="7" max="7"/>
+    <col width="19.543" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="28" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1">
+    <row r="1" ht="10.35" customHeight="1">
       <c r="A1" s="697" t="inlineStr">
         <is>
-          <t>ВСТРЕЧА ЦП — ЦКС — ЦСВ — СМАК  ·  Протокол ДД.ММ.ГГГГ</t>
-        </is>
-      </c>
+          <t>ВСТРЕЧА ЦП-ЦКС-ЦСВ-СМАК</t>
+        </is>
+      </c>
+      <c r="B1" s="698" t="n"/>
+      <c r="C1" s="698" t="n"/>
+      <c r="D1" s="698" t="n"/>
+      <c r="E1" s="698" t="n"/>
+      <c r="F1" s="698" t="n"/>
+      <c r="G1" s="698" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="698" t="inlineStr">
-        <is>
-          <t>Скопируйте лист и переименуйте в дату встречи. Обновите факты и таблицу периодов.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="699" t="inlineStr">
-        <is>
-          <t>ПЛАН ПО ЭПД</t>
-        </is>
-      </c>
-      <c r="I4" s="700" t="inlineStr">
+      <c r="A2" s="588" t="n"/>
+      <c r="B2" s="588" t="n"/>
+      <c r="C2" s="588" t="n"/>
+      <c r="D2" s="588" t="n"/>
+      <c r="E2" s="588" t="n"/>
+      <c r="F2" s="588" t="n"/>
+      <c r="G2" s="588" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="697" t="inlineStr">
+        <is>
+          <t>План по ЭПД</t>
+        </is>
+      </c>
+      <c r="B3" s="699" t="n"/>
+      <c r="C3" s="699" t="n"/>
+      <c r="D3" s="699" t="n"/>
+      <c r="E3" s="699" t="n"/>
+      <c r="F3" s="699" t="n"/>
+      <c r="G3" s="699" t="n"/>
+      <c r="I3" s="700" t="inlineStr">
         <is>
           <t>Соотношение к прошлому периоду</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="701" t="inlineStr">
+      <c r="J3" s="701" t="n"/>
+      <c r="K3" s="701" t="n"/>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="A4" s="702" t="inlineStr">
         <is>
           <t>План</t>
         </is>
       </c>
-      <c r="B5" s="702" t="n"/>
-      <c r="C5" s="701" t="inlineStr">
+      <c r="B4" s="702" t="n"/>
+      <c r="C4" s="702" t="inlineStr">
         <is>
           <t>Текущее значение</t>
         </is>
       </c>
-      <c r="D5" s="702" t="n"/>
-      <c r="E5" s="701" t="inlineStr">
+      <c r="D4" s="702" t="n"/>
+      <c r="E4" s="702" t="inlineStr">
         <is>
           <t>Итого до плана</t>
         </is>
       </c>
-      <c r="F5" s="702" t="n"/>
-      <c r="G5" s="701" t="inlineStr">
-        <is>
-          <t>% выполнения</t>
-        </is>
-      </c>
-      <c r="I5" s="703" t="inlineStr">
+      <c r="F4" s="702" t="n"/>
+      <c r="G4" s="702" t="inlineStr">
+        <is>
+          <t>% выполнения плана</t>
+        </is>
+      </c>
+      <c r="I4" s="702" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="J5" s="703" t="inlineStr">
+      <c r="J4" s="702" t="inlineStr">
         <is>
           <t>Клиенты</t>
         </is>
       </c>
-      <c r="K5" s="703" t="inlineStr">
+      <c r="K4" s="702" t="inlineStr">
         <is>
           <t>Изменение</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="704" t="n">
+    <row r="5" ht="28" customHeight="1">
+      <c r="A5" s="703" t="n">
         <v>500</v>
       </c>
-      <c r="C6" s="705">
-        <f>E11+E12+E13</f>
+      <c r="B5" s="704" t="n"/>
+      <c r="C5" s="705">
+        <f>E9+E10+E11</f>
         <v/>
       </c>
-      <c r="E6" s="706">
-        <f>A6-C6</f>
+      <c r="D5" s="706" t="n"/>
+      <c r="E5" s="703">
+        <f>A5-C5</f>
         <v/>
       </c>
-      <c r="G6" s="802">
-        <f>IF(A6=0,"—",C6/A6)</f>
+      <c r="F5" s="704" t="n"/>
+      <c r="G5" s="707">
+        <f>IF(A5=0,"—",C5/A5)</f>
         <v/>
       </c>
+      <c r="I5" s="708" t="inlineStr">
+        <is>
+          <t>27.08.2026</t>
+        </is>
+      </c>
+      <c r="J5" s="709">
+        <f>C5</f>
+        <v/>
+      </c>
+      <c r="K5" s="708" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="14.25" customHeight="1">
+      <c r="A6" s="710" t="inlineStr">
+        <is>
+          <t>«Текущее значение» = сумма ячеек «Факт» по отделам (ниже). Жёлтые ячейки — для ввода.</t>
+        </is>
+      </c>
+      <c r="B6" s="698" t="n"/>
+      <c r="C6" s="698" t="n"/>
+      <c r="D6" s="698" t="n"/>
+      <c r="E6" s="698" t="n"/>
+      <c r="F6" s="698" t="n"/>
+      <c r="G6" s="698" t="n"/>
       <c r="I6" s="708" t="inlineStr">
         <is>
-          <t>← дата</t>
-        </is>
-      </c>
-      <c r="J6" s="709">
-        <f>C6</f>
+          <t>03.09.2026</t>
+        </is>
+      </c>
+      <c r="J6" s="711" t="n">
+        <v>200</v>
+      </c>
+      <c r="K6" s="712">
+        <f>IF(OR(J5="",J5=0,J6=""),"—",IF(J6&gt;=J5,"увеличилось на "&amp;TEXT((J6-J5)/J5,"0.0%"),"уменьшилось на "&amp;TEXT((J5-J6)/J5,"0.0%")))</f>
         <v/>
       </c>
-      <c r="K6" s="708" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="I7" s="708" t="n"/>
-      <c r="J7" s="710" t="n"/>
-      <c r="K7" s="708">
+    </row>
+    <row r="7" ht="15.05" customHeight="1">
+      <c r="A7" s="700" t="inlineStr">
+        <is>
+          <t>План на МПП в месяц — по отделам</t>
+        </is>
+      </c>
+      <c r="B7" s="701" t="n"/>
+      <c r="C7" s="701" t="n"/>
+      <c r="D7" s="701" t="n"/>
+      <c r="E7" s="701" t="n"/>
+      <c r="F7" s="701" t="n"/>
+      <c r="G7" s="701" t="n"/>
+      <c r="I7" s="708" t="inlineStr">
+        <is>
+          <t>10.09.2026</t>
+        </is>
+      </c>
+      <c r="J7" s="711" t="n">
+        <v>250</v>
+      </c>
+      <c r="K7" s="712">
         <f>IF(OR(J6="",J6=0,J7=""),"—",IF(J7&gt;=J6,"увеличилось на "&amp;TEXT((J7-J6)/J6,"0.0%"),"уменьшилось на "&amp;TEXT((J6-J7)/J6,"0.0%")))</f>
         <v/>
       </c>
     </row>
     <row r="8">
+      <c r="A8" s="702" t="inlineStr">
+        <is>
+          <t>Отдел / группа</t>
+        </is>
+      </c>
+      <c r="B8" s="713" t="n"/>
+      <c r="C8" s="702" t="inlineStr">
+        <is>
+          <t>План на МПП в мес</t>
+        </is>
+      </c>
+      <c r="D8" s="713" t="n"/>
+      <c r="E8" s="702" t="inlineStr">
+        <is>
+          <t>Факт</t>
+        </is>
+      </c>
+      <c r="F8" s="702" t="inlineStr">
+        <is>
+          <t>% выполнения плана</t>
+        </is>
+      </c>
+      <c r="G8" s="713" t="n"/>
       <c r="I8" s="708" t="n"/>
-      <c r="J8" s="710" t="n"/>
-      <c r="K8" s="708">
+      <c r="J8" s="711" t="n"/>
+      <c r="K8" s="712">
         <f>IF(OR(J7="",J7=0,J8=""),"—",IF(J8&gt;=J7,"увеличилось на "&amp;TEXT((J8-J7)/J7,"0.0%"),"уменьшилось на "&amp;TEXT((J7-J8)/J7,"0.0%")))</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="711" t="inlineStr">
-        <is>
-          <t>План на МПП в месяц — по отделам</t>
-        </is>
-      </c>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="712" t="inlineStr">
+        <is>
+          <t>Группа «Новые деньги»</t>
+        </is>
+      </c>
+      <c r="B9" s="704" t="n"/>
+      <c r="C9" s="714" t="n">
+        <v>75</v>
+      </c>
+      <c r="D9" s="704" t="n"/>
+      <c r="E9" s="711" t="n">
+        <v>90</v>
+      </c>
+      <c r="F9" s="715">
+        <f>IF(OR(C9="",C9=0),"—",E9/C9)</f>
+        <v/>
+      </c>
+      <c r="G9" s="706" t="n"/>
       <c r="I9" s="708" t="n"/>
-      <c r="J9" s="710" t="n"/>
-      <c r="K9" s="708">
+      <c r="J9" s="711" t="n"/>
+      <c r="K9" s="712">
         <f>IF(OR(J8="",J8=0,J9=""),"—",IF(J9&gt;=J8,"увеличилось на "&amp;TEXT((J9-J8)/J8,"0.0%"),"уменьшилось на "&amp;TEXT((J8-J9)/J8,"0.0%")))</f>
         <v/>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="712" t="inlineStr">
         <is>
-          <t>Отдел / группа</t>
-        </is>
-      </c>
-      <c r="B10" s="712" t="n"/>
-      <c r="C10" s="712" t="inlineStr">
-        <is>
-          <t>План на МПП в мес</t>
-        </is>
-      </c>
-      <c r="D10" s="712" t="n"/>
-      <c r="E10" s="712" t="inlineStr">
-        <is>
-          <t>Факт</t>
-        </is>
-      </c>
-      <c r="F10" s="712" t="inlineStr">
-        <is>
-          <t>% выполнения плана</t>
-        </is>
-      </c>
-      <c r="G10" s="712" t="n"/>
+          <t>Группа продуктового запуска</t>
+        </is>
+      </c>
+      <c r="B10" s="704" t="n"/>
+      <c r="C10" s="714" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="704" t="n"/>
+      <c r="E10" s="711" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" s="715">
+        <f>IF(OR(C10="",C10=0),"—",E10/C10)</f>
+        <v/>
+      </c>
+      <c r="G10" s="706" t="n"/>
       <c r="I10" s="708" t="n"/>
-      <c r="J10" s="710" t="n"/>
-      <c r="K10" s="708">
+      <c r="J10" s="711" t="n"/>
+      <c r="K10" s="712">
         <f>IF(OR(J9="",J9=0,J10=""),"—",IF(J10&gt;=J9,"увеличилось на "&amp;TEXT((J10-J9)/J9,"0.0%"),"уменьшилось на "&amp;TEXT((J9-J10)/J9,"0.0%")))</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="713" t="inlineStr">
-        <is>
-          <t>Группа «Новые деньги»</t>
-        </is>
-      </c>
-      <c r="B11" s="713" t="n"/>
-      <c r="C11" s="713" t="n">
-        <v>75</v>
-      </c>
-      <c r="D11" s="713" t="n"/>
-      <c r="E11" s="714" t="n"/>
-      <c r="F11" s="803">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="712" t="inlineStr">
+        <is>
+          <t>ЦКС</t>
+        </is>
+      </c>
+      <c r="B11" s="704" t="n"/>
+      <c r="C11" s="716" t="n"/>
+      <c r="D11" s="698" t="n"/>
+      <c r="E11" s="711" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="715">
         <f>IF(OR(C11="",C11=0),"—",E11/C11)</f>
         <v/>
       </c>
-      <c r="G11" s="713" t="n"/>
+      <c r="G11" s="706" t="n"/>
       <c r="I11" s="708" t="n"/>
-      <c r="J11" s="710" t="n"/>
-      <c r="K11" s="708">
+      <c r="J11" s="711" t="n"/>
+      <c r="K11" s="712">
         <f>IF(OR(J10="",J10=0,J11=""),"—",IF(J11&gt;=J10,"увеличилось на "&amp;TEXT((J11-J10)/J10,"0.0%"),"уменьшилось на "&amp;TEXT((J10-J11)/J10,"0.0%")))</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="713" t="inlineStr">
-        <is>
-          <t>Группа продуктового запуска</t>
-        </is>
-      </c>
-      <c r="B12" s="713" t="n"/>
-      <c r="C12" s="713" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" s="713" t="n"/>
-      <c r="E12" s="714" t="n"/>
-      <c r="F12" s="803">
-        <f>IF(OR(C12="",C12=0),"—",E12/C12)</f>
+    <row r="12" ht="10" customHeight="1">
+      <c r="I12" s="708" t="n"/>
+      <c r="J12" s="711" t="n"/>
+      <c r="K12" s="712">
+        <f>IF(OR(J11="",J11=0,J12=""),"—",IF(J12&gt;=J11,"увеличилось на "&amp;TEXT((J12-J11)/J11,"0.0%"),"уменьшилось на "&amp;TEXT((J11-J12)/J11,"0.0%")))</f>
         <v/>
       </c>
-      <c r="G12" s="713" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="713" t="inlineStr">
-        <is>
-          <t>ЦКС</t>
-        </is>
-      </c>
-      <c r="B13" s="713" t="n"/>
-      <c r="C13" s="713" t="n"/>
-      <c r="D13" s="713" t="n"/>
-      <c r="E13" s="714" t="n"/>
-      <c r="F13" s="803">
-        <f>IF(OR(C13="",C13=0),"—",E13/C13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="713" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="716" t="inlineStr">
-        <is>
-          <t>1. Мониторинг предыдущих решений</t>
-        </is>
-      </c>
+    </row>
+    <row r="13" ht="14.95" customHeight="1">
+      <c r="I13" s="710" t="inlineStr">
+        <is>
+          <t>Строка 27.08 подтягивает текущее значение. Новые даты — в жёлтые ячейки «Клиенты».</t>
+        </is>
+      </c>
+      <c r="J13" s="698" t="n"/>
+      <c r="K13" s="698" t="n"/>
+    </row>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="589" t="inlineStr">
+        <is>
+          <t>Показатели рекламной кампании</t>
+        </is>
+      </c>
+      <c r="B17" s="717" t="n"/>
+      <c r="C17" s="717" t="n"/>
+      <c r="D17" s="717" t="n"/>
+      <c r="E17" s="717" t="n"/>
+      <c r="F17" s="717" t="n"/>
+      <c r="G17" s="718" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="717" t="inlineStr">
-        <is>
-          <t>2. Решения текущей встречи · поставленные задачи</t>
-        </is>
-      </c>
+      <c r="A18" s="590" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B18" s="590" t="inlineStr">
+        <is>
+          <t>Название рекламной кампании</t>
+        </is>
+      </c>
+      <c r="C18" s="590" t="inlineStr">
+        <is>
+          <t>Лидер</t>
+        </is>
+      </c>
+      <c r="D18" s="590" t="inlineStr">
+        <is>
+          <t>Кол-во ЛИДов</t>
+        </is>
+      </c>
+      <c r="E18" s="484" t="inlineStr">
+        <is>
+          <t>Стоимость ЛИДа</t>
+        </is>
+      </c>
+      <c r="F18" s="484" t="inlineStr">
+        <is>
+          <t>Сделок</t>
+        </is>
+      </c>
+      <c r="G18" s="446" t="inlineStr">
+        <is>
+          <t>Оплат</t>
+        </is>
+      </c>
+      <c r="H18" s="489" t="n"/>
+      <c r="I18" s="490" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="591" t="n"/>
+      <c r="B19" s="591" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЭПД </t>
+        </is>
+      </c>
+      <c r="C19" s="591" t="inlineStr">
+        <is>
+          <t>Савинская</t>
+        </is>
+      </c>
+      <c r="D19" s="592" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ЭПД Квиз - 9 шт, Заполнение CRM-формы "Внедрение и поддержка 1С:ЭПД" - 17 шт, Заявка с сайта - 1С-ЭПД | Обмен электронными перевозочными документами | Цена - 6 шт </t>
+        </is>
+      </c>
+      <c r="E19" s="592" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F19" s="683" t="inlineStr">
+        <is>
+          <t>ЭПД квиз  - 3 сделки (2 контроль оплаты),Заполнение CRM-формы "Внедрение и поддержка 1С:ЭПД" - 5 сделки (1 на контроле оплаты на 18 100), Заявка с сайта - 1С-ЭПД | Обмен электронными перевозочными документами | Цена - 5 сделок (2 оплаты, 3 на контроле оплаты)</t>
+        </is>
+      </c>
+      <c r="G19" s="468" t="inlineStr">
+        <is>
+          <t>2 шт/10 000 р</t>
+        </is>
+      </c>
+      <c r="H19" s="489" t="n"/>
+      <c r="I19" s="490" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="716" t="inlineStr">
-        <is>
-          <t>3. Обсуждаемые темы и выводы · блоки и тезисы</t>
-        </is>
-      </c>
+      <c r="A20" s="494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">МПП </t>
+        </is>
+      </c>
+      <c r="B20" s="593" t="inlineStr">
+        <is>
+          <t>Ссылка на лид</t>
+        </is>
+      </c>
+      <c r="C20" s="494" t="inlineStr">
+        <is>
+          <t>Клиент</t>
+        </is>
+      </c>
+      <c r="D20" s="494" t="inlineStr">
+        <is>
+          <t>Этап сделки</t>
+        </is>
+      </c>
+      <c r="E20" s="446" t="inlineStr">
+        <is>
+          <t>Поступила оплата</t>
+        </is>
+      </c>
+      <c r="F20" s="671" t="inlineStr">
+        <is>
+          <t>Время взятия ЛИДа в работу</t>
+        </is>
+      </c>
+      <c r="G20" s="671" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+      <c r="H20" s="481" t="n"/>
+      <c r="I20" s="481" t="n"/>
+      <c r="J20" s="481" t="n"/>
+      <c r="K20" s="481" t="n"/>
+      <c r="L20" s="481" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="594" t="n"/>
+      <c r="B21" s="636" t="n"/>
+      <c r="C21" s="594" t="n"/>
+      <c r="D21" s="596" t="n"/>
+      <c r="E21" s="448" t="n"/>
+      <c r="F21" s="496" t="n"/>
+      <c r="G21" s="496" t="n"/>
+      <c r="H21" s="492" t="n"/>
+      <c r="I21" s="492" t="n"/>
+      <c r="J21" s="482" t="n"/>
+      <c r="K21" s="482" t="n"/>
+      <c r="L21" s="482" t="n"/>
+    </row>
+    <row r="22" ht="53.05" customHeight="1">
+      <c r="A22" s="496" t="n"/>
+      <c r="B22" s="636" t="n"/>
+      <c r="C22" s="594" t="n"/>
+      <c r="D22" s="596" t="n"/>
+      <c r="E22" s="594" t="n"/>
+      <c r="F22" s="496" t="n"/>
+      <c r="G22" s="496" t="n"/>
+      <c r="H22" s="492" t="n"/>
+      <c r="I22" s="492" t="n"/>
+      <c r="J22" s="482" t="n"/>
+      <c r="K22" s="482" t="n"/>
+      <c r="L22" s="482" t="n"/>
+    </row>
+    <row r="23" ht="52.65" customHeight="1">
+      <c r="A23" s="496" t="n"/>
+      <c r="B23" s="636" t="n"/>
+      <c r="C23" s="594" t="n"/>
+      <c r="D23" s="599" t="n"/>
+      <c r="E23" s="594" t="n"/>
+      <c r="F23" s="632" t="n"/>
+      <c r="G23" s="632" t="n"/>
+      <c r="H23" s="492" t="n"/>
+      <c r="I23" s="492" t="n"/>
+      <c r="J23" s="482" t="n"/>
+      <c r="K23" s="482" t="n"/>
+      <c r="L23" s="482" t="n"/>
+    </row>
+    <row r="24" ht="49.7" customHeight="1">
+      <c r="A24" s="496" t="n"/>
+      <c r="B24" s="598" t="n"/>
+      <c r="C24" s="594" t="n"/>
+      <c r="D24" s="599" t="n"/>
+      <c r="E24" s="594" t="n"/>
+      <c r="F24" s="496" t="n"/>
+      <c r="G24" s="496" t="n"/>
+      <c r="H24" s="492" t="n"/>
+      <c r="I24" s="492" t="n"/>
+      <c r="J24" s="482" t="n"/>
+      <c r="K24" s="482" t="n"/>
+      <c r="L24" s="482" t="n"/>
+    </row>
+    <row r="25" ht="52.85" customHeight="1">
+      <c r="A25" s="496" t="n"/>
+      <c r="B25" s="598" t="n"/>
+      <c r="C25" s="594" t="n"/>
+      <c r="D25" s="599" t="n"/>
+      <c r="E25" s="594" t="n"/>
+      <c r="F25" s="496" t="n"/>
+      <c r="G25" s="496" t="n"/>
+      <c r="H25" s="492" t="n"/>
+      <c r="I25" s="492" t="n"/>
+      <c r="J25" s="482" t="n"/>
+      <c r="K25" s="482" t="n"/>
+      <c r="L25" s="482" t="n"/>
+    </row>
+    <row r="26" ht="38.45" customHeight="1">
+      <c r="A26" s="496" t="n"/>
+      <c r="B26" s="598" t="n"/>
+      <c r="C26" s="594" t="n"/>
+      <c r="D26" s="599" t="n"/>
+      <c r="E26" s="594" t="n"/>
+      <c r="F26" s="496" t="n"/>
+      <c r="G26" s="496" t="n"/>
+      <c r="H26" s="492" t="n"/>
+      <c r="I26" s="492" t="n"/>
+      <c r="J26" s="482" t="n"/>
+      <c r="K26" s="482" t="n"/>
+      <c r="L26" s="482" t="n"/>
+    </row>
+    <row r="27" ht="43.4" customHeight="1">
+      <c r="A27" s="496" t="n"/>
+      <c r="B27" s="600" t="n"/>
+      <c r="C27" s="594" t="n"/>
+      <c r="D27" s="599" t="n"/>
+      <c r="E27" s="594" t="n"/>
+      <c r="F27" s="496" t="n"/>
+      <c r="G27" s="496" t="n"/>
+      <c r="H27" s="492" t="n"/>
+      <c r="I27" s="492" t="n"/>
+      <c r="J27" s="482" t="n"/>
+      <c r="K27" s="482" t="n"/>
+      <c r="L27" s="482" t="n"/>
+    </row>
+    <row r="28" ht="91.25" customHeight="1">
+      <c r="A28" s="496" t="n"/>
+      <c r="B28" s="598" t="n"/>
+      <c r="C28" s="594" t="n"/>
+      <c r="D28" s="599" t="n"/>
+      <c r="E28" s="594" t="n"/>
+      <c r="F28" s="496" t="n"/>
+      <c r="G28" s="496" t="n"/>
+      <c r="H28" s="492" t="n"/>
+      <c r="I28" s="492" t="n"/>
+      <c r="J28" s="482" t="n"/>
+      <c r="K28" s="482" t="n"/>
+      <c r="L28" s="482" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="496" t="n"/>
+      <c r="B29" s="600" t="n"/>
+      <c r="C29" s="594" t="n"/>
+      <c r="D29" s="599" t="n"/>
+      <c r="E29" s="594" t="n"/>
+      <c r="F29" s="496" t="n"/>
+      <c r="G29" s="496" t="n"/>
+      <c r="H29" s="492" t="n"/>
+      <c r="I29" s="492" t="n"/>
+      <c r="J29" s="482" t="n"/>
+      <c r="K29" s="482" t="n"/>
+      <c r="L29" s="482" t="n"/>
+    </row>
+    <row r="30" ht="16.95" customHeight="1">
+      <c r="A30" s="496" t="n"/>
+      <c r="B30" s="601" t="n"/>
+      <c r="C30" s="594" t="n"/>
+      <c r="D30" s="602" t="n"/>
+      <c r="E30" s="594" t="n"/>
+      <c r="F30" s="496" t="n"/>
+      <c r="G30" s="496" t="n"/>
+      <c r="H30" s="492" t="n"/>
+      <c r="I30" s="492" t="n"/>
+      <c r="J30" s="482" t="n"/>
+      <c r="K30" s="482" t="n"/>
+      <c r="L30" s="482" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="496" t="n"/>
+      <c r="B31" s="603" t="n"/>
+      <c r="C31" s="594" t="n"/>
+      <c r="D31" s="604" t="n"/>
+      <c r="E31" s="603" t="n"/>
+      <c r="F31" s="496" t="n"/>
+      <c r="G31" s="496" t="n"/>
+      <c r="H31" s="492" t="n"/>
+      <c r="I31" s="492" t="n"/>
+      <c r="J31" s="482" t="n"/>
+      <c r="K31" s="482" t="n"/>
+      <c r="L31" s="482" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="502" t="n"/>
+      <c r="B32" s="503" t="n"/>
+      <c r="C32" s="504" t="n"/>
+      <c r="D32" s="505" t="n"/>
+      <c r="E32" s="508" t="n"/>
+      <c r="F32" s="496" t="n"/>
+      <c r="G32" s="496" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="110" t="n"/>
+      <c r="B33" s="57" t="n"/>
+      <c r="C33" s="89" t="n"/>
+      <c r="D33" s="184" t="n"/>
+      <c r="E33" s="113" t="n"/>
+      <c r="F33" s="496" t="n"/>
+      <c r="G33" s="496" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="672" t="inlineStr">
+        <is>
+          <t>1. Мониторинг предыдущих решений:</t>
+        </is>
+      </c>
+      <c r="B34" s="672" t="n"/>
+      <c r="C34" s="672" t="n"/>
+      <c r="D34" s="672" t="n"/>
+      <c r="E34" s="672" t="n"/>
+      <c r="F34" s="672" t="n"/>
+      <c r="G34" s="672" t="n"/>
+    </row>
+    <row r="35" ht="14.25" customHeight="1">
+      <c r="A35" s="590" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B35" s="590" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C35" s="590" t="inlineStr">
+        <is>
+          <t>Лидер</t>
+        </is>
+      </c>
+      <c r="D35" s="590" t="inlineStr">
+        <is>
+          <t>Срок</t>
+        </is>
+      </c>
+      <c r="E35" s="590" t="inlineStr">
+        <is>
+          <t>Статус*</t>
+        </is>
+      </c>
+      <c r="F35" s="590" t="inlineStr">
+        <is>
+          <t>Комментарии. Выводы</t>
+        </is>
+      </c>
+      <c r="G35" s="718" t="n"/>
+    </row>
+    <row r="36" ht="19.2" customHeight="1">
+      <c r="A36" s="606" t="n"/>
+      <c r="B36" s="653" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Включить поле время взятия в работу заявки с РК </t>
+        </is>
+      </c>
+      <c r="C36" s="654" t="inlineStr">
+        <is>
+          <t>Савинская</t>
+        </is>
+      </c>
+      <c r="D36" s="654" t="inlineStr">
+        <is>
+          <t>до 27.08</t>
+        </is>
+      </c>
+      <c r="E36" s="656" t="inlineStr">
+        <is>
+          <t xml:space="preserve">выполнено </t>
+        </is>
+      </c>
+      <c r="F36" s="656" t="n"/>
+      <c r="G36" s="718" t="n"/>
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
+      <c r="A37" s="719" t="n"/>
+      <c r="B37" s="657" t="inlineStr">
+        <is>
+          <t>Обсудить разделения стоимости РК между ЦП и ЦКС на очной встрече 27.08</t>
+        </is>
+      </c>
+      <c r="C37" s="657" t="inlineStr">
+        <is>
+          <t>все участники (Антонов В , Дербенева К)</t>
+        </is>
+      </c>
+      <c r="D37" s="657" t="inlineStr">
+        <is>
+          <t xml:space="preserve">до 27.08 </t>
+        </is>
+      </c>
+      <c r="E37" s="658" t="inlineStr">
+        <is>
+          <t xml:space="preserve">в работе </t>
+        </is>
+      </c>
+      <c r="F37" s="670" t="n"/>
+      <c r="G37" s="718" t="n"/>
+    </row>
+    <row r="38" ht="15.5" customHeight="1">
+      <c r="A38" s="720" t="n"/>
+      <c r="B38" s="660" t="inlineStr">
+        <is>
+          <t>текущая РК действует до середины сентября. Что дальше? Будем продлевать? Вопрос согласования бюджета</t>
+        </is>
+      </c>
+      <c r="C38" s="660" t="inlineStr">
+        <is>
+          <t>все участники</t>
+        </is>
+      </c>
+      <c r="D38" s="661" t="inlineStr">
+        <is>
+          <t>до 27.08</t>
+        </is>
+      </c>
+      <c r="E38" s="656" t="inlineStr">
+        <is>
+          <t xml:space="preserve">в работе </t>
+        </is>
+      </c>
+      <c r="F38" s="656" t="n"/>
+      <c r="G38" s="718" t="n"/>
+    </row>
+    <row r="39" ht="19.6" customHeight="1">
+      <c r="A39" s="719" t="n"/>
+      <c r="B39" s="662" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать ОС от МПП по поводу сервиса ЭПД (что говорят клиенты)  - основные проблемы, возражения и потребности </t>
+        </is>
+      </c>
+      <c r="C39" s="662" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Савинская/Блохина/Степанова </t>
+        </is>
+      </c>
+      <c r="D39" s="663" t="inlineStr">
+        <is>
+          <t>до 24.08 к 12:00</t>
+        </is>
+      </c>
+      <c r="E39" s="664" t="inlineStr">
+        <is>
+          <t>выполнено</t>
+        </is>
+      </c>
+      <c r="F39" s="665" t="inlineStr">
+        <is>
+          <t>создан документ (в беседе: ЭПДстратегия)</t>
+        </is>
+      </c>
+      <c r="G39" s="718" t="n"/>
+    </row>
+    <row r="40" ht="19.25" customHeight="1">
+      <c r="A40" s="721" t="n"/>
+      <c r="B40" s="666" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Собрать портрет клиента, который купил ЭПД </t>
+        </is>
+      </c>
+      <c r="C40" s="666" t="inlineStr">
+        <is>
+          <t>Корнева/Степанова</t>
+        </is>
+      </c>
+      <c r="D40" s="667" t="inlineStr">
+        <is>
+          <t>до 27.08</t>
+        </is>
+      </c>
+      <c r="E40" s="668" t="inlineStr">
+        <is>
+          <t xml:space="preserve">в работе </t>
+        </is>
+      </c>
+      <c r="F40" s="669" t="inlineStr">
+        <is>
+          <t>Коля, после встречи напишет Насте параметры, по которым будем собирать портрет клиента.</t>
+        </is>
+      </c>
+      <c r="G40" s="718" t="n"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>При чем тут Коля?</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="14.7" customHeight="1">
+      <c r="A41" s="719" t="n"/>
+      <c r="B41" s="657" t="inlineStr">
+        <is>
+          <t>Добавить Корневу и Степанову во встречу с Калугой</t>
+        </is>
+      </c>
+      <c r="C41" s="657" t="inlineStr">
+        <is>
+          <t>Блохина</t>
+        </is>
+      </c>
+      <c r="D41" s="663" t="inlineStr">
+        <is>
+          <t xml:space="preserve">до 24.08 </t>
+        </is>
+      </c>
+      <c r="E41" s="670" t="inlineStr">
+        <is>
+          <t>выполнено</t>
+        </is>
+      </c>
+      <c r="F41" s="657" t="n"/>
+      <c r="G41" s="718" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="673" t="n"/>
+      <c r="B42" s="396" t="inlineStr">
+        <is>
+          <t>Построить финансовую модель направления ЭПД – с учётом доходов (титулы, услуги, продления), затрат (реклама, зарплаты, производство), прогнозов по конверсиям и сценариев (с учётом возможного переноса штрафов).</t>
+        </is>
+      </c>
+      <c r="C42" s="666" t="inlineStr">
+        <is>
+          <t>Все участники</t>
+        </is>
+      </c>
+      <c r="D42" s="682" t="inlineStr">
+        <is>
+          <t xml:space="preserve">после стратег‑сессии </t>
+        </is>
+      </c>
+      <c r="E42" s="675" t="n"/>
+      <c r="F42" s="678" t="n"/>
+      <c r="G42" s="718" t="n"/>
+    </row>
+    <row r="43" ht="14.25" customHeight="1">
+      <c r="A43" s="115" t="n"/>
+      <c r="B43" s="161" t="n"/>
+      <c r="C43" s="161" t="n"/>
+      <c r="D43" s="162" t="n"/>
+      <c r="E43" s="172" t="n"/>
+      <c r="F43" s="409" t="n"/>
+      <c r="G43" s="718" t="n"/>
+    </row>
+    <row r="44" ht="14.25" customHeight="1">
+      <c r="A44" s="502" t="n"/>
+      <c r="B44" s="503" t="n"/>
+      <c r="C44" s="504" t="n"/>
+      <c r="D44" s="505" t="n"/>
+      <c r="E44" s="508" t="n"/>
+      <c r="F44" s="507" t="n"/>
+      <c r="G44" s="718" t="n"/>
+    </row>
+    <row r="45" ht="14.25" customHeight="1">
+      <c r="A45" s="134" t="n"/>
+      <c r="B45" s="72" t="n"/>
+      <c r="C45" s="88" t="n"/>
+      <c r="D45" s="135" t="n"/>
+      <c r="E45" s="624" t="n"/>
+      <c r="F45" s="86" t="n"/>
+      <c r="G45" s="718" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="589" t="inlineStr">
+        <is>
+          <t>2. Решения текущей встречи:</t>
+        </is>
+      </c>
+      <c r="B46" s="717" t="n"/>
+      <c r="C46" s="717" t="n"/>
+      <c r="D46" s="717" t="n"/>
+      <c r="E46" s="717" t="n"/>
+      <c r="F46" s="717" t="n"/>
+      <c r="G46" s="718" t="n"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1">
+      <c r="A47" s="702" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B47" s="702" t="inlineStr">
+        <is>
+          <t>Задача</t>
+        </is>
+      </c>
+      <c r="C47" s="702" t="inlineStr">
+        <is>
+          <t>Лидер</t>
+        </is>
+      </c>
+      <c r="D47" s="702" t="inlineStr">
+        <is>
+          <t>Срок</t>
+        </is>
+      </c>
+      <c r="E47" s="702" t="inlineStr">
+        <is>
+          <t>Статус*</t>
+        </is>
+      </c>
+      <c r="F47" s="702" t="inlineStr">
+        <is>
+          <t>Комментарии. Выводы</t>
+        </is>
+      </c>
+      <c r="G47" s="718" t="n"/>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="714" t="n">
+        <v>1</v>
+      </c>
+      <c r="B48" s="712" t="inlineStr">
+        <is>
+          <t>Разобраться с показателями охвата сервисом наших клиентов 1С-ЭПД из таблицы А. Дворяк</t>
+        </is>
+      </c>
+      <c r="C48" s="708" t="inlineStr">
+        <is>
+          <t>Корнева, Степанова</t>
+        </is>
+      </c>
+      <c r="D48" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E48" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F48" s="724" t="inlineStr">
+        <is>
+          <t>9000 ед. в охвате — уточнить: подключение или предоплаченные пакеты? Цифры расходятся с Калугой.</t>
+        </is>
+      </c>
+      <c r="G48" s="704" t="n"/>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="714" t="n">
+        <v>2</v>
+      </c>
+      <c r="B49" s="712" t="inlineStr">
+        <is>
+          <t>Уточнить у Суворовой статус Элиттрейд; предложить акцию 3 мес. Доки для захода к контрагентам</t>
+        </is>
+      </c>
+      <c r="C49" s="708" t="inlineStr">
+        <is>
+          <t>Блохина</t>
+        </is>
+      </c>
+      <c r="D49" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E49" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F49" s="724" t="inlineStr">
+        <is>
+          <t>Крупные производители задают правила → возможность выхода на контрагентов.</t>
+        </is>
+      </c>
+      <c r="G49" s="704" t="n"/>
+    </row>
+    <row r="50" ht="36" customHeight="1">
+      <c r="A50" s="714" t="n">
+        <v>3</v>
+      </c>
+      <c r="B50" s="712" t="inlineStr">
+        <is>
+          <t>Подключить Антона Гуркова к процессу изучения привязки клиента (Доки.Логистика / ЦКС)</t>
+        </is>
+      </c>
+      <c r="C50" s="708" t="inlineStr">
+        <is>
+          <t>Гурков А.</t>
+        </is>
+      </c>
+      <c r="D50" s="722" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="E50" s="725" t="inlineStr">
+        <is>
+          <t>взял на себя</t>
+        </is>
+      </c>
+      <c r="F50" s="724" t="inlineStr">
+        <is>
+          <t>Задача О. Ремез — прописать подробнее после пересмотра встречи.</t>
+        </is>
+      </c>
+      <c r="G50" s="704" t="n"/>
+    </row>
+    <row r="51" ht="36" customHeight="1">
+      <c r="A51" s="714" t="n">
+        <v>4</v>
+      </c>
+      <c r="B51" s="712" t="inlineStr">
+        <is>
+          <t>Выяснить у Калуги: можно ли отследить активность клиента в сервисе Доки</t>
+        </is>
+      </c>
+      <c r="C51" s="708" t="inlineStr">
+        <is>
+          <t>Дивакова М.</t>
+        </is>
+      </c>
+      <c r="D51" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E51" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F51" s="724" t="inlineStr"/>
+      <c r="G51" s="704" t="n"/>
+    </row>
+    <row r="52" ht="36" customHeight="1">
+      <c r="A52" s="714" t="n">
+        <v>5</v>
+      </c>
+      <c r="B52" s="712" t="inlineStr">
+        <is>
+          <t>Уточнить у Никитченко: считается ли Доки в охват сервисами ЭПД</t>
+        </is>
+      </c>
+      <c r="C52" s="708" t="inlineStr">
+        <is>
+          <t>Дворяк</t>
+        </is>
+      </c>
+      <c r="D52" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E52" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F52" s="724" t="inlineStr">
+        <is>
+          <t>Саша спросит.</t>
+        </is>
+      </c>
+      <c r="G52" s="704" t="n"/>
+    </row>
+    <row r="53" ht="36" customHeight="1">
+      <c r="A53" s="714" t="n">
+        <v>6</v>
+      </c>
+      <c r="B53" s="712" t="inlineStr">
+        <is>
+          <t>Подготовить со СМАК материалы для прогрева клиента на период демо-доступа</t>
+        </is>
+      </c>
+      <c r="C53" s="708" t="inlineStr">
+        <is>
+          <t>СМАК</t>
+        </is>
+      </c>
+      <c r="D53" s="722" t="inlineStr">
+        <is>
+          <t>к 01.10</t>
+        </is>
+      </c>
+      <c r="E53" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F53" s="724" t="inlineStr">
+        <is>
+          <t>С 01.10 демо = 14 дней; до 01.10 — 3 месяца бесплатно.</t>
+        </is>
+      </c>
+      <c r="G53" s="704" t="n"/>
+    </row>
+    <row r="54" ht="36" customHeight="1">
+      <c r="A54" s="714" t="n">
+        <v>7</v>
+      </c>
+      <c r="B54" s="712" t="inlineStr">
+        <is>
+          <t>Подготовить калькулятор пополнения титулов для менеджеров ЦКС</t>
+        </is>
+      </c>
+      <c r="C54" s="708" t="inlineStr">
+        <is>
+          <t>Вика / Маша</t>
+        </is>
+      </c>
+      <c r="D54" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E54" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F54" s="724" t="inlineStr">
+        <is>
+          <t>Обсуждали накануне лектория с 1С.</t>
+        </is>
+      </c>
+      <c r="G54" s="704" t="n"/>
+    </row>
+    <row r="55" ht="36" customHeight="1">
+      <c r="A55" s="714" t="n">
+        <v>8</v>
+      </c>
+      <c r="B55" s="712" t="inlineStr">
+        <is>
+          <t>Подготовить текст рассылки «проверьте контрагента и впишите в тандем» — сроки и текст</t>
+        </is>
+      </c>
+      <c r="C55" s="708" t="inlineStr">
+        <is>
+          <t>Блохина</t>
+        </is>
+      </c>
+      <c r="D55" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E55" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F55" s="724" t="inlineStr"/>
+      <c r="G55" s="704" t="n"/>
+    </row>
+    <row r="56" ht="36" customHeight="1">
+      <c r="A56" s="714" t="n">
+        <v>9</v>
+      </c>
+      <c r="B56" s="712" t="inlineStr">
+        <is>
+          <t>Обзвонить крупных клиентов (от 2000 титулов / генераторы трафика) и предложить ЭПД ТАНДЕМ</t>
+        </is>
+      </c>
+      <c r="C56" s="708" t="inlineStr">
+        <is>
+          <t>ЦП / ЦКС</t>
+        </is>
+      </c>
+      <c r="D56" s="722" t="inlineStr">
+        <is>
+          <t>сентябрь</t>
+        </is>
+      </c>
+      <c r="E56" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F56" s="724" t="inlineStr">
+        <is>
+          <t>Начать с крупных. Корп. сегмент продавал ЭПД даже в малом объёме.</t>
+        </is>
+      </c>
+      <c r="G56" s="704" t="n"/>
+    </row>
+    <row r="57" ht="36" customHeight="1">
+      <c r="A57" s="714" t="n">
+        <v>10</v>
+      </c>
+      <c r="B57" s="712" t="inlineStr">
+        <is>
+          <t>Обзвон подключённых клиентов: оценка удовлетворённости + проекты ЦАС (Доки)</t>
+        </is>
+      </c>
+      <c r="C57" s="708" t="inlineStr">
+        <is>
+          <t>Дворяк / Лазарчук</t>
+        </is>
+      </c>
+      <c r="D57" s="722" t="inlineStr">
+        <is>
+          <t>сентябрь</t>
+        </is>
+      </c>
+      <c r="E57" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F57" s="724" t="inlineStr">
+        <is>
+          <t>Задача по клиентам ЦАС (Доки).</t>
+        </is>
+      </c>
+      <c r="G57" s="704" t="n"/>
+    </row>
+    <row r="58" ht="36" customHeight="1">
+      <c r="A58" s="714" t="n">
+        <v>11</v>
+      </c>
+      <c r="B58" s="712" t="inlineStr">
+        <is>
+          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в 1-ю неделю сентября</t>
+        </is>
+      </c>
+      <c r="C58" s="708" t="inlineStr">
+        <is>
+          <t>Юлиана</t>
+        </is>
+      </c>
+      <c r="D58" s="722" t="inlineStr">
+        <is>
+          <t>1-я нед. сентября</t>
+        </is>
+      </c>
+      <c r="E58" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F58" s="724" t="inlineStr">
+        <is>
+          <t>Клиенты сбытового офиса уходят на СБИС — разобрать причины.</t>
+        </is>
+      </c>
+      <c r="G58" s="704" t="n"/>
+    </row>
+    <row r="59" ht="36" customHeight="1">
+      <c r="A59" s="714" t="n">
+        <v>12</v>
+      </c>
+      <c r="B59" s="712" t="inlineStr">
+        <is>
+          <t>Проверить в базе подключение клиентов к каналу ЭПД (МАКС / ТГ / ВК) как альт. канал</t>
+        </is>
+      </c>
+      <c r="C59" s="708" t="inlineStr">
+        <is>
+          <t>ЦП / ЦКС</t>
+        </is>
+      </c>
+      <c r="D59" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E59" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F59" s="724" t="inlineStr">
+        <is>
+          <t>Связать со стратегией и целями.</t>
+        </is>
+      </c>
+      <c r="G59" s="704" t="n"/>
+    </row>
+    <row r="60" ht="36" customHeight="1">
+      <c r="A60" s="714" t="n">
+        <v>13</v>
+      </c>
+      <c r="B60" s="712" t="inlineStr">
+        <is>
+          <t>Зафиксировать план 500 клиентов до конца 2026: 50 крупных / 300 средних / 150 мелких</t>
+        </is>
+      </c>
+      <c r="C60" s="708" t="inlineStr">
+        <is>
+          <t>Все участники</t>
+        </is>
+      </c>
+      <c r="D60" s="722" t="inlineStr">
+        <is>
+          <t>принято</t>
+        </is>
+      </c>
+      <c r="E60" s="725" t="inlineStr">
+        <is>
+          <t>принято</t>
+        </is>
+      </c>
+      <c r="F60" s="724" t="inlineStr">
+        <is>
+          <t>Приоритет — количество клиентов, не сумма выручки на старте.</t>
+        </is>
+      </c>
+      <c r="G60" s="704" t="n"/>
+    </row>
+    <row r="61" ht="34.15" customHeight="1">
+      <c r="A61" s="589" t="inlineStr">
+        <is>
+          <t>3. Обсуждаемые темы и выводы:</t>
+        </is>
+      </c>
+      <c r="B61" s="717" t="n"/>
+      <c r="C61" s="717" t="n"/>
+      <c r="D61" s="717" t="n"/>
+      <c r="E61" s="717" t="n"/>
+      <c r="F61" s="717" t="n"/>
+      <c r="G61" s="718" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="726" t="inlineStr">
+        <is>
+          <t>Обсуждаемая тема (проблема)</t>
+        </is>
+      </c>
+      <c r="B62" s="713" t="n"/>
+      <c r="C62" s="713" t="n"/>
+      <c r="D62" s="726" t="inlineStr">
+        <is>
+          <t>Выводы и решения</t>
+        </is>
+      </c>
+      <c r="E62" s="713" t="n"/>
+      <c r="F62" s="713" t="n"/>
+      <c r="G62" s="713" t="n"/>
+      <c r="H62" s="727" t="n"/>
+      <c r="I62" s="727" t="n"/>
+    </row>
+    <row r="63" ht="18" customHeight="1">
+      <c r="A63" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Акция и ЦСВ</t>
+        </is>
+      </c>
+      <c r="B63" s="698" t="n"/>
+      <c r="C63" s="698" t="n"/>
+      <c r="D63" s="698" t="n"/>
+      <c r="E63" s="698" t="n"/>
+      <c r="F63" s="698" t="n"/>
+      <c r="G63" s="698" t="n"/>
+      <c r="H63" s="727" t="n"/>
+      <c r="I63" s="727" t="n"/>
+    </row>
+    <row r="64" ht="48" customHeight="1">
+      <c r="A64" s="724" t="inlineStr">
+        <is>
+          <t>Обсудить с ЦСВ трудозатраты на акцию по ЭПД.</t>
+        </is>
+      </c>
+      <c r="B64" s="704" t="n"/>
+      <c r="C64" s="704" t="n"/>
+      <c r="D64" s="724" t="inlineStr">
+        <is>
+          <t>Оксана: уточнить адресата вопроса. Акцию продлили до 30.09.</t>
+        </is>
+      </c>
+      <c r="E64" s="704" t="n"/>
+      <c r="F64" s="704" t="n"/>
+      <c r="G64" s="704" t="n"/>
+      <c r="H64" s="727" t="n"/>
+      <c r="I64" s="727" t="n"/>
+    </row>
+    <row r="65" ht="18" customHeight="1">
+      <c r="A65" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Каналы МАКС / ТГ / ВК</t>
+        </is>
+      </c>
+      <c r="B65" s="698" t="n"/>
+      <c r="C65" s="698" t="n"/>
+      <c r="D65" s="698" t="n"/>
+      <c r="E65" s="698" t="n"/>
+      <c r="F65" s="698" t="n"/>
+      <c r="G65" s="698" t="n"/>
+      <c r="H65" s="727" t="n"/>
+      <c r="I65" s="727" t="n"/>
+    </row>
+    <row r="66" ht="48" customHeight="1">
+      <c r="A66" s="724" t="inlineStr">
+        <is>
+          <t>Канал ЭПД в МАКС, ТГ, ВК. Можем ли прорабатывать этих клиентов силами ЦП и ЦКС? Связать со стратегией; альтернативный канал привлечения.</t>
+        </is>
+      </c>
+      <c r="B66" s="704" t="n"/>
+      <c r="C66" s="704" t="n"/>
+      <c r="D66" s="724" t="inlineStr">
+        <is>
+          <t>Проверить из базы: подключён клиент к каналу или нет. Идея — просить менеджеров подключать клиентов (вопрос мотивации клиента открыт).</t>
+        </is>
+      </c>
+      <c r="E66" s="704" t="n"/>
+      <c r="F66" s="704" t="n"/>
+      <c r="G66" s="704" t="n"/>
+      <c r="H66" s="727" t="n"/>
+      <c r="I66" s="727" t="n"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Стратегия и сегментация</t>
+        </is>
+      </c>
+      <c r="B67" s="698" t="n"/>
+      <c r="C67" s="698" t="n"/>
+      <c r="D67" s="698" t="n"/>
+      <c r="E67" s="698" t="n"/>
+      <c r="F67" s="698" t="n"/>
+      <c r="G67" s="698" t="n"/>
+      <c r="H67" s="727" t="n"/>
+      <c r="I67" s="727" t="n"/>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="724" t="inlineStr">
+        <is>
+          <t>Заход в Элиттрейд (таблица А. Дворяк) — выход к контрагентам. Предложение Гуркова: сегментировать охваченных на крупных / средних / мелких.</t>
+        </is>
+      </c>
+      <c r="B68" s="704" t="n"/>
+      <c r="C68" s="704" t="n"/>
+      <c r="D68" s="729" t="inlineStr">
+        <is>
+          <t>Производители (крупные) задают правила для перевозчиков → те для получателей. Лиза уточнит у Суворовой статус Элиттрейд; можно предложить акцию 3 мес. Доки.</t>
+        </is>
+      </c>
+      <c r="E68" s="730" t="n"/>
+      <c r="F68" s="730" t="n"/>
+      <c r="G68" s="730" t="n"/>
+      <c r="H68" s="727" t="n"/>
+      <c r="I68" s="727" t="n"/>
+    </row>
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="724" t="inlineStr">
+        <is>
+          <t>К признаку «крупный» добавить: является ли клиент генератором трафика (привлечение контрагентов).</t>
+        </is>
+      </c>
+      <c r="B69" s="704" t="n"/>
+      <c r="C69" s="704" t="n"/>
+      <c r="D69" s="724" t="inlineStr">
+        <is>
+          <t>По соотношению базы (крупные / средние / мелкие) пришли к соглашению по процентам.</t>
+        </is>
+      </c>
+      <c r="E69" s="704" t="n"/>
+      <c r="F69" s="704" t="n"/>
+      <c r="G69" s="704" t="n"/>
+      <c r="H69" s="727" t="n"/>
+      <c r="I69" s="727" t="n"/>
+    </row>
+    <row r="70" ht="48" customHeight="1">
+      <c r="A70" s="724" t="inlineStr">
+        <is>
+          <t>Приоритет — количество привлечённых клиентов, а не сумма заработка. Выстроить цепочку «закрепления» и почкования с одного пакета на новых клиентов.</t>
+        </is>
+      </c>
+      <c r="B70" s="704" t="n"/>
+      <c r="C70" s="704" t="n"/>
+      <c r="D70" s="729" t="inlineStr">
+        <is>
+          <t>ПЛАН: 500 клиентов до конца 2026 → 50 крупных + 300 средних + 150 мелких.</t>
+        </is>
+      </c>
+      <c r="E70" s="730" t="n"/>
+      <c r="F70" s="730" t="n"/>
+      <c r="G70" s="730" t="n"/>
+      <c r="H70" s="727" t="n"/>
+      <c r="I70" s="727" t="n"/>
+    </row>
+    <row r="71" ht="18" customHeight="1">
+      <c r="A71" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Доки.Логистика и охват</t>
+        </is>
+      </c>
+      <c r="B71" s="698" t="n"/>
+      <c r="C71" s="698" t="n"/>
+      <c r="D71" s="698" t="n"/>
+      <c r="E71" s="698" t="n"/>
+      <c r="F71" s="698" t="n"/>
+      <c r="G71" s="698" t="n"/>
+      <c r="H71" s="727" t="n"/>
+      <c r="I71" s="727" t="n"/>
+    </row>
+    <row r="72" ht="48" customHeight="1">
+      <c r="A72" s="724" t="inlineStr">
+        <is>
+          <t>Задача по Доки.Логистика (Оксана Ремез) — прописать подробнее после пересмотра встречи.</t>
+        </is>
+      </c>
+      <c r="B72" s="704" t="n"/>
+      <c r="C72" s="704" t="n"/>
+      <c r="D72" s="729" t="inlineStr">
+        <is>
+          <t>Подключить Антона Гуркова к изучению привязки клиента. Антон взял на себя.</t>
+        </is>
+      </c>
+      <c r="E72" s="730" t="n"/>
+      <c r="F72" s="730" t="n"/>
+      <c r="G72" s="730" t="n"/>
+      <c r="H72" s="727" t="n"/>
+      <c r="I72" s="727" t="n"/>
+    </row>
+    <row r="73" ht="48" customHeight="1">
+      <c r="A73" s="724" t="inlineStr">
+        <is>
+          <t>Можем ли отследить активность клиента в сервисе Доки? (вопрос Калуге)</t>
+        </is>
+      </c>
+      <c r="B73" s="704" t="n"/>
+      <c r="C73" s="704" t="n"/>
+      <c r="D73" s="729" t="inlineStr">
+        <is>
+          <t>Маша Дивакова выяснит.</t>
+        </is>
+      </c>
+      <c r="E73" s="730" t="n"/>
+      <c r="F73" s="730" t="n"/>
+      <c r="G73" s="730" t="n"/>
+      <c r="H73" s="727" t="n"/>
+      <c r="I73" s="727" t="n"/>
+    </row>
+    <row r="74" ht="48" customHeight="1">
+      <c r="A74" s="724" t="inlineStr">
+        <is>
+          <t>Считается ли Доки в охват сервисами ЭПД?</t>
+        </is>
+      </c>
+      <c r="B74" s="704" t="n"/>
+      <c r="C74" s="704" t="n"/>
+      <c r="D74" s="729" t="inlineStr">
+        <is>
+          <t>Вопрос Никитченко — Саша спросит. Цифры расходятся с Калугой; проблемы с закреплением.</t>
+        </is>
+      </c>
+      <c r="E74" s="730" t="n"/>
+      <c r="F74" s="730" t="n"/>
+      <c r="G74" s="730" t="n"/>
+      <c r="H74" s="727" t="n"/>
+      <c r="I74" s="727" t="n"/>
+    </row>
+    <row r="75" ht="48" customHeight="1">
+      <c r="A75" s="724" t="inlineStr">
+        <is>
+          <t>Все проданные ЭПД: центр компетенции изучает — всё ли продано, подключились ли.</t>
+        </is>
+      </c>
+      <c r="B75" s="704" t="n"/>
+      <c r="C75" s="704" t="n"/>
+      <c r="D75" s="724" t="inlineStr">
+        <is>
+          <t>Трафик не видим → не квалифицируем активность пользования пакетом. 1С обещают данные в сентябре.</t>
+        </is>
+      </c>
+      <c r="E75" s="704" t="n"/>
+      <c r="F75" s="704" t="n"/>
+      <c r="G75" s="704" t="n"/>
+      <c r="H75" s="727" t="n"/>
+      <c r="I75" s="727" t="n"/>
+    </row>
+    <row r="76" ht="18" customHeight="1">
+      <c r="A76" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Демо и прогрев (СМАК)</t>
+        </is>
+      </c>
+      <c r="B76" s="698" t="n"/>
+      <c r="C76" s="698" t="n"/>
+      <c r="D76" s="698" t="n"/>
+      <c r="E76" s="698" t="n"/>
+      <c r="F76" s="698" t="n"/>
+      <c r="G76" s="698" t="n"/>
+      <c r="H76" s="727" t="n"/>
+      <c r="I76" s="727" t="n"/>
+    </row>
+    <row r="77" ht="48" customHeight="1">
+      <c r="A77" s="724" t="inlineStr">
+        <is>
+          <t>Со СМАК подготовить материалы для прогрева клиента во время демо-доступа.</t>
+        </is>
+      </c>
+      <c r="B77" s="704" t="n"/>
+      <c r="C77" s="704" t="n"/>
+      <c r="D77" s="724" t="inlineStr">
+        <is>
+          <t>С 01.10 — 14 дней демо; до 01.10 — 3 месяца бесплатно.</t>
+        </is>
+      </c>
+      <c r="E77" s="704" t="n"/>
+      <c r="F77" s="704" t="n"/>
+      <c r="G77" s="704" t="n"/>
+      <c r="H77" s="727" t="n"/>
+      <c r="I77" s="727" t="n"/>
+    </row>
+    <row r="78" ht="18" customHeight="1">
+      <c r="A78" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Сопровождение МПП / ЦКС</t>
+        </is>
+      </c>
+      <c r="B78" s="698" t="n"/>
+      <c r="C78" s="698" t="n"/>
+      <c r="D78" s="698" t="n"/>
+      <c r="E78" s="698" t="n"/>
+      <c r="F78" s="698" t="n"/>
+      <c r="G78" s="698" t="n"/>
+      <c r="H78" s="727" t="n"/>
+      <c r="I78" s="727" t="n"/>
+    </row>
+    <row r="79" ht="48" customHeight="1">
+      <c r="A79" s="724" t="inlineStr">
+        <is>
+          <t>План для МПП: платные / бесплатные клиенты; «выхаживать» может другой человек (идея — Антон Гурков).</t>
+        </is>
+      </c>
+      <c r="B79" s="704" t="n"/>
+      <c r="C79" s="704" t="n"/>
+      <c r="D79" s="724" t="inlineStr">
+        <is>
+          <t>Если есть ИТС — менеджер ЦКС смотрит динамику расхода ЭПД/Доки. Трафика пока нет; можно писать в Калугу с перечнем ИНН. Риск: кто выхаживает — текущие менеджеры или новый человек?</t>
+        </is>
+      </c>
+      <c r="E79" s="704" t="n"/>
+      <c r="F79" s="704" t="n"/>
+      <c r="G79" s="704" t="n"/>
+      <c r="H79" s="727" t="n"/>
+      <c r="I79" s="727" t="n"/>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="724" t="inlineStr">
+        <is>
+          <t>Клиенту продают минимальный пакет («пока не понятно»). Кто ведёт дальше при продлении? Получают ли ЦКС сигнал о дозакупке титулов?</t>
+        </is>
+      </c>
+      <c r="B80" s="704" t="n"/>
+      <c r="C80" s="704" t="n"/>
+      <c r="D80" s="724" t="inlineStr">
+        <is>
+          <t>По логике — ЦКС. Нужен калькулятор — Вика с Машей обсуждали накануне лектория с 1С.</t>
+        </is>
+      </c>
+      <c r="E80" s="704" t="n"/>
+      <c r="F80" s="704" t="n"/>
+      <c r="G80" s="704" t="n"/>
+      <c r="H80" s="727" t="n"/>
+      <c r="I80" s="727" t="n"/>
+    </row>
+    <row r="81" ht="48" customHeight="1">
+      <c r="A81" s="724" t="inlineStr">
+        <is>
+          <t>Ожидание: ЦКС категоризирует клиента по кол-ву титулов / УАТ и своевременно пополняет баланс.</t>
+        </is>
+      </c>
+      <c r="B81" s="704" t="n"/>
+      <c r="C81" s="704" t="n"/>
+      <c r="D81" s="724" t="inlineStr">
+        <is>
+          <t>Зафиксировано как рабочий процесс.</t>
+        </is>
+      </c>
+      <c r="E81" s="704" t="n"/>
+      <c r="F81" s="704" t="n"/>
+      <c r="G81" s="704" t="n"/>
+      <c r="H81" s="727" t="n"/>
+      <c r="I81" s="727" t="n"/>
+    </row>
+    <row r="82" ht="18" customHeight="1">
+      <c r="A82" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Тандем и обзвоны</t>
+        </is>
+      </c>
+      <c r="B82" s="698" t="n"/>
+      <c r="C82" s="698" t="n"/>
+      <c r="D82" s="698" t="n"/>
+      <c r="E82" s="698" t="n"/>
+      <c r="F82" s="698" t="n"/>
+      <c r="G82" s="698" t="n"/>
+      <c r="H82" s="727" t="n"/>
+      <c r="I82" s="727" t="n"/>
+    </row>
+    <row r="83" ht="48" customHeight="1">
+      <c r="A83" s="724" t="inlineStr">
+        <is>
+          <t>Рассылка по клиентам: «проверьте своего контрагента и впишите в тандем».</t>
+        </is>
+      </c>
+      <c r="B83" s="704" t="n"/>
+      <c r="C83" s="704" t="n"/>
+      <c r="D83" s="729" t="inlineStr">
+        <is>
+          <t>Лиза — когда и какой текст.</t>
+        </is>
+      </c>
+      <c r="E83" s="730" t="n"/>
+      <c r="F83" s="730" t="n"/>
+      <c r="G83" s="730" t="n"/>
+      <c r="H83" s="727" t="n"/>
+      <c r="I83" s="727" t="n"/>
+    </row>
+    <row r="84" ht="48" customHeight="1">
+      <c r="A84" s="724" t="inlineStr">
+        <is>
+          <t>Начать с крупных клиентов: прозвонить и предложить подключить контрагента в ЭПД ТАНДЕМ.</t>
+        </is>
+      </c>
+      <c r="B84" s="704" t="n"/>
+      <c r="C84" s="704" t="n"/>
+      <c r="D84" s="724" t="inlineStr">
+        <is>
+          <t>Крупные = от 2000 титулов. Корп. клиенты продавали ЭПД даже в малом объёме.</t>
+        </is>
+      </c>
+      <c r="E84" s="704" t="n"/>
+      <c r="F84" s="704" t="n"/>
+      <c r="G84" s="704" t="n"/>
+      <c r="H84" s="727" t="n"/>
+      <c r="I84" s="727" t="n"/>
+    </row>
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="724" t="inlineStr">
+        <is>
+          <t>Обзвон подключённых клиентов: оценка удовлетворённости + проекты ЦАС (Доки).</t>
+        </is>
+      </c>
+      <c r="B85" s="704" t="n"/>
+      <c r="C85" s="704" t="n"/>
+      <c r="D85" s="729" t="inlineStr">
+        <is>
+          <t>Задача на Сашу Дворяк / Лазарчук — клиенты ЦАС.</t>
+        </is>
+      </c>
+      <c r="E85" s="730" t="n"/>
+      <c r="F85" s="730" t="n"/>
+      <c r="G85" s="730" t="n"/>
+      <c r="H85" s="727" t="n"/>
+      <c r="I85" s="727" t="n"/>
+    </row>
+    <row r="86" ht="18" customHeight="1">
+      <c r="A86" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Корп. сегмент / сбытовой офис</t>
+        </is>
+      </c>
+      <c r="B86" s="698" t="n"/>
+      <c r="C86" s="698" t="n"/>
+      <c r="D86" s="698" t="n"/>
+      <c r="E86" s="698" t="n"/>
+      <c r="F86" s="698" t="n"/>
+      <c r="G86" s="698" t="n"/>
+      <c r="H86" s="727" t="n"/>
+      <c r="I86" s="727" t="n"/>
+    </row>
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="724" t="inlineStr">
+        <is>
+          <t>Почему клиенты сбытового офиса не переходят в ЭПД / уходят на СБИС?</t>
+        </is>
+      </c>
+      <c r="B87" s="704" t="n"/>
+      <c r="C87" s="704" t="n"/>
+      <c r="D87" s="729" t="inlineStr">
+        <is>
+          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в 1-ю неделю сентября (Юлиана).</t>
+        </is>
+      </c>
+      <c r="E87" s="730" t="n"/>
+      <c r="F87" s="730" t="n"/>
+      <c r="G87" s="730" t="n"/>
+      <c r="H87" s="727" t="n"/>
+      <c r="I87" s="727" t="n"/>
+    </row>
+    <row r="88" ht="48" customHeight="1">
+      <c r="A88" s="724" t="inlineStr">
+        <is>
+          <t>Юля: предлагать всем клиентам бесплатно Доки (дублирующий сервис) на 3 мес.; KPI менеджерам на сентябрь.</t>
+        </is>
+      </c>
+      <c r="B88" s="704" t="n"/>
+      <c r="C88" s="704" t="n"/>
+      <c r="D88" s="724" t="inlineStr">
+        <is>
+          <t>Зафиксировано как предложение.</t>
+        </is>
+      </c>
+      <c r="E88" s="704" t="n"/>
+      <c r="F88" s="704" t="n"/>
+      <c r="G88" s="704" t="n"/>
+      <c r="H88" s="727" t="n"/>
+      <c r="I88" s="727" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="710" t="inlineStr">
+        <is>
+          <t>Подсветка выводов: строки с поручениями/задачами выделены мягким оранжевым. Поставленные задачи продублированы в блоке «2. Решения текущей встречи».</t>
+        </is>
+      </c>
+      <c r="B89" s="698" t="n"/>
+      <c r="C89" s="698" t="n"/>
+      <c r="D89" s="698" t="n"/>
+      <c r="E89" s="698" t="n"/>
+      <c r="F89" s="698" t="n"/>
+      <c r="G89" s="698" t="n"/>
+      <c r="H89" s="727" t="n"/>
+      <c r="I89" s="727" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="727" t="n"/>
+      <c r="B90" s="717" t="n"/>
+      <c r="C90" s="718" t="n"/>
+      <c r="D90" s="727" t="n"/>
+      <c r="E90" s="727" t="n"/>
+      <c r="F90" s="727" t="n"/>
+      <c r="G90" s="727" t="n"/>
+      <c r="H90" s="727" t="n"/>
+      <c r="I90" s="727" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="727" t="n"/>
+      <c r="B91" s="717" t="n"/>
+      <c r="C91" s="718" t="n"/>
+      <c r="D91" s="727" t="n"/>
+      <c r="E91" s="727" t="n"/>
+      <c r="F91" s="727" t="n"/>
+      <c r="G91" s="727" t="n"/>
+      <c r="H91" s="727" t="n"/>
+      <c r="I91" s="727" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="727" t="n"/>
+      <c r="B92" s="717" t="n"/>
+      <c r="C92" s="718" t="n"/>
+      <c r="D92" s="727" t="n"/>
+      <c r="E92" s="727" t="n"/>
+      <c r="F92" s="727" t="n"/>
+      <c r="G92" s="727" t="n"/>
+      <c r="H92" s="727" t="n"/>
+      <c r="I92" s="727" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="727" t="n"/>
+      <c r="B93" s="727" t="n"/>
+      <c r="C93" s="727" t="n"/>
+      <c r="D93" s="727" t="n"/>
+      <c r="E93" s="727" t="n"/>
+      <c r="F93" s="727" t="n"/>
+      <c r="G93" s="727" t="n"/>
+      <c r="H93" s="727" t="n"/>
+      <c r="I93" s="727" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="727" t="n"/>
+      <c r="B94" s="727" t="n"/>
+      <c r="C94" s="727" t="n"/>
+      <c r="D94" s="727" t="n"/>
+      <c r="E94" s="727" t="n"/>
+      <c r="F94" s="727" t="n"/>
+      <c r="G94" s="727" t="n"/>
+      <c r="H94" s="727" t="n"/>
+      <c r="I94" s="727" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="727" t="n"/>
+      <c r="B95" s="727" t="n"/>
+      <c r="C95" s="727" t="n"/>
+      <c r="D95" s="727" t="n"/>
+      <c r="E95" s="727" t="n"/>
+      <c r="F95" s="727" t="n"/>
+      <c r="G95" s="727" t="n"/>
+      <c r="H95" s="727" t="n"/>
+      <c r="I95" s="727" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="727" t="n"/>
+      <c r="B96" s="727" t="n"/>
+      <c r="C96" s="727" t="n"/>
+      <c r="D96" s="727" t="n"/>
+      <c r="E96" s="727" t="n"/>
+      <c r="F96" s="727" t="n"/>
+      <c r="G96" s="727" t="n"/>
+      <c r="H96" s="727" t="n"/>
+      <c r="I96" s="727" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="727" t="n"/>
+      <c r="B97" s="727" t="n"/>
+      <c r="C97" s="727" t="n"/>
+      <c r="D97" s="727" t="n"/>
+      <c r="E97" s="727" t="n"/>
+      <c r="F97" s="727" t="n"/>
+      <c r="G97" s="727" t="n"/>
+      <c r="H97" s="727" t="n"/>
+      <c r="I97" s="727" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="727" t="n"/>
+      <c r="B98" s="727" t="n"/>
+      <c r="C98" s="727" t="n"/>
+      <c r="D98" s="727" t="n"/>
+      <c r="E98" s="727" t="n"/>
+      <c r="F98" s="727" t="n"/>
+      <c r="G98" s="727" t="n"/>
+      <c r="H98" s="727" t="n"/>
+      <c r="I98" s="727" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="727" t="n"/>
+      <c r="B99" s="727" t="n"/>
+      <c r="C99" s="727" t="n"/>
+      <c r="D99" s="727" t="n"/>
+      <c r="E99" s="727" t="n"/>
+      <c r="F99" s="727" t="n"/>
+      <c r="G99" s="727" t="n"/>
+      <c r="H99" s="727" t="n"/>
+      <c r="I99" s="727" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="727" t="n"/>
+      <c r="B100" s="727" t="n"/>
+      <c r="C100" s="727" t="n"/>
+      <c r="D100" s="727" t="n"/>
+      <c r="E100" s="727" t="n"/>
+      <c r="F100" s="727" t="n"/>
+      <c r="G100" s="727" t="n"/>
+      <c r="H100" s="727" t="n"/>
+      <c r="I100" s="727" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="727" t="n"/>
+      <c r="B101" s="727" t="n"/>
+      <c r="C101" s="727" t="n"/>
+      <c r="D101" s="727" t="n"/>
+      <c r="E101" s="727" t="n"/>
+      <c r="F101" s="727" t="n"/>
+      <c r="G101" s="727" t="n"/>
+      <c r="H101" s="727" t="n"/>
+      <c r="I101" s="727" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="727" t="n"/>
+      <c r="B102" s="727" t="n"/>
+      <c r="C102" s="727" t="n"/>
+      <c r="D102" s="727" t="n"/>
+      <c r="E102" s="727" t="n"/>
+      <c r="F102" s="727" t="n"/>
+      <c r="G102" s="727" t="n"/>
+      <c r="H102" s="727" t="n"/>
+      <c r="I102" s="727" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="112">
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D74:G74"/>
+    <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D84:G84"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D77:G77"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="D70:G70"/>
+    <mergeCell ref="A89:G89"/>
+    <mergeCell ref="D72:G72"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="F57:G57"/>
+    <mergeCell ref="D62:G62"/>
+    <mergeCell ref="A66:C66"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D73:G73"/>
+    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="D88:G88"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F31:G31"/>
+    <mergeCell ref="A78:G78"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="A65:G65"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="F48:G48"/>
+    <mergeCell ref="D75:G75"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A84:C84"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="I13:K13"/>
+    <mergeCell ref="A6:G6"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A64:C64"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="A79:C79"/>
+    <mergeCell ref="A61:C61"/>
+    <mergeCell ref="A88:C88"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="F49:G49"/>
+    <mergeCell ref="A86:G86"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="F40:G40"/>
+    <mergeCell ref="D85:G85"/>
+    <mergeCell ref="F59:G59"/>
+    <mergeCell ref="F55:G55"/>
+    <mergeCell ref="F24:G24"/>
     <mergeCell ref="C10:D10"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A85:C85"/>
+    <mergeCell ref="D69:G69"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="F35:G35"/>
+    <mergeCell ref="D80:G80"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="F38:G38"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="F58:G58"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="F60:G60"/>
+    <mergeCell ref="A87:C87"/>
+    <mergeCell ref="A76:G76"/>
+    <mergeCell ref="F44:G44"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3830,3518 +5190,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:AE77"/>
-  <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
-    <col width="28" customWidth="1" min="11" max="11"/>
-    <col width="3" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="697" t="inlineStr">
-        <is>
-          <t>ВСТРЕЧА ЦП — ЦКС — ЦСВ — СМАК  ·  Протокол 27.08.2026</t>
-        </is>
-      </c>
-      <c r="H1" s="718" t="n"/>
-      <c r="I1" s="718" t="n"/>
-      <c r="J1" s="718" t="n"/>
-      <c r="K1" s="718" t="n"/>
-      <c r="L1" s="718" t="n"/>
-      <c r="M1" s="718" t="n"/>
-      <c r="N1" s="718" t="n"/>
-      <c r="O1" s="718" t="n"/>
-      <c r="P1" s="718" t="n"/>
-      <c r="Q1" s="718" t="n"/>
-      <c r="R1" s="718" t="n"/>
-      <c r="S1" s="718" t="n"/>
-      <c r="T1" s="718" t="n"/>
-      <c r="U1" s="718" t="n"/>
-      <c r="V1" s="718" t="n"/>
-      <c r="W1" s="718" t="n"/>
-      <c r="X1" s="718" t="n"/>
-      <c r="Y1" s="718" t="n"/>
-      <c r="Z1" s="718" t="n"/>
-      <c r="AA1" s="718" t="n"/>
-      <c r="AB1" s="718" t="n"/>
-      <c r="AC1" s="718" t="n"/>
-      <c r="AD1" s="718" t="n"/>
-      <c r="AE1" s="718" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="719" t="inlineStr">
-        <is>
-          <t>Проект ЭПД  ·  еженедельный статус</t>
-        </is>
-      </c>
-      <c r="H2" s="718" t="n"/>
-      <c r="I2" s="718" t="n"/>
-      <c r="J2" s="718" t="n"/>
-      <c r="K2" s="718" t="n"/>
-      <c r="L2" s="718" t="n"/>
-      <c r="M2" s="718" t="n"/>
-      <c r="N2" s="718" t="n"/>
-      <c r="O2" s="718" t="n"/>
-      <c r="P2" s="718" t="n"/>
-      <c r="Q2" s="718" t="n"/>
-      <c r="R2" s="718" t="n"/>
-      <c r="S2" s="718" t="n"/>
-      <c r="T2" s="718" t="n"/>
-      <c r="U2" s="718" t="n"/>
-      <c r="V2" s="718" t="n"/>
-      <c r="W2" s="718" t="n"/>
-      <c r="X2" s="718" t="n"/>
-      <c r="Y2" s="718" t="n"/>
-      <c r="Z2" s="718" t="n"/>
-      <c r="AA2" s="718" t="n"/>
-      <c r="AB2" s="718" t="n"/>
-      <c r="AC2" s="718" t="n"/>
-      <c r="AD2" s="718" t="n"/>
-      <c r="AE2" s="718" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="718" t="n"/>
-      <c r="B3" s="718" t="n"/>
-      <c r="C3" s="718" t="n"/>
-      <c r="D3" s="718" t="n"/>
-      <c r="E3" s="718" t="n"/>
-      <c r="F3" s="718" t="n"/>
-      <c r="G3" s="718" t="n"/>
-      <c r="H3" s="718" t="n"/>
-      <c r="I3" s="718" t="n"/>
-      <c r="J3" s="718" t="n"/>
-      <c r="K3" s="718" t="n"/>
-      <c r="L3" s="718" t="n"/>
-      <c r="M3" s="718" t="n"/>
-      <c r="N3" s="718" t="n"/>
-      <c r="O3" s="718" t="n"/>
-      <c r="P3" s="718" t="n"/>
-      <c r="Q3" s="718" t="n"/>
-      <c r="R3" s="718" t="n"/>
-      <c r="S3" s="718" t="n"/>
-      <c r="T3" s="718" t="n"/>
-      <c r="U3" s="718" t="n"/>
-      <c r="V3" s="718" t="n"/>
-      <c r="W3" s="718" t="n"/>
-      <c r="X3" s="718" t="n"/>
-      <c r="Y3" s="718" t="n"/>
-      <c r="Z3" s="718" t="n"/>
-      <c r="AA3" s="718" t="n"/>
-      <c r="AB3" s="718" t="n"/>
-      <c r="AC3" s="718" t="n"/>
-      <c r="AD3" s="718" t="n"/>
-      <c r="AE3" s="718" t="n"/>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="720" t="inlineStr">
-        <is>
-          <t>ПЛАН ПО ЭПД</t>
-        </is>
-      </c>
-      <c r="H4" s="718" t="n"/>
-      <c r="I4" s="721" t="inlineStr">
-        <is>
-          <t>Соотношение к прошлому периоду</t>
-        </is>
-      </c>
-      <c r="L4" s="718" t="n"/>
-      <c r="M4" s="718" t="n"/>
-      <c r="N4" s="718" t="n"/>
-      <c r="O4" s="718" t="n"/>
-      <c r="P4" s="718" t="n"/>
-      <c r="Q4" s="718" t="n"/>
-      <c r="R4" s="718" t="n"/>
-      <c r="S4" s="718" t="n"/>
-      <c r="T4" s="718" t="n"/>
-      <c r="U4" s="718" t="n"/>
-      <c r="V4" s="718" t="n"/>
-      <c r="W4" s="718" t="n"/>
-      <c r="X4" s="718" t="n"/>
-      <c r="Y4" s="718" t="n"/>
-      <c r="Z4" s="718" t="n"/>
-      <c r="AA4" s="718" t="n"/>
-      <c r="AB4" s="718" t="n"/>
-      <c r="AC4" s="718" t="n"/>
-      <c r="AD4" s="718" t="n"/>
-      <c r="AE4" s="718" t="n"/>
-    </row>
-    <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="701" t="inlineStr">
-        <is>
-          <t>План</t>
-        </is>
-      </c>
-      <c r="B5" s="702" t="n"/>
-      <c r="C5" s="701" t="inlineStr">
-        <is>
-          <t>Текущее значение</t>
-        </is>
-      </c>
-      <c r="D5" s="702" t="n"/>
-      <c r="E5" s="701" t="inlineStr">
-        <is>
-          <t>Итого до плана</t>
-        </is>
-      </c>
-      <c r="F5" s="702" t="n"/>
-      <c r="G5" s="701" t="inlineStr">
-        <is>
-          <t>% выполнения</t>
-        </is>
-      </c>
-      <c r="H5" s="718" t="n"/>
-      <c r="I5" s="703" t="inlineStr">
-        <is>
-          <t>Дата</t>
-        </is>
-      </c>
-      <c r="J5" s="703" t="inlineStr">
-        <is>
-          <t>Клиенты</t>
-        </is>
-      </c>
-      <c r="K5" s="703" t="inlineStr">
-        <is>
-          <t>Изменение</t>
-        </is>
-      </c>
-      <c r="L5" s="718" t="n"/>
-      <c r="M5" s="718" t="n"/>
-      <c r="N5" s="718" t="n"/>
-      <c r="O5" s="718" t="n"/>
-      <c r="P5" s="718" t="n"/>
-      <c r="Q5" s="718" t="n"/>
-      <c r="R5" s="718" t="n"/>
-      <c r="S5" s="718" t="n"/>
-      <c r="T5" s="718" t="n"/>
-      <c r="U5" s="718" t="n"/>
-      <c r="V5" s="718" t="n"/>
-      <c r="W5" s="718" t="n"/>
-      <c r="X5" s="718" t="n"/>
-      <c r="Y5" s="718" t="n"/>
-      <c r="Z5" s="718" t="n"/>
-      <c r="AA5" s="718" t="n"/>
-      <c r="AB5" s="718" t="n"/>
-      <c r="AC5" s="718" t="n"/>
-      <c r="AD5" s="718" t="n"/>
-      <c r="AE5" s="718" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="804" t="n">
-        <v>500</v>
-      </c>
-      <c r="B6" s="723" t="n"/>
-      <c r="C6" s="805">
-        <f>E11+E12+E13</f>
-        <v/>
-      </c>
-      <c r="D6" s="709" t="n"/>
-      <c r="E6" s="806">
-        <f>A6-C6</f>
-        <v/>
-      </c>
-      <c r="F6" s="726" t="n"/>
-      <c r="G6" s="807">
-        <f>IF(A6=0,"—",C6/A6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="718" t="n"/>
-      <c r="I6" s="728" t="inlineStr">
-        <is>
-          <t>27.08.2026</t>
-        </is>
-      </c>
-      <c r="J6" s="729">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="K6" s="730" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L6" s="718" t="n"/>
-      <c r="M6" s="718" t="n"/>
-      <c r="N6" s="718" t="n"/>
-      <c r="O6" s="718" t="n"/>
-      <c r="P6" s="718" t="n"/>
-      <c r="Q6" s="718" t="n"/>
-      <c r="R6" s="718" t="n"/>
-      <c r="S6" s="718" t="n"/>
-      <c r="T6" s="718" t="n"/>
-      <c r="U6" s="718" t="n"/>
-      <c r="V6" s="718" t="n"/>
-      <c r="W6" s="718" t="n"/>
-      <c r="X6" s="718" t="n"/>
-      <c r="Y6" s="718" t="n"/>
-      <c r="Z6" s="718" t="n"/>
-      <c r="AA6" s="718" t="n"/>
-      <c r="AB6" s="718" t="n"/>
-      <c r="AC6" s="718" t="n"/>
-      <c r="AD6" s="718" t="n"/>
-      <c r="AE6" s="718" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="731" t="inlineStr">
-        <is>
-          <t>«Текущее значение» = сумма ячеек «Факт» по отделам (ниже). Меняйте факты — обновятся итог, остаток и % выполнения.</t>
-        </is>
-      </c>
-      <c r="H7" s="718" t="n"/>
-      <c r="I7" s="732" t="inlineStr">
-        <is>
-          <t>03.09.2026</t>
-        </is>
-      </c>
-      <c r="J7" s="733" t="n">
-        <v>200</v>
-      </c>
-      <c r="K7" s="730">
-        <f>IF(OR(J6="",J6=0,J7=""),"—",IF(J7&gt;=J6,"увеличилось на "&amp;TEXT((J7-J6)/J6,"0.0%"),"уменьшилось на "&amp;TEXT((J6-J7)/J6,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L7" s="718" t="n"/>
-      <c r="M7" s="718" t="n"/>
-      <c r="N7" s="718" t="n"/>
-      <c r="O7" s="718" t="n"/>
-      <c r="P7" s="718" t="n"/>
-      <c r="Q7" s="718" t="n"/>
-      <c r="R7" s="718" t="n"/>
-      <c r="S7" s="718" t="n"/>
-      <c r="T7" s="718" t="n"/>
-      <c r="U7" s="718" t="n"/>
-      <c r="V7" s="718" t="n"/>
-      <c r="W7" s="718" t="n"/>
-      <c r="X7" s="718" t="n"/>
-      <c r="Y7" s="718" t="n"/>
-      <c r="Z7" s="718" t="n"/>
-      <c r="AA7" s="718" t="n"/>
-      <c r="AB7" s="718" t="n"/>
-      <c r="AC7" s="718" t="n"/>
-      <c r="AD7" s="718" t="n"/>
-      <c r="AE7" s="718" t="n"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="718" t="n"/>
-      <c r="B8" s="718" t="n"/>
-      <c r="C8" s="718" t="n"/>
-      <c r="D8" s="718" t="n"/>
-      <c r="E8" s="718" t="n"/>
-      <c r="F8" s="718" t="n"/>
-      <c r="G8" s="718" t="n"/>
-      <c r="H8" s="718" t="n"/>
-      <c r="I8" s="732" t="inlineStr">
-        <is>
-          <t>10.09.2026</t>
-        </is>
-      </c>
-      <c r="J8" s="733" t="n">
-        <v>250</v>
-      </c>
-      <c r="K8" s="730">
-        <f>IF(OR(J7="",J7=0,J8=""),"—",IF(J8&gt;=J7,"увеличилось на "&amp;TEXT((J8-J7)/J7,"0.0%"),"уменьшилось на "&amp;TEXT((J7-J8)/J7,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L8" s="718" t="n"/>
-      <c r="M8" s="718" t="n"/>
-      <c r="N8" s="718" t="n"/>
-      <c r="O8" s="718" t="n"/>
-      <c r="P8" s="718" t="n"/>
-      <c r="Q8" s="718" t="n"/>
-      <c r="R8" s="718" t="n"/>
-      <c r="S8" s="718" t="n"/>
-      <c r="T8" s="718" t="n"/>
-      <c r="U8" s="718" t="n"/>
-      <c r="V8" s="718" t="n"/>
-      <c r="W8" s="718" t="n"/>
-      <c r="X8" s="718" t="n"/>
-      <c r="Y8" s="718" t="n"/>
-      <c r="Z8" s="718" t="n"/>
-      <c r="AA8" s="718" t="n"/>
-      <c r="AB8" s="718" t="n"/>
-      <c r="AC8" s="718" t="n"/>
-      <c r="AD8" s="718" t="n"/>
-      <c r="AE8" s="718" t="n"/>
-    </row>
-    <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="734" t="inlineStr">
-        <is>
-          <t>План на МПП в месяц — по отделам</t>
-        </is>
-      </c>
-      <c r="H9" s="718" t="n"/>
-      <c r="I9" s="732" t="n"/>
-      <c r="J9" s="733" t="n"/>
-      <c r="K9" s="730">
-        <f>IF(OR(J8="",J8=0,J9=""),"—",IF(J9&gt;=J8,"увеличилось на "&amp;TEXT((J9-J8)/J8,"0.0%"),"уменьшилось на "&amp;TEXT((J8-J9)/J8,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L9" s="718" t="n"/>
-      <c r="M9" s="718" t="n"/>
-      <c r="N9" s="718" t="n"/>
-      <c r="O9" s="718" t="n"/>
-      <c r="P9" s="718" t="n"/>
-      <c r="Q9" s="718" t="n"/>
-      <c r="R9" s="718" t="n"/>
-      <c r="S9" s="718" t="n"/>
-      <c r="T9" s="718" t="n"/>
-      <c r="U9" s="718" t="n"/>
-      <c r="V9" s="718" t="n"/>
-      <c r="W9" s="718" t="n"/>
-      <c r="X9" s="718" t="n"/>
-      <c r="Y9" s="718" t="n"/>
-      <c r="Z9" s="718" t="n"/>
-      <c r="AA9" s="718" t="n"/>
-      <c r="AB9" s="718" t="n"/>
-      <c r="AC9" s="718" t="n"/>
-      <c r="AD9" s="718" t="n"/>
-      <c r="AE9" s="718" t="n"/>
-    </row>
-    <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="712" t="inlineStr">
-        <is>
-          <t>Отдел / группа</t>
-        </is>
-      </c>
-      <c r="B10" s="712" t="n"/>
-      <c r="C10" s="712" t="inlineStr">
-        <is>
-          <t>План на МПП в мес</t>
-        </is>
-      </c>
-      <c r="D10" s="712" t="n"/>
-      <c r="E10" s="712" t="inlineStr">
-        <is>
-          <t>Факт</t>
-        </is>
-      </c>
-      <c r="F10" s="712" t="inlineStr">
-        <is>
-          <t>% выполнения плана</t>
-        </is>
-      </c>
-      <c r="G10" s="712" t="n"/>
-      <c r="H10" s="718" t="n"/>
-      <c r="I10" s="732" t="n"/>
-      <c r="J10" s="733" t="n"/>
-      <c r="K10" s="730">
-        <f>IF(OR(J9="",J9=0,J10=""),"—",IF(J10&gt;=J9,"увеличилось на "&amp;TEXT((J10-J9)/J9,"0.0%"),"уменьшилось на "&amp;TEXT((J9-J10)/J9,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L10" s="718" t="n"/>
-      <c r="M10" s="718" t="n"/>
-      <c r="N10" s="718" t="n"/>
-      <c r="O10" s="718" t="n"/>
-      <c r="P10" s="718" t="n"/>
-      <c r="Q10" s="718" t="n"/>
-      <c r="R10" s="718" t="n"/>
-      <c r="S10" s="718" t="n"/>
-      <c r="T10" s="718" t="n"/>
-      <c r="U10" s="718" t="n"/>
-      <c r="V10" s="718" t="n"/>
-      <c r="W10" s="718" t="n"/>
-      <c r="X10" s="718" t="n"/>
-      <c r="Y10" s="718" t="n"/>
-      <c r="Z10" s="718" t="n"/>
-      <c r="AA10" s="718" t="n"/>
-      <c r="AB10" s="718" t="n"/>
-      <c r="AC10" s="718" t="n"/>
-      <c r="AD10" s="718" t="n"/>
-      <c r="AE10" s="718" t="n"/>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="735" t="inlineStr">
-        <is>
-          <t>Группа «Новые деньги»</t>
-        </is>
-      </c>
-      <c r="B11" s="709" t="n"/>
-      <c r="C11" s="736" t="n">
-        <v>75</v>
-      </c>
-      <c r="D11" s="737" t="n"/>
-      <c r="E11" s="738" t="n">
-        <v>90</v>
-      </c>
-      <c r="F11" s="808">
-        <f>IF(OR(C11="",C11=0),"—",E11/C11)</f>
-        <v/>
-      </c>
-      <c r="G11" s="708" t="n"/>
-      <c r="H11" s="718" t="n"/>
-      <c r="I11" s="732" t="n"/>
-      <c r="J11" s="733" t="n"/>
-      <c r="K11" s="730">
-        <f>IF(OR(J10="",J10=0,J11=""),"—",IF(J11&gt;=J10,"увеличилось на "&amp;TEXT((J11-J10)/J10,"0.0%"),"уменьшилось на "&amp;TEXT((J10-J11)/J10,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="718" t="n"/>
-      <c r="M11" s="718" t="n"/>
-      <c r="N11" s="718">
-        <f>E11</f>
-        <v/>
-      </c>
-      <c r="O11" s="718" t="n"/>
-      <c r="P11" s="718" t="n"/>
-      <c r="Q11" s="718" t="n"/>
-      <c r="R11" s="718" t="n"/>
-      <c r="S11" s="718" t="n"/>
-      <c r="T11" s="718" t="n"/>
-      <c r="U11" s="718" t="n"/>
-      <c r="V11" s="718" t="n"/>
-      <c r="W11" s="718" t="n"/>
-      <c r="X11" s="718" t="n"/>
-      <c r="Y11" s="718" t="n"/>
-      <c r="Z11" s="718" t="n"/>
-      <c r="AA11" s="718" t="n"/>
-      <c r="AB11" s="718" t="n"/>
-      <c r="AC11" s="718" t="n"/>
-      <c r="AD11" s="718" t="n"/>
-      <c r="AE11" s="718" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="735" t="inlineStr">
-        <is>
-          <t>Группа продуктового запуска</t>
-        </is>
-      </c>
-      <c r="B12" s="709" t="n"/>
-      <c r="C12" s="736" t="n">
-        <v>25</v>
-      </c>
-      <c r="D12" s="737" t="n"/>
-      <c r="E12" s="738" t="n">
-        <v>40</v>
-      </c>
-      <c r="F12" s="808">
-        <f>IF(OR(C12="",C12=0),"—",E12/C12)</f>
-        <v/>
-      </c>
-      <c r="G12" s="708" t="n"/>
-      <c r="H12" s="718" t="n"/>
-      <c r="I12" s="732" t="n"/>
-      <c r="J12" s="733" t="n"/>
-      <c r="K12" s="730">
-        <f>IF(OR(J11="",J11=0,J12=""),"—",IF(J12&gt;=J11,"увеличилось на "&amp;TEXT((J12-J11)/J11,"0.0%"),"уменьшилось на "&amp;TEXT((J11-J12)/J11,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L12" s="718" t="n"/>
-      <c r="M12" s="718" t="n"/>
-      <c r="N12" s="718">
-        <f>E12</f>
-        <v/>
-      </c>
-      <c r="O12" s="718" t="n"/>
-      <c r="P12" s="718" t="n"/>
-      <c r="Q12" s="718" t="n"/>
-      <c r="R12" s="718" t="n"/>
-      <c r="S12" s="718" t="n"/>
-      <c r="T12" s="718" t="n"/>
-      <c r="U12" s="718" t="n"/>
-      <c r="V12" s="718" t="n"/>
-      <c r="W12" s="718" t="n"/>
-      <c r="X12" s="718" t="n"/>
-      <c r="Y12" s="718" t="n"/>
-      <c r="Z12" s="718" t="n"/>
-      <c r="AA12" s="718" t="n"/>
-      <c r="AB12" s="718" t="n"/>
-      <c r="AC12" s="718" t="n"/>
-      <c r="AD12" s="718" t="n"/>
-      <c r="AE12" s="718" t="n"/>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="735" t="inlineStr">
-        <is>
-          <t>ЦКС</t>
-        </is>
-      </c>
-      <c r="B13" s="709" t="n"/>
-      <c r="C13" s="740" t="n"/>
-      <c r="D13" s="741" t="n"/>
-      <c r="E13" s="738" t="n">
-        <v>20</v>
-      </c>
-      <c r="F13" s="808">
-        <f>IF(OR(C13="",C13=0),"—",E13/C13)</f>
-        <v/>
-      </c>
-      <c r="G13" s="708" t="n"/>
-      <c r="H13" s="718" t="n"/>
-      <c r="I13" s="732" t="n"/>
-      <c r="J13" s="733" t="n"/>
-      <c r="K13" s="730">
-        <f>IF(OR(J12="",J12=0,J13=""),"—",IF(J13&gt;=J12,"увеличилось на "&amp;TEXT((J13-J12)/J12,"0.0%"),"уменьшилось на "&amp;TEXT((J12-J13)/J12,"0.0%")))</f>
-        <v/>
-      </c>
-      <c r="L13" s="718" t="n"/>
-      <c r="M13" s="718" t="n"/>
-      <c r="N13" s="718">
-        <f>E13</f>
-        <v/>
-      </c>
-      <c r="O13" s="718" t="n"/>
-      <c r="P13" s="718" t="n"/>
-      <c r="Q13" s="718" t="n"/>
-      <c r="R13" s="718" t="n"/>
-      <c r="S13" s="718" t="n"/>
-      <c r="T13" s="718" t="n"/>
-      <c r="U13" s="718" t="n"/>
-      <c r="V13" s="718" t="n"/>
-      <c r="W13" s="718" t="n"/>
-      <c r="X13" s="718" t="n"/>
-      <c r="Y13" s="718" t="n"/>
-      <c r="Z13" s="718" t="n"/>
-      <c r="AA13" s="718" t="n"/>
-      <c r="AB13" s="718" t="n"/>
-      <c r="AC13" s="718" t="n"/>
-      <c r="AD13" s="718" t="n"/>
-      <c r="AE13" s="718" t="n"/>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="718" t="n"/>
-      <c r="B14" s="718" t="n"/>
-      <c r="C14" s="718" t="n"/>
-      <c r="D14" s="718" t="n"/>
-      <c r="E14" s="718" t="n"/>
-      <c r="F14" s="718" t="n"/>
-      <c r="G14" s="718" t="n"/>
-      <c r="H14" s="718" t="n"/>
-      <c r="I14" s="742" t="inlineStr">
-        <is>
-          <t>Жёлтые ячейки «Клиенты» — вводите вручную на новые даты. Строка 27.08 подтягивает текущее значение из плана.</t>
-        </is>
-      </c>
-      <c r="L14" s="718" t="n"/>
-      <c r="M14" s="718" t="n"/>
-      <c r="N14" s="718" t="n"/>
-      <c r="O14" s="718" t="n"/>
-      <c r="P14" s="718" t="n"/>
-      <c r="Q14" s="718" t="n"/>
-      <c r="R14" s="718" t="n"/>
-      <c r="S14" s="718" t="n"/>
-      <c r="T14" s="718" t="n"/>
-      <c r="U14" s="718" t="n"/>
-      <c r="V14" s="718" t="n"/>
-      <c r="W14" s="718" t="n"/>
-      <c r="X14" s="718" t="n"/>
-      <c r="Y14" s="718" t="n"/>
-      <c r="Z14" s="718" t="n"/>
-      <c r="AA14" s="718" t="n"/>
-      <c r="AB14" s="718" t="n"/>
-      <c r="AC14" s="718" t="n"/>
-      <c r="AD14" s="718" t="n"/>
-      <c r="AE14" s="718" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="718" t="n"/>
-      <c r="B15" s="718" t="n"/>
-      <c r="C15" s="718" t="n"/>
-      <c r="D15" s="718" t="n"/>
-      <c r="E15" s="718" t="n"/>
-      <c r="F15" s="718" t="n"/>
-      <c r="G15" s="718" t="n"/>
-      <c r="H15" s="718" t="n"/>
-      <c r="I15" s="718" t="n"/>
-      <c r="J15" s="718" t="n"/>
-      <c r="K15" s="718" t="n"/>
-      <c r="L15" s="718" t="n"/>
-      <c r="M15" s="718" t="n"/>
-      <c r="N15" s="718" t="n"/>
-      <c r="O15" s="718" t="n"/>
-      <c r="P15" s="718" t="n"/>
-      <c r="Q15" s="718" t="n"/>
-      <c r="R15" s="718" t="n"/>
-      <c r="S15" s="718" t="n"/>
-      <c r="T15" s="718" t="n"/>
-      <c r="U15" s="718" t="n"/>
-      <c r="V15" s="718" t="n"/>
-      <c r="W15" s="718" t="n"/>
-      <c r="X15" s="718" t="n"/>
-      <c r="Y15" s="718" t="n"/>
-      <c r="Z15" s="718" t="n"/>
-      <c r="AA15" s="718" t="n"/>
-      <c r="AB15" s="718" t="n"/>
-      <c r="AC15" s="718" t="n"/>
-      <c r="AD15" s="718" t="n"/>
-      <c r="AE15" s="718" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="743" t="inlineStr">
-        <is>
-          <t>Показатели рекламной кампании</t>
-        </is>
-      </c>
-      <c r="H16" s="718" t="n"/>
-      <c r="I16" s="718" t="n"/>
-      <c r="J16" s="718" t="n"/>
-      <c r="K16" s="718" t="n"/>
-      <c r="L16" s="718" t="n"/>
-      <c r="M16" s="718" t="n"/>
-      <c r="N16" s="718" t="n"/>
-      <c r="O16" s="718" t="n"/>
-      <c r="P16" s="718" t="n"/>
-      <c r="Q16" s="718" t="n"/>
-      <c r="R16" s="718" t="n"/>
-      <c r="S16" s="718" t="n"/>
-      <c r="T16" s="718" t="n"/>
-      <c r="U16" s="718" t="n"/>
-      <c r="V16" s="718" t="n"/>
-      <c r="W16" s="718" t="n"/>
-      <c r="X16" s="718" t="n"/>
-      <c r="Y16" s="718" t="n"/>
-      <c r="Z16" s="718" t="n"/>
-      <c r="AA16" s="718" t="n"/>
-      <c r="AB16" s="718" t="n"/>
-      <c r="AC16" s="718" t="n"/>
-      <c r="AD16" s="718" t="n"/>
-      <c r="AE16" s="718" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="744" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B17" s="744" t="inlineStr">
-        <is>
-          <t>Название РК</t>
-        </is>
-      </c>
-      <c r="C17" s="744" t="inlineStr">
-        <is>
-          <t>Лидер</t>
-        </is>
-      </c>
-      <c r="D17" s="744" t="inlineStr">
-        <is>
-          <t>Кол-во ЛИДов</t>
-        </is>
-      </c>
-      <c r="E17" s="744" t="inlineStr">
-        <is>
-          <t>Стоимость ЛИДа</t>
-        </is>
-      </c>
-      <c r="F17" s="744" t="inlineStr">
-        <is>
-          <t>Сделок</t>
-        </is>
-      </c>
-      <c r="G17" s="744" t="inlineStr">
-        <is>
-          <t>Оплат</t>
-        </is>
-      </c>
-      <c r="H17" s="718" t="n"/>
-      <c r="I17" s="718" t="n"/>
-      <c r="J17" s="718" t="n"/>
-      <c r="K17" s="718" t="n"/>
-      <c r="L17" s="718" t="n"/>
-      <c r="M17" s="718" t="n"/>
-      <c r="N17" s="718" t="n"/>
-      <c r="O17" s="718" t="n"/>
-      <c r="P17" s="718" t="n"/>
-      <c r="Q17" s="718" t="n"/>
-      <c r="R17" s="718" t="n"/>
-      <c r="S17" s="718" t="n"/>
-      <c r="T17" s="718" t="n"/>
-      <c r="U17" s="718" t="n"/>
-      <c r="V17" s="718" t="n"/>
-      <c r="W17" s="718" t="n"/>
-      <c r="X17" s="718" t="n"/>
-      <c r="Y17" s="718" t="n"/>
-      <c r="Z17" s="718" t="n"/>
-      <c r="AA17" s="718" t="n"/>
-      <c r="AB17" s="718" t="n"/>
-      <c r="AC17" s="718" t="n"/>
-      <c r="AD17" s="718" t="n"/>
-      <c r="AE17" s="718" t="n"/>
-    </row>
-    <row r="18" ht="48" customHeight="1">
-      <c r="A18" s="745" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="745" t="inlineStr">
-        <is>
-          <t>ЭПД</t>
-        </is>
-      </c>
-      <c r="C18" s="745" t="inlineStr">
-        <is>
-          <t>Савинская</t>
-        </is>
-      </c>
-      <c r="D18" s="745" t="inlineStr">
-        <is>
-          <t>ЭПД Квиз — 9 шт; CRM-форма «Внедрение и поддержка 1С:ЭПД» — 17 шт; Заявка с сайта — 6 шт</t>
-        </is>
-      </c>
-      <c r="E18" s="746" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F18" s="745" t="inlineStr">
-        <is>
-          <t>Квиз — 3 сделки (2 контроль оплаты); CRM-форма — 5 сделок (1 контроль оплаты на 18 100); Заявка с сайта — 5 сделок (2 оплаты, 3 контроль)</t>
-        </is>
-      </c>
-      <c r="G18" s="745" t="inlineStr">
-        <is>
-          <t>2 шт / 10 000 ₽</t>
-        </is>
-      </c>
-      <c r="H18" s="718" t="n"/>
-      <c r="I18" s="718" t="n"/>
-      <c r="J18" s="718" t="n"/>
-      <c r="K18" s="718" t="n"/>
-      <c r="L18" s="718" t="n"/>
-      <c r="M18" s="718" t="n"/>
-      <c r="N18" s="718" t="n"/>
-      <c r="O18" s="718" t="n"/>
-      <c r="P18" s="718" t="n"/>
-      <c r="Q18" s="718" t="n"/>
-      <c r="R18" s="718" t="n"/>
-      <c r="S18" s="718" t="n"/>
-      <c r="T18" s="718" t="n"/>
-      <c r="U18" s="718" t="n"/>
-      <c r="V18" s="718" t="n"/>
-      <c r="W18" s="718" t="n"/>
-      <c r="X18" s="718" t="n"/>
-      <c r="Y18" s="718" t="n"/>
-      <c r="Z18" s="718" t="n"/>
-      <c r="AA18" s="718" t="n"/>
-      <c r="AB18" s="718" t="n"/>
-      <c r="AC18" s="718" t="n"/>
-      <c r="AD18" s="718" t="n"/>
-      <c r="AE18" s="718" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="718" t="n"/>
-      <c r="B19" s="718" t="n"/>
-      <c r="C19" s="718" t="n"/>
-      <c r="D19" s="718" t="n"/>
-      <c r="E19" s="718" t="n"/>
-      <c r="F19" s="718" t="n"/>
-      <c r="G19" s="718" t="n"/>
-      <c r="H19" s="718" t="n"/>
-      <c r="I19" s="718" t="n"/>
-      <c r="J19" s="718" t="n"/>
-      <c r="K19" s="718" t="n"/>
-      <c r="L19" s="718" t="n"/>
-      <c r="M19" s="718" t="n"/>
-      <c r="N19" s="718" t="n"/>
-      <c r="O19" s="718" t="n"/>
-      <c r="P19" s="718" t="n"/>
-      <c r="Q19" s="718" t="n"/>
-      <c r="R19" s="718" t="n"/>
-      <c r="S19" s="718" t="n"/>
-      <c r="T19" s="718" t="n"/>
-      <c r="U19" s="718" t="n"/>
-      <c r="V19" s="718" t="n"/>
-      <c r="W19" s="718" t="n"/>
-      <c r="X19" s="718" t="n"/>
-      <c r="Y19" s="718" t="n"/>
-      <c r="Z19" s="718" t="n"/>
-      <c r="AA19" s="718" t="n"/>
-      <c r="AB19" s="718" t="n"/>
-      <c r="AC19" s="718" t="n"/>
-      <c r="AD19" s="718" t="n"/>
-      <c r="AE19" s="718" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="743" t="inlineStr">
-        <is>
-          <t>1. Мониторинг предыдущих решений</t>
-        </is>
-      </c>
-      <c r="H20" s="718" t="n"/>
-      <c r="I20" s="718" t="n"/>
-      <c r="J20" s="718" t="n"/>
-      <c r="K20" s="718" t="n"/>
-      <c r="L20" s="718" t="n"/>
-      <c r="M20" s="718" t="n"/>
-      <c r="N20" s="718" t="n"/>
-      <c r="O20" s="718" t="n"/>
-      <c r="P20" s="718" t="n"/>
-      <c r="Q20" s="718" t="n"/>
-      <c r="R20" s="718" t="n"/>
-      <c r="S20" s="718" t="n"/>
-      <c r="T20" s="718" t="n"/>
-      <c r="U20" s="718" t="n"/>
-      <c r="V20" s="718" t="n"/>
-      <c r="W20" s="718" t="n"/>
-      <c r="X20" s="718" t="n"/>
-      <c r="Y20" s="718" t="n"/>
-      <c r="Z20" s="718" t="n"/>
-      <c r="AA20" s="718" t="n"/>
-      <c r="AB20" s="718" t="n"/>
-      <c r="AC20" s="718" t="n"/>
-      <c r="AD20" s="718" t="n"/>
-      <c r="AE20" s="718" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="744" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B21" s="744" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-      <c r="C21" s="744" t="inlineStr">
-        <is>
-          <t>Лидер</t>
-        </is>
-      </c>
-      <c r="D21" s="744" t="inlineStr">
-        <is>
-          <t>Срок</t>
-        </is>
-      </c>
-      <c r="E21" s="744" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="F21" s="744" t="inlineStr">
-        <is>
-          <t>Комментарии / выводы</t>
-        </is>
-      </c>
-      <c r="G21" s="702" t="n"/>
-      <c r="H21" s="718" t="n"/>
-      <c r="I21" s="718" t="n"/>
-      <c r="J21" s="718" t="n"/>
-      <c r="K21" s="718" t="n"/>
-      <c r="L21" s="718" t="n"/>
-      <c r="M21" s="718" t="n"/>
-      <c r="N21" s="718" t="n"/>
-      <c r="O21" s="718" t="n"/>
-      <c r="P21" s="718" t="n"/>
-      <c r="Q21" s="718" t="n"/>
-      <c r="R21" s="718" t="n"/>
-      <c r="S21" s="718" t="n"/>
-      <c r="T21" s="718" t="n"/>
-      <c r="U21" s="718" t="n"/>
-      <c r="V21" s="718" t="n"/>
-      <c r="W21" s="718" t="n"/>
-      <c r="X21" s="718" t="n"/>
-      <c r="Y21" s="718" t="n"/>
-      <c r="Z21" s="718" t="n"/>
-      <c r="AA21" s="718" t="n"/>
-      <c r="AB21" s="718" t="n"/>
-      <c r="AC21" s="718" t="n"/>
-      <c r="AD21" s="718" t="n"/>
-      <c r="AE21" s="718" t="n"/>
-    </row>
-    <row r="22" ht="32" customHeight="1">
-      <c r="A22" s="732" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="747" t="inlineStr">
-        <is>
-          <t>Включить поле «время взятия в работу» заявки с РК</t>
-        </is>
-      </c>
-      <c r="C22" s="747" t="inlineStr">
-        <is>
-          <t>Савинская</t>
-        </is>
-      </c>
-      <c r="D22" s="747" t="inlineStr">
-        <is>
-          <t>до 27.08</t>
-        </is>
-      </c>
-      <c r="E22" s="748" t="inlineStr">
-        <is>
-          <t>выполнено</t>
-        </is>
-      </c>
-      <c r="F22" s="747" t="inlineStr"/>
-      <c r="G22" s="747" t="n"/>
-      <c r="H22" s="718" t="n"/>
-      <c r="I22" s="718" t="n"/>
-      <c r="J22" s="718" t="n"/>
-      <c r="K22" s="718" t="n"/>
-      <c r="L22" s="718" t="n"/>
-      <c r="M22" s="718" t="n"/>
-      <c r="N22" s="718" t="n"/>
-      <c r="O22" s="718" t="n"/>
-      <c r="P22" s="718" t="n"/>
-      <c r="Q22" s="718" t="n"/>
-      <c r="R22" s="718" t="n"/>
-      <c r="S22" s="718" t="n"/>
-      <c r="T22" s="718" t="n"/>
-      <c r="U22" s="718" t="n"/>
-      <c r="V22" s="718" t="n"/>
-      <c r="W22" s="718" t="n"/>
-      <c r="X22" s="718" t="n"/>
-      <c r="Y22" s="718" t="n"/>
-      <c r="Z22" s="718" t="n"/>
-      <c r="AA22" s="718" t="n"/>
-      <c r="AB22" s="718" t="n"/>
-      <c r="AC22" s="718" t="n"/>
-      <c r="AD22" s="718" t="n"/>
-      <c r="AE22" s="718" t="n"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
-      <c r="A23" s="732" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="747" t="inlineStr">
-        <is>
-          <t>Обсудить разделение стоимости РК между ЦП и ЦКС на очной встрече 27.08</t>
-        </is>
-      </c>
-      <c r="C23" s="747" t="inlineStr">
-        <is>
-          <t>Антонов В., Дербенева К. (все)</t>
-        </is>
-      </c>
-      <c r="D23" s="747" t="inlineStr">
-        <is>
-          <t>до 27.08</t>
-        </is>
-      </c>
-      <c r="E23" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F23" s="747" t="inlineStr"/>
-      <c r="G23" s="747" t="n"/>
-      <c r="H23" s="718" t="n"/>
-      <c r="I23" s="718" t="n"/>
-      <c r="J23" s="718" t="n"/>
-      <c r="K23" s="718" t="n"/>
-      <c r="L23" s="718" t="n"/>
-      <c r="M23" s="718" t="n"/>
-      <c r="N23" s="718" t="n"/>
-      <c r="O23" s="718" t="n"/>
-      <c r="P23" s="718" t="n"/>
-      <c r="Q23" s="718" t="n"/>
-      <c r="R23" s="718" t="n"/>
-      <c r="S23" s="718" t="n"/>
-      <c r="T23" s="718" t="n"/>
-      <c r="U23" s="718" t="n"/>
-      <c r="V23" s="718" t="n"/>
-      <c r="W23" s="718" t="n"/>
-      <c r="X23" s="718" t="n"/>
-      <c r="Y23" s="718" t="n"/>
-      <c r="Z23" s="718" t="n"/>
-      <c r="AA23" s="718" t="n"/>
-      <c r="AB23" s="718" t="n"/>
-      <c r="AC23" s="718" t="n"/>
-      <c r="AD23" s="718" t="n"/>
-      <c r="AE23" s="718" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1">
-      <c r="A24" s="732" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="747" t="inlineStr">
-        <is>
-          <t>Текущая РК действует до середины сентября. Продлеваем? Согласование бюджета</t>
-        </is>
-      </c>
-      <c r="C24" s="747" t="inlineStr">
-        <is>
-          <t>Все участники</t>
-        </is>
-      </c>
-      <c r="D24" s="747" t="inlineStr">
-        <is>
-          <t>до 27.08</t>
-        </is>
-      </c>
-      <c r="E24" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F24" s="747" t="inlineStr"/>
-      <c r="G24" s="747" t="n"/>
-      <c r="H24" s="718" t="n"/>
-      <c r="I24" s="718" t="n"/>
-      <c r="J24" s="718" t="n"/>
-      <c r="K24" s="718" t="n"/>
-      <c r="L24" s="718" t="n"/>
-      <c r="M24" s="718" t="n"/>
-      <c r="N24" s="718" t="n"/>
-      <c r="O24" s="718" t="n"/>
-      <c r="P24" s="718" t="n"/>
-      <c r="Q24" s="718" t="n"/>
-      <c r="R24" s="718" t="n"/>
-      <c r="S24" s="718" t="n"/>
-      <c r="T24" s="718" t="n"/>
-      <c r="U24" s="718" t="n"/>
-      <c r="V24" s="718" t="n"/>
-      <c r="W24" s="718" t="n"/>
-      <c r="X24" s="718" t="n"/>
-      <c r="Y24" s="718" t="n"/>
-      <c r="Z24" s="718" t="n"/>
-      <c r="AA24" s="718" t="n"/>
-      <c r="AB24" s="718" t="n"/>
-      <c r="AC24" s="718" t="n"/>
-      <c r="AD24" s="718" t="n"/>
-      <c r="AE24" s="718" t="n"/>
-    </row>
-    <row r="25" ht="32" customHeight="1">
-      <c r="A25" s="732" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="747" t="inlineStr">
-        <is>
-          <t>Собрать ОС от МПП по ЭПД — проблемы, возражения, потребности</t>
-        </is>
-      </c>
-      <c r="C25" s="747" t="inlineStr">
-        <is>
-          <t>Савинская / Блохина / Степанова</t>
-        </is>
-      </c>
-      <c r="D25" s="747" t="inlineStr">
-        <is>
-          <t>до 24.08</t>
-        </is>
-      </c>
-      <c r="E25" s="748" t="inlineStr">
-        <is>
-          <t>выполнено</t>
-        </is>
-      </c>
-      <c r="F25" s="747" t="inlineStr">
-        <is>
-          <t>Документ в беседе «ЭПД стратегия»</t>
-        </is>
-      </c>
-      <c r="G25" s="747" t="n"/>
-      <c r="H25" s="718" t="n"/>
-      <c r="I25" s="718" t="n"/>
-      <c r="J25" s="718" t="n"/>
-      <c r="K25" s="718" t="n"/>
-      <c r="L25" s="718" t="n"/>
-      <c r="M25" s="718" t="n"/>
-      <c r="N25" s="718" t="n"/>
-      <c r="O25" s="718" t="n"/>
-      <c r="P25" s="718" t="n"/>
-      <c r="Q25" s="718" t="n"/>
-      <c r="R25" s="718" t="n"/>
-      <c r="S25" s="718" t="n"/>
-      <c r="T25" s="718" t="n"/>
-      <c r="U25" s="718" t="n"/>
-      <c r="V25" s="718" t="n"/>
-      <c r="W25" s="718" t="n"/>
-      <c r="X25" s="718" t="n"/>
-      <c r="Y25" s="718" t="n"/>
-      <c r="Z25" s="718" t="n"/>
-      <c r="AA25" s="718" t="n"/>
-      <c r="AB25" s="718" t="n"/>
-      <c r="AC25" s="718" t="n"/>
-      <c r="AD25" s="718" t="n"/>
-      <c r="AE25" s="718" t="n"/>
-    </row>
-    <row r="26" ht="32" customHeight="1">
-      <c r="A26" s="732" t="n">
-        <v>5</v>
-      </c>
-      <c r="B26" s="747" t="inlineStr">
-        <is>
-          <t>Собрать портрет клиента, который купил ЭПД</t>
-        </is>
-      </c>
-      <c r="C26" s="747" t="inlineStr">
-        <is>
-          <t>Корнева / Степанова</t>
-        </is>
-      </c>
-      <c r="D26" s="747" t="inlineStr">
-        <is>
-          <t>до 27.08</t>
-        </is>
-      </c>
-      <c r="E26" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F26" s="747" t="inlineStr">
-        <is>
-          <t>Параметры портрета — после встречи</t>
-        </is>
-      </c>
-      <c r="G26" s="747" t="n"/>
-      <c r="H26" s="718" t="n"/>
-      <c r="I26" s="718" t="n"/>
-      <c r="J26" s="718" t="n"/>
-      <c r="K26" s="718" t="n"/>
-      <c r="L26" s="718" t="n"/>
-      <c r="M26" s="718" t="n"/>
-      <c r="N26" s="718" t="n"/>
-      <c r="O26" s="718" t="n"/>
-      <c r="P26" s="718" t="n"/>
-      <c r="Q26" s="718" t="n"/>
-      <c r="R26" s="718" t="n"/>
-      <c r="S26" s="718" t="n"/>
-      <c r="T26" s="718" t="n"/>
-      <c r="U26" s="718" t="n"/>
-      <c r="V26" s="718" t="n"/>
-      <c r="W26" s="718" t="n"/>
-      <c r="X26" s="718" t="n"/>
-      <c r="Y26" s="718" t="n"/>
-      <c r="Z26" s="718" t="n"/>
-      <c r="AA26" s="718" t="n"/>
-      <c r="AB26" s="718" t="n"/>
-      <c r="AC26" s="718" t="n"/>
-      <c r="AD26" s="718" t="n"/>
-      <c r="AE26" s="718" t="n"/>
-    </row>
-    <row r="27" ht="32" customHeight="1">
-      <c r="A27" s="732" t="n">
-        <v>6</v>
-      </c>
-      <c r="B27" s="747" t="inlineStr">
-        <is>
-          <t>Добавить Корневу и Степанову во встречу с Калугой</t>
-        </is>
-      </c>
-      <c r="C27" s="747" t="inlineStr">
-        <is>
-          <t>Блохина</t>
-        </is>
-      </c>
-      <c r="D27" s="747" t="inlineStr">
-        <is>
-          <t>до 24.08</t>
-        </is>
-      </c>
-      <c r="E27" s="748" t="inlineStr">
-        <is>
-          <t>выполнено</t>
-        </is>
-      </c>
-      <c r="F27" s="747" t="inlineStr"/>
-      <c r="G27" s="747" t="n"/>
-      <c r="H27" s="718" t="n"/>
-      <c r="I27" s="718" t="n"/>
-      <c r="J27" s="718" t="n"/>
-      <c r="K27" s="718" t="n"/>
-      <c r="L27" s="718" t="n"/>
-      <c r="M27" s="718" t="n"/>
-      <c r="N27" s="718" t="n"/>
-      <c r="O27" s="718" t="n"/>
-      <c r="P27" s="718" t="n"/>
-      <c r="Q27" s="718" t="n"/>
-      <c r="R27" s="718" t="n"/>
-      <c r="S27" s="718" t="n"/>
-      <c r="T27" s="718" t="n"/>
-      <c r="U27" s="718" t="n"/>
-      <c r="V27" s="718" t="n"/>
-      <c r="W27" s="718" t="n"/>
-      <c r="X27" s="718" t="n"/>
-      <c r="Y27" s="718" t="n"/>
-      <c r="Z27" s="718" t="n"/>
-      <c r="AA27" s="718" t="n"/>
-      <c r="AB27" s="718" t="n"/>
-      <c r="AC27" s="718" t="n"/>
-      <c r="AD27" s="718" t="n"/>
-      <c r="AE27" s="718" t="n"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
-      <c r="A28" s="732" t="n">
-        <v>7</v>
-      </c>
-      <c r="B28" s="747" t="inlineStr">
-        <is>
-          <t>Построить финмодель направления ЭПД (доходы, затраты, конверсии, сценарии)</t>
-        </is>
-      </c>
-      <c r="C28" s="747" t="inlineStr">
-        <is>
-          <t>Все участники</t>
-        </is>
-      </c>
-      <c r="D28" s="747" t="inlineStr">
-        <is>
-          <t>после стратег-сессии</t>
-        </is>
-      </c>
-      <c r="E28" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F28" s="747" t="inlineStr"/>
-      <c r="G28" s="747" t="n"/>
-      <c r="H28" s="718" t="n"/>
-      <c r="I28" s="718" t="n"/>
-      <c r="J28" s="718" t="n"/>
-      <c r="K28" s="718" t="n"/>
-      <c r="L28" s="718" t="n"/>
-      <c r="M28" s="718" t="n"/>
-      <c r="N28" s="718" t="n"/>
-      <c r="O28" s="718" t="n"/>
-      <c r="P28" s="718" t="n"/>
-      <c r="Q28" s="718" t="n"/>
-      <c r="R28" s="718" t="n"/>
-      <c r="S28" s="718" t="n"/>
-      <c r="T28" s="718" t="n"/>
-      <c r="U28" s="718" t="n"/>
-      <c r="V28" s="718" t="n"/>
-      <c r="W28" s="718" t="n"/>
-      <c r="X28" s="718" t="n"/>
-      <c r="Y28" s="718" t="n"/>
-      <c r="Z28" s="718" t="n"/>
-      <c r="AA28" s="718" t="n"/>
-      <c r="AB28" s="718" t="n"/>
-      <c r="AC28" s="718" t="n"/>
-      <c r="AD28" s="718" t="n"/>
-      <c r="AE28" s="718" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="718" t="n"/>
-      <c r="B29" s="718" t="n"/>
-      <c r="C29" s="718" t="n"/>
-      <c r="D29" s="718" t="n"/>
-      <c r="E29" s="718" t="n"/>
-      <c r="F29" s="718" t="n"/>
-      <c r="G29" s="718" t="n"/>
-      <c r="H29" s="718" t="n"/>
-      <c r="I29" s="718" t="n"/>
-      <c r="J29" s="718" t="n"/>
-      <c r="K29" s="718" t="n"/>
-      <c r="L29" s="718" t="n"/>
-      <c r="M29" s="718" t="n"/>
-      <c r="N29" s="718" t="n"/>
-      <c r="O29" s="718" t="n"/>
-      <c r="P29" s="718" t="n"/>
-      <c r="Q29" s="718" t="n"/>
-      <c r="R29" s="718" t="n"/>
-      <c r="S29" s="718" t="n"/>
-      <c r="T29" s="718" t="n"/>
-      <c r="U29" s="718" t="n"/>
-      <c r="V29" s="718" t="n"/>
-      <c r="W29" s="718" t="n"/>
-      <c r="X29" s="718" t="n"/>
-      <c r="Y29" s="718" t="n"/>
-      <c r="Z29" s="718" t="n"/>
-      <c r="AA29" s="718" t="n"/>
-      <c r="AB29" s="718" t="n"/>
-      <c r="AC29" s="718" t="n"/>
-      <c r="AD29" s="718" t="n"/>
-      <c r="AE29" s="718" t="n"/>
-    </row>
-    <row r="30" ht="16.95" customHeight="1">
-      <c r="A30" s="750" t="inlineStr">
-        <is>
-          <t>2. Решения текущей встречи  ·  поставленные задачи</t>
-        </is>
-      </c>
-      <c r="H30" s="718" t="n"/>
-      <c r="I30" s="718" t="n"/>
-      <c r="J30" s="718" t="n"/>
-      <c r="K30" s="718" t="n"/>
-      <c r="L30" s="718" t="n"/>
-      <c r="M30" s="718" t="n"/>
-      <c r="N30" s="718" t="n"/>
-      <c r="O30" s="718" t="n"/>
-      <c r="P30" s="718" t="n"/>
-      <c r="Q30" s="718" t="n"/>
-      <c r="R30" s="718" t="n"/>
-      <c r="S30" s="718" t="n"/>
-      <c r="T30" s="718" t="n"/>
-      <c r="U30" s="718" t="n"/>
-      <c r="V30" s="718" t="n"/>
-      <c r="W30" s="718" t="n"/>
-      <c r="X30" s="718" t="n"/>
-      <c r="Y30" s="718" t="n"/>
-      <c r="Z30" s="718" t="n"/>
-      <c r="AA30" s="718" t="n"/>
-      <c r="AB30" s="718" t="n"/>
-      <c r="AC30" s="718" t="n"/>
-      <c r="AD30" s="718" t="n"/>
-      <c r="AE30" s="718" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="703" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B31" s="703" t="inlineStr">
-        <is>
-          <t>Задача</t>
-        </is>
-      </c>
-      <c r="C31" s="703" t="inlineStr">
-        <is>
-          <t>Лидер</t>
-        </is>
-      </c>
-      <c r="D31" s="703" t="inlineStr">
-        <is>
-          <t>Срок</t>
-        </is>
-      </c>
-      <c r="E31" s="703" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="F31" s="703" t="inlineStr">
-        <is>
-          <t>Комментарии / выводы</t>
-        </is>
-      </c>
-      <c r="G31" s="702" t="n"/>
-      <c r="H31" s="718" t="n"/>
-      <c r="I31" s="718" t="n"/>
-      <c r="J31" s="718" t="n"/>
-      <c r="K31" s="718" t="n"/>
-      <c r="L31" s="718" t="n"/>
-      <c r="M31" s="718" t="n"/>
-      <c r="N31" s="718" t="n"/>
-      <c r="O31" s="718" t="n"/>
-      <c r="P31" s="718" t="n"/>
-      <c r="Q31" s="718" t="n"/>
-      <c r="R31" s="718" t="n"/>
-      <c r="S31" s="718" t="n"/>
-      <c r="T31" s="718" t="n"/>
-      <c r="U31" s="718" t="n"/>
-      <c r="V31" s="718" t="n"/>
-      <c r="W31" s="718" t="n"/>
-      <c r="X31" s="718" t="n"/>
-      <c r="Y31" s="718" t="n"/>
-      <c r="Z31" s="718" t="n"/>
-      <c r="AA31" s="718" t="n"/>
-      <c r="AB31" s="718" t="n"/>
-      <c r="AC31" s="718" t="n"/>
-      <c r="AD31" s="718" t="n"/>
-      <c r="AE31" s="718" t="n"/>
-    </row>
-    <row r="32" ht="42" customHeight="1">
-      <c r="A32" s="751" t="n">
-        <v>1</v>
-      </c>
-      <c r="B32" s="752" t="inlineStr">
-        <is>
-          <t>Разобраться с показателями охвата сервисом 1С-ЭПД из таблицы А. Дворяк (9 000 ед.): что считается охватом — подключение или предоплаченные пакеты?</t>
-        </is>
-      </c>
-      <c r="C32" s="752" t="inlineStr">
-        <is>
-          <t>Корнева, Степанова</t>
-        </is>
-      </c>
-      <c r="D32" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E32" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F32" s="752" t="inlineStr">
-        <is>
-          <t>Цифры расходятся с Калугой; проблемы с закреплением</t>
-        </is>
-      </c>
-      <c r="G32" s="752" t="n"/>
-      <c r="H32" s="718" t="n"/>
-      <c r="I32" s="718" t="n"/>
-      <c r="J32" s="718" t="n"/>
-      <c r="K32" s="718" t="n"/>
-      <c r="L32" s="718" t="n"/>
-      <c r="M32" s="718" t="n"/>
-      <c r="N32" s="718" t="n"/>
-      <c r="O32" s="718" t="n"/>
-      <c r="P32" s="718" t="n"/>
-      <c r="Q32" s="718" t="n"/>
-      <c r="R32" s="718" t="n"/>
-      <c r="S32" s="718" t="n"/>
-      <c r="T32" s="718" t="n"/>
-      <c r="U32" s="718" t="n"/>
-      <c r="V32" s="718" t="n"/>
-      <c r="W32" s="718" t="n"/>
-      <c r="X32" s="718" t="n"/>
-      <c r="Y32" s="718" t="n"/>
-      <c r="Z32" s="718" t="n"/>
-      <c r="AA32" s="718" t="n"/>
-      <c r="AB32" s="718" t="n"/>
-      <c r="AC32" s="718" t="n"/>
-      <c r="AD32" s="718" t="n"/>
-      <c r="AE32" s="718" t="n"/>
-    </row>
-    <row r="33" ht="42" customHeight="1">
-      <c r="A33" s="751" t="n">
-        <v>2</v>
-      </c>
-      <c r="B33" s="752" t="inlineStr">
-        <is>
-          <t>Уточнить у Суворовой статус Элиттрейд; предложить акцию 3 мес. Доки для захода к контрагентам</t>
-        </is>
-      </c>
-      <c r="C33" s="752" t="inlineStr">
-        <is>
-          <t>Блохина (Лиза)</t>
-        </is>
-      </c>
-      <c r="D33" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E33" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F33" s="752" t="inlineStr">
-        <is>
-          <t>Крупные производители «диктуют» правила → возможность почкования базы</t>
-        </is>
-      </c>
-      <c r="G33" s="752" t="n"/>
-      <c r="H33" s="718" t="n"/>
-      <c r="I33" s="718" t="n"/>
-      <c r="J33" s="718" t="n"/>
-      <c r="K33" s="718" t="n"/>
-      <c r="L33" s="718" t="n"/>
-      <c r="M33" s="718" t="n"/>
-      <c r="N33" s="718" t="n"/>
-      <c r="O33" s="718" t="n"/>
-      <c r="P33" s="718" t="n"/>
-      <c r="Q33" s="718" t="n"/>
-      <c r="R33" s="718" t="n"/>
-      <c r="S33" s="718" t="n"/>
-      <c r="T33" s="718" t="n"/>
-      <c r="U33" s="718" t="n"/>
-      <c r="V33" s="718" t="n"/>
-      <c r="W33" s="718" t="n"/>
-      <c r="X33" s="718" t="n"/>
-      <c r="Y33" s="718" t="n"/>
-      <c r="Z33" s="718" t="n"/>
-      <c r="AA33" s="718" t="n"/>
-      <c r="AB33" s="718" t="n"/>
-      <c r="AC33" s="718" t="n"/>
-      <c r="AD33" s="718" t="n"/>
-      <c r="AE33" s="718" t="n"/>
-    </row>
-    <row r="34" ht="42" customHeight="1">
-      <c r="A34" s="751" t="n">
-        <v>3</v>
-      </c>
-      <c r="B34" s="752" t="inlineStr">
-        <is>
-          <t>Подключить Антона Гуркова к процессу изучения привязки клиента (Доки.Логистика / ЦКС)</t>
-        </is>
-      </c>
-      <c r="C34" s="752" t="inlineStr">
-        <is>
-          <t>Гурков А.</t>
-        </is>
-      </c>
-      <c r="D34" s="752" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="E34" s="753" t="inlineStr">
-        <is>
-          <t>взял на себя</t>
-        </is>
-      </c>
-      <c r="F34" s="752" t="inlineStr">
-        <is>
-          <t>Задача Оксаны Ремез — прописать подробнее после пересмотра встречи</t>
-        </is>
-      </c>
-      <c r="G34" s="752" t="n"/>
-      <c r="H34" s="718" t="n"/>
-      <c r="I34" s="718" t="n"/>
-      <c r="J34" s="718" t="n"/>
-      <c r="K34" s="718" t="n"/>
-      <c r="L34" s="718" t="n"/>
-      <c r="M34" s="718" t="n"/>
-      <c r="N34" s="718" t="n"/>
-      <c r="O34" s="718" t="n"/>
-      <c r="P34" s="718" t="n"/>
-      <c r="Q34" s="718" t="n"/>
-      <c r="R34" s="718" t="n"/>
-      <c r="S34" s="718" t="n"/>
-      <c r="T34" s="718" t="n"/>
-      <c r="U34" s="718" t="n"/>
-      <c r="V34" s="718" t="n"/>
-      <c r="W34" s="718" t="n"/>
-      <c r="X34" s="718" t="n"/>
-      <c r="Y34" s="718" t="n"/>
-      <c r="Z34" s="718" t="n"/>
-      <c r="AA34" s="718" t="n"/>
-      <c r="AB34" s="718" t="n"/>
-      <c r="AC34" s="718" t="n"/>
-      <c r="AD34" s="718" t="n"/>
-      <c r="AE34" s="718" t="n"/>
-    </row>
-    <row r="35" ht="42" customHeight="1">
-      <c r="A35" s="751" t="n">
-        <v>4</v>
-      </c>
-      <c r="B35" s="752" t="inlineStr">
-        <is>
-          <t>Выяснить у Калуги: можно ли отследить активность клиента в сервисе Доки</t>
-        </is>
-      </c>
-      <c r="C35" s="752" t="inlineStr">
-        <is>
-          <t>Дивакова М.</t>
-        </is>
-      </c>
-      <c r="D35" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E35" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F35" s="752" t="inlineStr"/>
-      <c r="G35" s="752" t="n"/>
-      <c r="H35" s="718" t="n"/>
-      <c r="I35" s="718" t="n"/>
-      <c r="J35" s="718" t="n"/>
-      <c r="K35" s="718" t="n"/>
-      <c r="L35" s="718" t="n"/>
-      <c r="M35" s="718" t="n"/>
-      <c r="N35" s="718" t="n"/>
-      <c r="O35" s="718" t="n"/>
-      <c r="P35" s="718" t="n"/>
-      <c r="Q35" s="718" t="n"/>
-      <c r="R35" s="718" t="n"/>
-      <c r="S35" s="718" t="n"/>
-      <c r="T35" s="718" t="n"/>
-      <c r="U35" s="718" t="n"/>
-      <c r="V35" s="718" t="n"/>
-      <c r="W35" s="718" t="n"/>
-      <c r="X35" s="718" t="n"/>
-      <c r="Y35" s="718" t="n"/>
-      <c r="Z35" s="718" t="n"/>
-      <c r="AA35" s="718" t="n"/>
-      <c r="AB35" s="718" t="n"/>
-      <c r="AC35" s="718" t="n"/>
-      <c r="AD35" s="718" t="n"/>
-      <c r="AE35" s="718" t="n"/>
-    </row>
-    <row r="36" ht="42" customHeight="1">
-      <c r="A36" s="751" t="n">
-        <v>5</v>
-      </c>
-      <c r="B36" s="752" t="inlineStr">
-        <is>
-          <t>Уточнить у Никитченко: считается ли Доки в охват сервисами ЭПД</t>
-        </is>
-      </c>
-      <c r="C36" s="752" t="inlineStr">
-        <is>
-          <t>Дворяк (Саша)</t>
-        </is>
-      </c>
-      <c r="D36" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E36" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F36" s="752" t="inlineStr">
-        <is>
-          <t>Саша спросит</t>
-        </is>
-      </c>
-      <c r="G36" s="752" t="n"/>
-      <c r="H36" s="718" t="n"/>
-      <c r="I36" s="718" t="n"/>
-      <c r="J36" s="718" t="n"/>
-      <c r="K36" s="718" t="n"/>
-      <c r="L36" s="718" t="n"/>
-      <c r="M36" s="718" t="n"/>
-      <c r="N36" s="718" t="n"/>
-      <c r="O36" s="718" t="n"/>
-      <c r="P36" s="718" t="n"/>
-      <c r="Q36" s="718" t="n"/>
-      <c r="R36" s="718" t="n"/>
-      <c r="S36" s="718" t="n"/>
-      <c r="T36" s="718" t="n"/>
-      <c r="U36" s="718" t="n"/>
-      <c r="V36" s="718" t="n"/>
-      <c r="W36" s="718" t="n"/>
-      <c r="X36" s="718" t="n"/>
-      <c r="Y36" s="718" t="n"/>
-      <c r="Z36" s="718" t="n"/>
-      <c r="AA36" s="718" t="n"/>
-      <c r="AB36" s="718" t="n"/>
-      <c r="AC36" s="718" t="n"/>
-      <c r="AD36" s="718" t="n"/>
-      <c r="AE36" s="718" t="n"/>
-    </row>
-    <row r="37" ht="42" customHeight="1">
-      <c r="A37" s="751" t="n">
-        <v>6</v>
-      </c>
-      <c r="B37" s="752" t="inlineStr">
-        <is>
-          <t>Подготовить со СМАК материалы для прогрева клиента на период демо-доступа</t>
-        </is>
-      </c>
-      <c r="C37" s="752" t="inlineStr">
-        <is>
-          <t>СМАК + ответственный</t>
-        </is>
-      </c>
-      <c r="D37" s="752" t="inlineStr">
-        <is>
-          <t>к 01.10</t>
-        </is>
-      </c>
-      <c r="E37" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F37" s="752" t="inlineStr">
-        <is>
-          <t>С 01.10 демо = 14 дней; до 01.10 — 3 месяца бесплатно</t>
-        </is>
-      </c>
-      <c r="G37" s="752" t="n"/>
-      <c r="H37" s="718" t="n"/>
-      <c r="I37" s="718" t="n"/>
-      <c r="J37" s="718" t="n"/>
-      <c r="K37" s="718" t="n"/>
-      <c r="L37" s="718" t="n"/>
-      <c r="M37" s="718" t="n"/>
-      <c r="N37" s="718" t="n"/>
-      <c r="O37" s="718" t="n"/>
-      <c r="P37" s="718" t="n"/>
-      <c r="Q37" s="718" t="n"/>
-      <c r="R37" s="718" t="n"/>
-      <c r="S37" s="718" t="n"/>
-      <c r="T37" s="718" t="n"/>
-      <c r="U37" s="718" t="n"/>
-      <c r="V37" s="718" t="n"/>
-      <c r="W37" s="718" t="n"/>
-      <c r="X37" s="718" t="n"/>
-      <c r="Y37" s="718" t="n"/>
-      <c r="Z37" s="718" t="n"/>
-      <c r="AA37" s="718" t="n"/>
-      <c r="AB37" s="718" t="n"/>
-      <c r="AC37" s="718" t="n"/>
-      <c r="AD37" s="718" t="n"/>
-      <c r="AE37" s="718" t="n"/>
-    </row>
-    <row r="38" ht="42" customHeight="1">
-      <c r="A38" s="751" t="n">
-        <v>7</v>
-      </c>
-      <c r="B38" s="752" t="inlineStr">
-        <is>
-          <t>Подготовить калькулятор пополнения титулов / помощи менеджеру ЦКС при продлении</t>
-        </is>
-      </c>
-      <c r="C38" s="752" t="inlineStr">
-        <is>
-          <t>Вика + Маша</t>
-        </is>
-      </c>
-      <c r="D38" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E38" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F38" s="752" t="inlineStr">
-        <is>
-          <t>Обсуждали накануне лектория с 1С</t>
-        </is>
-      </c>
-      <c r="G38" s="752" t="n"/>
-      <c r="H38" s="718" t="n"/>
-      <c r="I38" s="718" t="n"/>
-      <c r="J38" s="718" t="n"/>
-      <c r="K38" s="718" t="n"/>
-      <c r="L38" s="718" t="n"/>
-      <c r="M38" s="718" t="n"/>
-      <c r="N38" s="718" t="n"/>
-      <c r="O38" s="718" t="n"/>
-      <c r="P38" s="718" t="n"/>
-      <c r="Q38" s="718" t="n"/>
-      <c r="R38" s="718" t="n"/>
-      <c r="S38" s="718" t="n"/>
-      <c r="T38" s="718" t="n"/>
-      <c r="U38" s="718" t="n"/>
-      <c r="V38" s="718" t="n"/>
-      <c r="W38" s="718" t="n"/>
-      <c r="X38" s="718" t="n"/>
-      <c r="Y38" s="718" t="n"/>
-      <c r="Z38" s="718" t="n"/>
-      <c r="AA38" s="718" t="n"/>
-      <c r="AB38" s="718" t="n"/>
-      <c r="AC38" s="718" t="n"/>
-      <c r="AD38" s="718" t="n"/>
-      <c r="AE38" s="718" t="n"/>
-    </row>
-    <row r="39" ht="42" customHeight="1">
-      <c r="A39" s="751" t="n">
-        <v>8</v>
-      </c>
-      <c r="B39" s="752" t="inlineStr">
-        <is>
-          <t>Подготовить текст рассылки: «проверьте своего контрагента и впишите в тандем» — показать сроки и текст</t>
-        </is>
-      </c>
-      <c r="C39" s="752" t="inlineStr">
-        <is>
-          <t>Блохина (Лиза)</t>
-        </is>
-      </c>
-      <c r="D39" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E39" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F39" s="752" t="inlineStr"/>
-      <c r="G39" s="752" t="n"/>
-      <c r="H39" s="718" t="n"/>
-      <c r="I39" s="718" t="n"/>
-      <c r="J39" s="718" t="n"/>
-      <c r="K39" s="718" t="n"/>
-      <c r="L39" s="718" t="n"/>
-      <c r="M39" s="718" t="n"/>
-      <c r="N39" s="718" t="n"/>
-      <c r="O39" s="718" t="n"/>
-      <c r="P39" s="718" t="n"/>
-      <c r="Q39" s="718" t="n"/>
-      <c r="R39" s="718" t="n"/>
-      <c r="S39" s="718" t="n"/>
-      <c r="T39" s="718" t="n"/>
-      <c r="U39" s="718" t="n"/>
-      <c r="V39" s="718" t="n"/>
-      <c r="W39" s="718" t="n"/>
-      <c r="X39" s="718" t="n"/>
-      <c r="Y39" s="718" t="n"/>
-      <c r="Z39" s="718" t="n"/>
-      <c r="AA39" s="718" t="n"/>
-      <c r="AB39" s="718" t="n"/>
-      <c r="AC39" s="718" t="n"/>
-      <c r="AD39" s="718" t="n"/>
-      <c r="AE39" s="718" t="n"/>
-    </row>
-    <row r="40" ht="42" customHeight="1">
-      <c r="A40" s="751" t="n">
-        <v>9</v>
-      </c>
-      <c r="B40" s="752" t="inlineStr">
-        <is>
-          <t>Обзвонить крупных клиентов (от 2 000 титулов / генераторы трафика) и предложить ЭПД ТАНДЕМ</t>
-        </is>
-      </c>
-      <c r="C40" s="752" t="inlineStr">
-        <is>
-          <t>ЦП / ЦКС</t>
-        </is>
-      </c>
-      <c r="D40" s="752" t="inlineStr">
-        <is>
-          <t>сентябрь</t>
-        </is>
-      </c>
-      <c r="E40" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F40" s="752" t="inlineStr">
-        <is>
-          <t>Начать с крупных; корп. сегмент продавал ЭПД даже в малом объёме</t>
-        </is>
-      </c>
-      <c r="G40" s="752" t="n"/>
-      <c r="H40" s="718" t="n"/>
-      <c r="I40" s="718" t="n"/>
-      <c r="J40" s="718" t="n"/>
-      <c r="K40" s="718" t="n"/>
-      <c r="L40" s="718" t="n"/>
-      <c r="M40" s="718" t="n"/>
-      <c r="N40" s="718" t="n"/>
-      <c r="O40" s="718" t="n"/>
-      <c r="P40" s="718" t="n"/>
-      <c r="Q40" s="718" t="n"/>
-      <c r="R40" s="718" t="n"/>
-      <c r="S40" s="718" t="n"/>
-      <c r="T40" s="718" t="n"/>
-      <c r="U40" s="718" t="n"/>
-      <c r="V40" s="718" t="n"/>
-      <c r="W40" s="718" t="n"/>
-      <c r="X40" s="718" t="n"/>
-      <c r="Y40" s="718" t="n"/>
-      <c r="Z40" s="718" t="n"/>
-      <c r="AA40" s="718" t="n"/>
-      <c r="AB40" s="718" t="n"/>
-      <c r="AC40" s="718" t="n"/>
-      <c r="AD40" s="718" t="n"/>
-      <c r="AE40" s="718" t="n"/>
-    </row>
-    <row r="41" ht="42" customHeight="1">
-      <c r="A41" s="751" t="n">
-        <v>10</v>
-      </c>
-      <c r="B41" s="752" t="inlineStr">
-        <is>
-          <t>Обзвон подключённых клиентов: оценка удовлетворённости + проекты ЦАС (Доки)</t>
-        </is>
-      </c>
-      <c r="C41" s="752" t="inlineStr">
-        <is>
-          <t>Дворяк / Лазарчук</t>
-        </is>
-      </c>
-      <c r="D41" s="752" t="inlineStr">
-        <is>
-          <t>сентябрь</t>
-        </is>
-      </c>
-      <c r="E41" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F41" s="752" t="inlineStr">
-        <is>
-          <t>Задача по клиентам ЦАС (Доки)</t>
-        </is>
-      </c>
-      <c r="G41" s="752" t="n"/>
-      <c r="H41" s="718" t="n"/>
-      <c r="I41" s="718" t="n"/>
-      <c r="J41" s="718" t="n"/>
-      <c r="K41" s="718" t="n"/>
-      <c r="L41" s="718" t="n"/>
-      <c r="M41" s="718" t="n"/>
-      <c r="N41" s="718" t="n"/>
-      <c r="O41" s="718" t="n"/>
-      <c r="P41" s="718" t="n"/>
-      <c r="Q41" s="718" t="n"/>
-      <c r="R41" s="718" t="n"/>
-      <c r="S41" s="718" t="n"/>
-      <c r="T41" s="718" t="n"/>
-      <c r="U41" s="718" t="n"/>
-      <c r="V41" s="718" t="n"/>
-      <c r="W41" s="718" t="n"/>
-      <c r="X41" s="718" t="n"/>
-      <c r="Y41" s="718" t="n"/>
-      <c r="Z41" s="718" t="n"/>
-      <c r="AA41" s="718" t="n"/>
-      <c r="AB41" s="718" t="n"/>
-      <c r="AC41" s="718" t="n"/>
-      <c r="AD41" s="718" t="n"/>
-      <c r="AE41" s="718" t="n"/>
-    </row>
-    <row r="42" ht="42" customHeight="1">
-      <c r="A42" s="751" t="n">
-        <v>11</v>
-      </c>
-      <c r="B42" s="752" t="inlineStr">
-        <is>
-          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в первую неделю сентября</t>
-        </is>
-      </c>
-      <c r="C42" s="752" t="inlineStr">
-        <is>
-          <t>Юлиана</t>
-        </is>
-      </c>
-      <c r="D42" s="752" t="inlineStr">
-        <is>
-          <t>1-я неделя сентября</t>
-        </is>
-      </c>
-      <c r="E42" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F42" s="752" t="inlineStr">
-        <is>
-          <t>Клиенты сбытового офиса уходят на СБИС — разобрать причины</t>
-        </is>
-      </c>
-      <c r="G42" s="752" t="n"/>
-      <c r="H42" s="718" t="n"/>
-      <c r="I42" s="718" t="n"/>
-      <c r="J42" s="718" t="n"/>
-      <c r="K42" s="718" t="n"/>
-      <c r="L42" s="718" t="n"/>
-      <c r="M42" s="718" t="n"/>
-      <c r="N42" s="718" t="n"/>
-      <c r="O42" s="718" t="n"/>
-      <c r="P42" s="718" t="n"/>
-      <c r="Q42" s="718" t="n"/>
-      <c r="R42" s="718" t="n"/>
-      <c r="S42" s="718" t="n"/>
-      <c r="T42" s="718" t="n"/>
-      <c r="U42" s="718" t="n"/>
-      <c r="V42" s="718" t="n"/>
-      <c r="W42" s="718" t="n"/>
-      <c r="X42" s="718" t="n"/>
-      <c r="Y42" s="718" t="n"/>
-      <c r="Z42" s="718" t="n"/>
-      <c r="AA42" s="718" t="n"/>
-      <c r="AB42" s="718" t="n"/>
-      <c r="AC42" s="718" t="n"/>
-      <c r="AD42" s="718" t="n"/>
-      <c r="AE42" s="718" t="n"/>
-    </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="751" t="n">
-        <v>12</v>
-      </c>
-      <c r="B43" s="752" t="inlineStr">
-        <is>
-          <t>Проверить в базе: подключён ли клиент к каналу ЭПД (МАКС / ТГ / ВК); оценить как альт. канал привлечения</t>
-        </is>
-      </c>
-      <c r="C43" s="752" t="inlineStr">
-        <is>
-          <t>ЦП / ЦКС</t>
-        </is>
-      </c>
-      <c r="D43" s="752" t="inlineStr">
-        <is>
-          <t>до след. встречи</t>
-        </is>
-      </c>
-      <c r="E43" s="749" t="inlineStr">
-        <is>
-          <t>в работе</t>
-        </is>
-      </c>
-      <c r="F43" s="752" t="inlineStr">
-        <is>
-          <t>Связать со стратегией и целями</t>
-        </is>
-      </c>
-      <c r="G43" s="752" t="n"/>
-      <c r="H43" s="718" t="n"/>
-      <c r="I43" s="718" t="n"/>
-      <c r="J43" s="718" t="n"/>
-      <c r="K43" s="718" t="n"/>
-      <c r="L43" s="718" t="n"/>
-      <c r="M43" s="718" t="n"/>
-      <c r="N43" s="718" t="n"/>
-      <c r="O43" s="718" t="n"/>
-      <c r="P43" s="718" t="n"/>
-      <c r="Q43" s="718" t="n"/>
-      <c r="R43" s="718" t="n"/>
-      <c r="S43" s="718" t="n"/>
-      <c r="T43" s="718" t="n"/>
-      <c r="U43" s="718" t="n"/>
-      <c r="V43" s="718" t="n"/>
-      <c r="W43" s="718" t="n"/>
-      <c r="X43" s="718" t="n"/>
-      <c r="Y43" s="718" t="n"/>
-      <c r="Z43" s="718" t="n"/>
-      <c r="AA43" s="718" t="n"/>
-      <c r="AB43" s="718" t="n"/>
-      <c r="AC43" s="718" t="n"/>
-      <c r="AD43" s="718" t="n"/>
-      <c r="AE43" s="718" t="n"/>
-    </row>
-    <row r="44" ht="42" customHeight="1">
-      <c r="A44" s="751" t="n">
-        <v>13</v>
-      </c>
-      <c r="B44" s="752" t="inlineStr">
-        <is>
-          <t>Зафиксировать целевую структуру плана 500 клиентов до конца 2026: 50 крупных / 300 средних / 150 мелких</t>
-        </is>
-      </c>
-      <c r="C44" s="752" t="inlineStr">
-        <is>
-          <t>Все участники</t>
-        </is>
-      </c>
-      <c r="D44" s="752" t="inlineStr">
-        <is>
-          <t>принято</t>
-        </is>
-      </c>
-      <c r="E44" s="748" t="inlineStr">
-        <is>
-          <t>принято</t>
-        </is>
-      </c>
-      <c r="F44" s="752" t="inlineStr">
-        <is>
-          <t>Приоритет — количество клиентов, не сумма выручки на старте</t>
-        </is>
-      </c>
-      <c r="G44" s="752" t="n"/>
-      <c r="H44" s="718" t="n"/>
-      <c r="I44" s="718" t="n"/>
-      <c r="J44" s="718" t="n"/>
-      <c r="K44" s="718" t="n"/>
-      <c r="L44" s="718" t="n"/>
-      <c r="M44" s="718" t="n"/>
-      <c r="N44" s="718" t="n"/>
-      <c r="O44" s="718" t="n"/>
-      <c r="P44" s="718" t="n"/>
-      <c r="Q44" s="718" t="n"/>
-      <c r="R44" s="718" t="n"/>
-      <c r="S44" s="718" t="n"/>
-      <c r="T44" s="718" t="n"/>
-      <c r="U44" s="718" t="n"/>
-      <c r="V44" s="718" t="n"/>
-      <c r="W44" s="718" t="n"/>
-      <c r="X44" s="718" t="n"/>
-      <c r="Y44" s="718" t="n"/>
-      <c r="Z44" s="718" t="n"/>
-      <c r="AA44" s="718" t="n"/>
-      <c r="AB44" s="718" t="n"/>
-      <c r="AC44" s="718" t="n"/>
-      <c r="AD44" s="718" t="n"/>
-      <c r="AE44" s="718" t="n"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="A45" s="718" t="n"/>
-      <c r="B45" s="718" t="n"/>
-      <c r="C45" s="718" t="n"/>
-      <c r="D45" s="718" t="n"/>
-      <c r="E45" s="718" t="n"/>
-      <c r="F45" s="718" t="n"/>
-      <c r="G45" s="718" t="n"/>
-      <c r="H45" s="718" t="n"/>
-      <c r="I45" s="718" t="n"/>
-      <c r="J45" s="718" t="n"/>
-      <c r="K45" s="718" t="n"/>
-      <c r="L45" s="718" t="n"/>
-      <c r="M45" s="718" t="n"/>
-      <c r="N45" s="718" t="n"/>
-      <c r="O45" s="718" t="n"/>
-      <c r="P45" s="718" t="n"/>
-      <c r="Q45" s="718" t="n"/>
-      <c r="R45" s="718" t="n"/>
-      <c r="S45" s="718" t="n"/>
-      <c r="T45" s="718" t="n"/>
-      <c r="U45" s="718" t="n"/>
-      <c r="V45" s="718" t="n"/>
-      <c r="W45" s="718" t="n"/>
-      <c r="X45" s="718" t="n"/>
-      <c r="Y45" s="718" t="n"/>
-      <c r="Z45" s="718" t="n"/>
-      <c r="AA45" s="718" t="n"/>
-      <c r="AB45" s="718" t="n"/>
-      <c r="AC45" s="718" t="n"/>
-      <c r="AD45" s="718" t="n"/>
-      <c r="AE45" s="718" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="743" t="inlineStr">
-        <is>
-          <t>3. Обсуждаемые темы и выводы  ·  блоки и тезисы</t>
-        </is>
-      </c>
-      <c r="H46" s="718" t="n"/>
-      <c r="I46" s="718" t="n"/>
-      <c r="J46" s="718" t="n"/>
-      <c r="K46" s="718" t="n"/>
-      <c r="L46" s="718" t="n"/>
-      <c r="M46" s="718" t="n"/>
-      <c r="N46" s="718" t="n"/>
-      <c r="O46" s="718" t="n"/>
-      <c r="P46" s="718" t="n"/>
-      <c r="Q46" s="718" t="n"/>
-      <c r="R46" s="718" t="n"/>
-      <c r="S46" s="718" t="n"/>
-      <c r="T46" s="718" t="n"/>
-      <c r="U46" s="718" t="n"/>
-      <c r="V46" s="718" t="n"/>
-      <c r="W46" s="718" t="n"/>
-      <c r="X46" s="718" t="n"/>
-      <c r="Y46" s="718" t="n"/>
-      <c r="Z46" s="718" t="n"/>
-      <c r="AA46" s="718" t="n"/>
-      <c r="AB46" s="718" t="n"/>
-      <c r="AC46" s="718" t="n"/>
-      <c r="AD46" s="718" t="n"/>
-      <c r="AE46" s="718" t="n"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="A47" s="744" t="inlineStr">
-        <is>
-          <t>Блок</t>
-        </is>
-      </c>
-      <c r="B47" s="744" t="inlineStr">
-        <is>
-          <t>Тема / тезис</t>
-        </is>
-      </c>
-      <c r="C47" s="744" t="n"/>
-      <c r="D47" s="744" t="inlineStr">
-        <is>
-          <t>Выводы и решения</t>
-        </is>
-      </c>
-      <c r="E47" s="744" t="n"/>
-      <c r="F47" s="744" t="n"/>
-      <c r="G47" s="744" t="n"/>
-      <c r="H47" s="718" t="n"/>
-      <c r="I47" s="718" t="n"/>
-      <c r="J47" s="718" t="n"/>
-      <c r="K47" s="718" t="n"/>
-      <c r="L47" s="718" t="n"/>
-      <c r="M47" s="718" t="n"/>
-      <c r="N47" s="718" t="n"/>
-      <c r="O47" s="718" t="n"/>
-      <c r="P47" s="718" t="n"/>
-      <c r="Q47" s="718" t="n"/>
-      <c r="R47" s="718" t="n"/>
-      <c r="S47" s="718" t="n"/>
-      <c r="T47" s="718" t="n"/>
-      <c r="U47" s="718" t="n"/>
-      <c r="V47" s="718" t="n"/>
-      <c r="W47" s="718" t="n"/>
-      <c r="X47" s="718" t="n"/>
-      <c r="Y47" s="718" t="n"/>
-      <c r="Z47" s="718" t="n"/>
-      <c r="AA47" s="718" t="n"/>
-      <c r="AB47" s="718" t="n"/>
-      <c r="AC47" s="718" t="n"/>
-      <c r="AD47" s="718" t="n"/>
-      <c r="AE47" s="718" t="n"/>
-    </row>
-    <row r="48" ht="48" customHeight="1">
-      <c r="A48" s="754" t="inlineStr">
-        <is>
-          <t>Акция и ЦСВ</t>
-        </is>
-      </c>
-      <c r="B48" s="755" t="inlineStr">
-        <is>
-          <t>Трудозатраты ЦСВ на акцию по ЭПД</t>
-        </is>
-      </c>
-      <c r="C48" s="756" t="n"/>
-      <c r="D48" s="757" t="inlineStr">
-        <is>
-          <t>Акцию продлили до 30.09. Уточнить адресата вопроса у Оксаны.</t>
-        </is>
-      </c>
-      <c r="E48" s="756" t="n"/>
-      <c r="F48" s="756" t="n"/>
-      <c r="G48" s="756" t="n"/>
-      <c r="H48" s="718" t="n"/>
-      <c r="I48" s="718" t="n"/>
-      <c r="J48" s="718" t="n"/>
-      <c r="K48" s="718" t="n"/>
-      <c r="L48" s="718" t="n"/>
-      <c r="M48" s="718" t="n"/>
-      <c r="N48" s="718" t="n"/>
-      <c r="O48" s="718" t="n"/>
-      <c r="P48" s="718" t="n"/>
-      <c r="Q48" s="718" t="n"/>
-      <c r="R48" s="718" t="n"/>
-      <c r="S48" s="718" t="n"/>
-      <c r="T48" s="718" t="n"/>
-      <c r="U48" s="718" t="n"/>
-      <c r="V48" s="718" t="n"/>
-      <c r="W48" s="718" t="n"/>
-      <c r="X48" s="718" t="n"/>
-      <c r="Y48" s="718" t="n"/>
-      <c r="Z48" s="718" t="n"/>
-      <c r="AA48" s="718" t="n"/>
-      <c r="AB48" s="718" t="n"/>
-      <c r="AC48" s="718" t="n"/>
-      <c r="AD48" s="718" t="n"/>
-      <c r="AE48" s="718" t="n"/>
-    </row>
-    <row r="49" ht="48" customHeight="1">
-      <c r="A49" s="758" t="inlineStr">
-        <is>
-          <t>Каналы
-МАКС / ТГ / ВК</t>
-        </is>
-      </c>
-      <c r="B49" s="759" t="inlineStr">
-        <is>
-          <t>Можем ли прорабатывать клиентов канала ЭПД силами ЦП и ЦКС? Альтернативный канал привлечения.</t>
-        </is>
-      </c>
-      <c r="C49" s="760" t="n"/>
-      <c r="D49" s="760" t="inlineStr">
-        <is>
-          <t>Нужна проверка базы: подключён клиент к каналу или нет. Идея — просить менеджеров подключать клиентов; вопрос мотивации клиента открыт.</t>
-        </is>
-      </c>
-      <c r="E49" s="760" t="n"/>
-      <c r="F49" s="760" t="n"/>
-      <c r="G49" s="760" t="n"/>
-      <c r="H49" s="718" t="n"/>
-      <c r="I49" s="718" t="n"/>
-      <c r="J49" s="718" t="n"/>
-      <c r="K49" s="718" t="n"/>
-      <c r="L49" s="718" t="n"/>
-      <c r="M49" s="718" t="n"/>
-      <c r="N49" s="718" t="n"/>
-      <c r="O49" s="718" t="n"/>
-      <c r="P49" s="718" t="n"/>
-      <c r="Q49" s="718" t="n"/>
-      <c r="R49" s="718" t="n"/>
-      <c r="S49" s="718" t="n"/>
-      <c r="T49" s="718" t="n"/>
-      <c r="U49" s="718" t="n"/>
-      <c r="V49" s="718" t="n"/>
-      <c r="W49" s="718" t="n"/>
-      <c r="X49" s="718" t="n"/>
-      <c r="Y49" s="718" t="n"/>
-      <c r="Z49" s="718" t="n"/>
-      <c r="AA49" s="718" t="n"/>
-      <c r="AB49" s="718" t="n"/>
-      <c r="AC49" s="718" t="n"/>
-      <c r="AD49" s="718" t="n"/>
-      <c r="AE49" s="718" t="n"/>
-    </row>
-    <row r="50" ht="48" customHeight="1">
-      <c r="A50" s="761" t="inlineStr">
-        <is>
-          <t>Стратегия
-и сегментация</t>
-        </is>
-      </c>
-      <c r="B50" s="762" t="inlineStr">
-        <is>
-          <t>Заход в Элиттрейд (таблица Дворяк) → контрагенты. Сегментировать охваченных на крупных / средних / мелких.</t>
-        </is>
-      </c>
-      <c r="C50" s="730" t="n"/>
-      <c r="D50" s="752" t="inlineStr">
-        <is>
-          <t>Производители (крупные) задают правила для перевозчиков → те для получателей. Лиза уточнит у Суворовой статус Элиттрейд + акция 3 мес. Доки.</t>
-        </is>
-      </c>
-      <c r="E50" s="730" t="n"/>
-      <c r="F50" s="730" t="n"/>
-      <c r="G50" s="730" t="n"/>
-      <c r="H50" s="718" t="n"/>
-      <c r="I50" s="718" t="n"/>
-      <c r="J50" s="718" t="n"/>
-      <c r="K50" s="718" t="n"/>
-      <c r="L50" s="718" t="n"/>
-      <c r="M50" s="718" t="n"/>
-      <c r="N50" s="718" t="n"/>
-      <c r="O50" s="718" t="n"/>
-      <c r="P50" s="718" t="n"/>
-      <c r="Q50" s="718" t="n"/>
-      <c r="R50" s="718" t="n"/>
-      <c r="S50" s="718" t="n"/>
-      <c r="T50" s="718" t="n"/>
-      <c r="U50" s="718" t="n"/>
-      <c r="V50" s="718" t="n"/>
-      <c r="W50" s="718" t="n"/>
-      <c r="X50" s="718" t="n"/>
-      <c r="Y50" s="718" t="n"/>
-      <c r="Z50" s="718" t="n"/>
-      <c r="AA50" s="718" t="n"/>
-      <c r="AB50" s="718" t="n"/>
-      <c r="AC50" s="718" t="n"/>
-      <c r="AD50" s="718" t="n"/>
-      <c r="AE50" s="718" t="n"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="763" t="n"/>
-      <c r="B51" s="762" t="inlineStr">
-        <is>
-          <t>Признак «крупный» = генератор трафика (привлечение контрагентов).</t>
-        </is>
-      </c>
-      <c r="C51" s="730" t="n"/>
-      <c r="D51" s="757" t="inlineStr">
-        <is>
-          <t>Согласовали целевое соотношение базы под план 500.</t>
-        </is>
-      </c>
-      <c r="E51" s="730" t="n"/>
-      <c r="F51" s="730" t="n"/>
-      <c r="G51" s="730" t="n"/>
-      <c r="H51" s="718" t="n"/>
-      <c r="I51" s="718" t="n"/>
-      <c r="J51" s="718" t="n"/>
-      <c r="K51" s="718" t="n"/>
-      <c r="L51" s="718" t="n"/>
-      <c r="M51" s="718" t="n"/>
-      <c r="N51" s="718" t="n"/>
-      <c r="O51" s="718" t="n"/>
-      <c r="P51" s="718" t="n"/>
-      <c r="Q51" s="718" t="n"/>
-      <c r="R51" s="718" t="n"/>
-      <c r="S51" s="718" t="n"/>
-      <c r="T51" s="718" t="n"/>
-      <c r="U51" s="718" t="n"/>
-      <c r="V51" s="718" t="n"/>
-      <c r="W51" s="718" t="n"/>
-      <c r="X51" s="718" t="n"/>
-      <c r="Y51" s="718" t="n"/>
-      <c r="Z51" s="718" t="n"/>
-      <c r="AA51" s="718" t="n"/>
-      <c r="AB51" s="718" t="n"/>
-      <c r="AC51" s="718" t="n"/>
-      <c r="AD51" s="718" t="n"/>
-      <c r="AE51" s="718" t="n"/>
-    </row>
-    <row r="52" ht="48" customHeight="1">
-      <c r="A52" s="764" t="n"/>
-      <c r="B52" s="762" t="inlineStr">
-        <is>
-          <t>Приоритет — количество привлечённых клиентов, не сумма заработка. Выстроить цепочку «закрепления» и почкования с одного пакета.</t>
-        </is>
-      </c>
-      <c r="C52" s="730" t="n"/>
-      <c r="D52" s="752" t="inlineStr">
-        <is>
-          <t>ПЛАН: 500 клиентов до конца 2026 → 50 крупных + 300 средних + 150 мелких.</t>
-        </is>
-      </c>
-      <c r="E52" s="730" t="n"/>
-      <c r="F52" s="730" t="n"/>
-      <c r="G52" s="730" t="n"/>
-      <c r="H52" s="718" t="n"/>
-      <c r="I52" s="718" t="n"/>
-      <c r="J52" s="718" t="n"/>
-      <c r="K52" s="718" t="n"/>
-      <c r="L52" s="718" t="n"/>
-      <c r="M52" s="718" t="n"/>
-      <c r="N52" s="718" t="n"/>
-      <c r="O52" s="718" t="n"/>
-      <c r="P52" s="718" t="n"/>
-      <c r="Q52" s="718" t="n"/>
-      <c r="R52" s="718" t="n"/>
-      <c r="S52" s="718" t="n"/>
-      <c r="T52" s="718" t="n"/>
-      <c r="U52" s="718" t="n"/>
-      <c r="V52" s="718" t="n"/>
-      <c r="W52" s="718" t="n"/>
-      <c r="X52" s="718" t="n"/>
-      <c r="Y52" s="718" t="n"/>
-      <c r="Z52" s="718" t="n"/>
-      <c r="AA52" s="718" t="n"/>
-      <c r="AB52" s="718" t="n"/>
-      <c r="AC52" s="718" t="n"/>
-      <c r="AD52" s="718" t="n"/>
-      <c r="AE52" s="718" t="n"/>
-    </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="765" t="inlineStr">
-        <is>
-          <t>Доки.
-Логистика
-и охват</t>
-        </is>
-      </c>
-      <c r="B53" s="766" t="inlineStr">
-        <is>
-          <t>Задача по Доки.Логистика (Оксана Ремез) — детализировать после пересмотра встречи.</t>
-        </is>
-      </c>
-      <c r="C53" s="767" t="n"/>
-      <c r="D53" s="752" t="inlineStr">
-        <is>
-          <t>Подключить Антона Гуркова к изучению привязки клиента. Антон взял на себя.</t>
-        </is>
-      </c>
-      <c r="E53" s="767" t="n"/>
-      <c r="F53" s="767" t="n"/>
-      <c r="G53" s="767" t="n"/>
-      <c r="H53" s="718" t="n"/>
-      <c r="I53" s="718" t="n"/>
-      <c r="J53" s="718" t="n"/>
-      <c r="K53" s="718" t="n"/>
-      <c r="L53" s="718" t="n"/>
-      <c r="M53" s="718" t="n"/>
-      <c r="N53" s="718" t="n"/>
-      <c r="O53" s="718" t="n"/>
-      <c r="P53" s="718" t="n"/>
-      <c r="Q53" s="718" t="n"/>
-      <c r="R53" s="718" t="n"/>
-      <c r="S53" s="718" t="n"/>
-      <c r="T53" s="718" t="n"/>
-      <c r="U53" s="718" t="n"/>
-      <c r="V53" s="718" t="n"/>
-      <c r="W53" s="718" t="n"/>
-      <c r="X53" s="718" t="n"/>
-      <c r="Y53" s="718" t="n"/>
-      <c r="Z53" s="718" t="n"/>
-      <c r="AA53" s="718" t="n"/>
-      <c r="AB53" s="718" t="n"/>
-      <c r="AC53" s="718" t="n"/>
-      <c r="AD53" s="718" t="n"/>
-      <c r="AE53" s="718" t="n"/>
-    </row>
-    <row r="54" ht="48" customHeight="1">
-      <c r="A54" s="763" t="n"/>
-      <c r="B54" s="766" t="inlineStr">
-        <is>
-          <t>Можем ли отследить активность клиента в Доки? (вопрос Калуге)</t>
-        </is>
-      </c>
-      <c r="C54" s="767" t="n"/>
-      <c r="D54" s="752" t="inlineStr">
-        <is>
-          <t>Маша Дивакова выяснит.</t>
-        </is>
-      </c>
-      <c r="E54" s="767" t="n"/>
-      <c r="F54" s="767" t="n"/>
-      <c r="G54" s="767" t="n"/>
-      <c r="H54" s="718" t="n"/>
-      <c r="I54" s="718" t="n"/>
-      <c r="J54" s="718" t="n"/>
-      <c r="K54" s="718" t="n"/>
-      <c r="L54" s="718" t="n"/>
-      <c r="M54" s="718" t="n"/>
-      <c r="N54" s="718" t="n"/>
-      <c r="O54" s="718" t="n"/>
-      <c r="P54" s="718" t="n"/>
-      <c r="Q54" s="718" t="n"/>
-      <c r="R54" s="718" t="n"/>
-      <c r="S54" s="718" t="n"/>
-      <c r="T54" s="718" t="n"/>
-      <c r="U54" s="718" t="n"/>
-      <c r="V54" s="718" t="n"/>
-      <c r="W54" s="718" t="n"/>
-      <c r="X54" s="718" t="n"/>
-      <c r="Y54" s="718" t="n"/>
-      <c r="Z54" s="718" t="n"/>
-      <c r="AA54" s="718" t="n"/>
-      <c r="AB54" s="718" t="n"/>
-      <c r="AC54" s="718" t="n"/>
-      <c r="AD54" s="718" t="n"/>
-      <c r="AE54" s="718" t="n"/>
-    </row>
-    <row r="55" ht="48" customHeight="1">
-      <c r="A55" s="763" t="n"/>
-      <c r="B55" s="766" t="inlineStr">
-        <is>
-          <t>Считается ли Доки в охват сервисами ЭПД?</t>
-        </is>
-      </c>
-      <c r="C55" s="767" t="n"/>
-      <c r="D55" s="752" t="inlineStr">
-        <is>
-          <t>Вопрос Никитченко — Саша спросит. Цифры расходятся с Калугой; проблемы с закреплением.</t>
-        </is>
-      </c>
-      <c r="E55" s="767" t="n"/>
-      <c r="F55" s="767" t="n"/>
-      <c r="G55" s="767" t="n"/>
-      <c r="H55" s="718" t="n"/>
-      <c r="I55" s="718" t="n"/>
-      <c r="J55" s="718" t="n"/>
-      <c r="K55" s="718" t="n"/>
-      <c r="L55" s="718" t="n"/>
-      <c r="M55" s="718" t="n"/>
-      <c r="N55" s="718" t="n"/>
-      <c r="O55" s="718" t="n"/>
-      <c r="P55" s="718" t="n"/>
-      <c r="Q55" s="718" t="n"/>
-      <c r="R55" s="718" t="n"/>
-      <c r="S55" s="718" t="n"/>
-      <c r="T55" s="718" t="n"/>
-      <c r="U55" s="718" t="n"/>
-      <c r="V55" s="718" t="n"/>
-      <c r="W55" s="718" t="n"/>
-      <c r="X55" s="718" t="n"/>
-      <c r="Y55" s="718" t="n"/>
-      <c r="Z55" s="718" t="n"/>
-      <c r="AA55" s="718" t="n"/>
-      <c r="AB55" s="718" t="n"/>
-      <c r="AC55" s="718" t="n"/>
-      <c r="AD55" s="718" t="n"/>
-      <c r="AE55" s="718" t="n"/>
-    </row>
-    <row r="56" ht="48" customHeight="1">
-      <c r="A56" s="764" t="n"/>
-      <c r="B56" s="766" t="inlineStr">
-        <is>
-          <t>Все проданные ЭПД: центр компетенции изучает — всё ли продано, подключились ли.</t>
-        </is>
-      </c>
-      <c r="C56" s="767" t="n"/>
-      <c r="D56" s="767" t="inlineStr">
-        <is>
-          <t>Трафик не видим → не квалифицируем активность. 1С обещают данные в сентябре.</t>
-        </is>
-      </c>
-      <c r="E56" s="767" t="n"/>
-      <c r="F56" s="767" t="n"/>
-      <c r="G56" s="767" t="n"/>
-      <c r="H56" s="718" t="n"/>
-      <c r="I56" s="718" t="n"/>
-      <c r="J56" s="718" t="n"/>
-      <c r="K56" s="718" t="n"/>
-      <c r="L56" s="718" t="n"/>
-      <c r="M56" s="718" t="n"/>
-      <c r="N56" s="718" t="n"/>
-      <c r="O56" s="718" t="n"/>
-      <c r="P56" s="718" t="n"/>
-      <c r="Q56" s="718" t="n"/>
-      <c r="R56" s="718" t="n"/>
-      <c r="S56" s="718" t="n"/>
-      <c r="T56" s="718" t="n"/>
-      <c r="U56" s="718" t="n"/>
-      <c r="V56" s="718" t="n"/>
-      <c r="W56" s="718" t="n"/>
-      <c r="X56" s="718" t="n"/>
-      <c r="Y56" s="718" t="n"/>
-      <c r="Z56" s="718" t="n"/>
-      <c r="AA56" s="718" t="n"/>
-      <c r="AB56" s="718" t="n"/>
-      <c r="AC56" s="718" t="n"/>
-      <c r="AD56" s="718" t="n"/>
-      <c r="AE56" s="718" t="n"/>
-    </row>
-    <row r="57" ht="48" customHeight="1">
-      <c r="A57" s="768" t="inlineStr">
-        <is>
-          <t>Демо
-и прогрев</t>
-        </is>
-      </c>
-      <c r="B57" s="769" t="inlineStr">
-        <is>
-          <t>Со СМАК подготовить материалы прогрева на период демо-доступа.</t>
-        </is>
-      </c>
-      <c r="C57" s="770" t="n"/>
-      <c r="D57" s="757" t="inlineStr">
-        <is>
-          <t>С 01.10 — 14 дней демо; до 01.10 — 3 месяца бесплатно.</t>
-        </is>
-      </c>
-      <c r="E57" s="770" t="n"/>
-      <c r="F57" s="770" t="n"/>
-      <c r="G57" s="770" t="n"/>
-      <c r="H57" s="718" t="n"/>
-      <c r="I57" s="718" t="n"/>
-      <c r="J57" s="718" t="n"/>
-      <c r="K57" s="718" t="n"/>
-      <c r="L57" s="718" t="n"/>
-      <c r="M57" s="718" t="n"/>
-      <c r="N57" s="718" t="n"/>
-      <c r="O57" s="718" t="n"/>
-      <c r="P57" s="718" t="n"/>
-      <c r="Q57" s="718" t="n"/>
-      <c r="R57" s="718" t="n"/>
-      <c r="S57" s="718" t="n"/>
-      <c r="T57" s="718" t="n"/>
-      <c r="U57" s="718" t="n"/>
-      <c r="V57" s="718" t="n"/>
-      <c r="W57" s="718" t="n"/>
-      <c r="X57" s="718" t="n"/>
-      <c r="Y57" s="718" t="n"/>
-      <c r="Z57" s="718" t="n"/>
-      <c r="AA57" s="718" t="n"/>
-      <c r="AB57" s="718" t="n"/>
-      <c r="AC57" s="718" t="n"/>
-      <c r="AD57" s="718" t="n"/>
-      <c r="AE57" s="718" t="n"/>
-    </row>
-    <row r="58" ht="48" customHeight="1">
-      <c r="A58" s="771" t="inlineStr">
-        <is>
-          <t>Сопровождение
-МПП / ЦКС</t>
-        </is>
-      </c>
-      <c r="B58" s="772" t="inlineStr">
-        <is>
-          <t>План МПП: платные / бесплатные клиенты; «выхаживать» может отдельный человек (идея — Гурков).</t>
-        </is>
-      </c>
-      <c r="C58" s="773" t="n"/>
-      <c r="D58" s="773" t="inlineStr">
-        <is>
-          <t>Если есть ИТС — ЦКС смотрит динамику расхода ЭПД/Доки. Трафика пока нет; можно писать в Калугу с перечнем ИНН. Риск: кто выхаживает — текущие МПП или новый человек?</t>
-        </is>
-      </c>
-      <c r="E58" s="773" t="n"/>
-      <c r="F58" s="773" t="n"/>
-      <c r="G58" s="773" t="n"/>
-      <c r="H58" s="718" t="n"/>
-      <c r="I58" s="718" t="n"/>
-      <c r="J58" s="718" t="n"/>
-      <c r="K58" s="718" t="n"/>
-      <c r="L58" s="718" t="n"/>
-      <c r="M58" s="718" t="n"/>
-      <c r="N58" s="718" t="n"/>
-      <c r="O58" s="718" t="n"/>
-      <c r="P58" s="718" t="n"/>
-      <c r="Q58" s="718" t="n"/>
-      <c r="R58" s="718" t="n"/>
-      <c r="S58" s="718" t="n"/>
-      <c r="T58" s="718" t="n"/>
-      <c r="U58" s="718" t="n"/>
-      <c r="V58" s="718" t="n"/>
-      <c r="W58" s="718" t="n"/>
-      <c r="X58" s="718" t="n"/>
-      <c r="Y58" s="718" t="n"/>
-      <c r="Z58" s="718" t="n"/>
-      <c r="AA58" s="718" t="n"/>
-      <c r="AB58" s="718" t="n"/>
-      <c r="AC58" s="718" t="n"/>
-      <c r="AD58" s="718" t="n"/>
-      <c r="AE58" s="718" t="n"/>
-    </row>
-    <row r="59" ht="48" customHeight="1">
-      <c r="A59" s="763" t="n"/>
-      <c r="B59" s="772" t="inlineStr">
-        <is>
-          <t>Клиенту продают мин. пакет («пока не понятно»). Кто ведёт дальше? Когда собирать ОС перед продлением?</t>
-        </is>
-      </c>
-      <c r="C59" s="773" t="n"/>
-      <c r="D59" s="773" t="inlineStr">
-        <is>
-          <t>По логике — ЦКС. Нужен калькулятор — Вика с Машей обсуждали накануне лектория.</t>
-        </is>
-      </c>
-      <c r="E59" s="773" t="n"/>
-      <c r="F59" s="773" t="n"/>
-      <c r="G59" s="773" t="n"/>
-      <c r="H59" s="718" t="n"/>
-      <c r="I59" s="718" t="n"/>
-      <c r="J59" s="718" t="n"/>
-      <c r="K59" s="718" t="n"/>
-      <c r="L59" s="718" t="n"/>
-      <c r="M59" s="718" t="n"/>
-      <c r="N59" s="718" t="n"/>
-      <c r="O59" s="718" t="n"/>
-      <c r="P59" s="718" t="n"/>
-      <c r="Q59" s="718" t="n"/>
-      <c r="R59" s="718" t="n"/>
-      <c r="S59" s="718" t="n"/>
-      <c r="T59" s="718" t="n"/>
-      <c r="U59" s="718" t="n"/>
-      <c r="V59" s="718" t="n"/>
-      <c r="W59" s="718" t="n"/>
-      <c r="X59" s="718" t="n"/>
-      <c r="Y59" s="718" t="n"/>
-      <c r="Z59" s="718" t="n"/>
-      <c r="AA59" s="718" t="n"/>
-      <c r="AB59" s="718" t="n"/>
-      <c r="AC59" s="718" t="n"/>
-      <c r="AD59" s="718" t="n"/>
-      <c r="AE59" s="718" t="n"/>
-    </row>
-    <row r="60" ht="48" customHeight="1">
-      <c r="A60" s="764" t="n"/>
-      <c r="B60" s="772" t="inlineStr">
-        <is>
-          <t>ЦКС категоризирует клиента по титулам / УАТ и вовремя пополняет баланс.</t>
-        </is>
-      </c>
-      <c r="C60" s="773" t="n"/>
-      <c r="D60" s="773" t="inlineStr">
-        <is>
-          <t>Ожидание зафиксировано как рабочий процесс.</t>
-        </is>
-      </c>
-      <c r="E60" s="773" t="n"/>
-      <c r="F60" s="773" t="n"/>
-      <c r="G60" s="773" t="n"/>
-      <c r="H60" s="718" t="n"/>
-      <c r="I60" s="718" t="n"/>
-      <c r="J60" s="718" t="n"/>
-      <c r="K60" s="718" t="n"/>
-      <c r="L60" s="718" t="n"/>
-      <c r="M60" s="718" t="n"/>
-      <c r="N60" s="718" t="n"/>
-      <c r="O60" s="718" t="n"/>
-      <c r="P60" s="718" t="n"/>
-      <c r="Q60" s="718" t="n"/>
-      <c r="R60" s="718" t="n"/>
-      <c r="S60" s="718" t="n"/>
-      <c r="T60" s="718" t="n"/>
-      <c r="U60" s="718" t="n"/>
-      <c r="V60" s="718" t="n"/>
-      <c r="W60" s="718" t="n"/>
-      <c r="X60" s="718" t="n"/>
-      <c r="Y60" s="718" t="n"/>
-      <c r="Z60" s="718" t="n"/>
-      <c r="AA60" s="718" t="n"/>
-      <c r="AB60" s="718" t="n"/>
-      <c r="AC60" s="718" t="n"/>
-      <c r="AD60" s="718" t="n"/>
-      <c r="AE60" s="718" t="n"/>
-    </row>
-    <row r="61" ht="48" customHeight="1">
-      <c r="A61" s="774" t="inlineStr">
-        <is>
-          <t>Тандем
-и обзвоны</t>
-        </is>
-      </c>
-      <c r="B61" s="775" t="inlineStr">
-        <is>
-          <t>Рассылка: «проверьте контрагента и впишите в тандем».</t>
-        </is>
-      </c>
-      <c r="C61" s="776" t="n"/>
-      <c r="D61" s="752" t="inlineStr">
-        <is>
-          <t>Лиза — когда и какой текст.</t>
-        </is>
-      </c>
-      <c r="E61" s="776" t="n"/>
-      <c r="F61" s="776" t="n"/>
-      <c r="G61" s="776" t="n"/>
-      <c r="H61" s="718" t="n"/>
-      <c r="I61" s="718" t="n"/>
-      <c r="J61" s="718" t="n"/>
-      <c r="K61" s="718" t="n"/>
-      <c r="L61" s="718" t="n"/>
-      <c r="M61" s="718" t="n"/>
-      <c r="N61" s="718" t="n"/>
-      <c r="O61" s="718" t="n"/>
-      <c r="P61" s="718" t="n"/>
-      <c r="Q61" s="718" t="n"/>
-      <c r="R61" s="718" t="n"/>
-      <c r="S61" s="718" t="n"/>
-      <c r="T61" s="718" t="n"/>
-      <c r="U61" s="718" t="n"/>
-      <c r="V61" s="718" t="n"/>
-      <c r="W61" s="718" t="n"/>
-      <c r="X61" s="718" t="n"/>
-      <c r="Y61" s="718" t="n"/>
-      <c r="Z61" s="718" t="n"/>
-      <c r="AA61" s="718" t="n"/>
-      <c r="AB61" s="718" t="n"/>
-      <c r="AC61" s="718" t="n"/>
-      <c r="AD61" s="718" t="n"/>
-      <c r="AE61" s="718" t="n"/>
-    </row>
-    <row r="62" ht="48" customHeight="1">
-      <c r="A62" s="763" t="n"/>
-      <c r="B62" s="775" t="inlineStr">
-        <is>
-          <t>Начать с крупных: прозвонить и предложить подключить контрагента в ЭПД ТАНДЕМ.</t>
-        </is>
-      </c>
-      <c r="C62" s="776" t="n"/>
-      <c r="D62" s="757" t="inlineStr">
-        <is>
-          <t>Крупные = от 2 000 титулов. Корп. клиенты покупали ЭПД даже в малом объёме.</t>
-        </is>
-      </c>
-      <c r="E62" s="776" t="n"/>
-      <c r="F62" s="776" t="n"/>
-      <c r="G62" s="776" t="n"/>
-      <c r="H62" s="718" t="n"/>
-      <c r="I62" s="718" t="n"/>
-      <c r="J62" s="718" t="n"/>
-      <c r="K62" s="718" t="n"/>
-      <c r="L62" s="718" t="n"/>
-      <c r="M62" s="718" t="n"/>
-      <c r="N62" s="718" t="n"/>
-      <c r="O62" s="718" t="n"/>
-      <c r="P62" s="718" t="n"/>
-      <c r="Q62" s="718" t="n"/>
-      <c r="R62" s="718" t="n"/>
-      <c r="S62" s="718" t="n"/>
-      <c r="T62" s="718" t="n"/>
-      <c r="U62" s="718" t="n"/>
-      <c r="V62" s="718" t="n"/>
-      <c r="W62" s="718" t="n"/>
-      <c r="X62" s="718" t="n"/>
-      <c r="Y62" s="718" t="n"/>
-      <c r="Z62" s="718" t="n"/>
-      <c r="AA62" s="718" t="n"/>
-      <c r="AB62" s="718" t="n"/>
-      <c r="AC62" s="718" t="n"/>
-      <c r="AD62" s="718" t="n"/>
-      <c r="AE62" s="718" t="n"/>
-    </row>
-    <row r="63" ht="48" customHeight="1">
-      <c r="A63" s="764" t="n"/>
-      <c r="B63" s="775" t="inlineStr">
-        <is>
-          <t>Обзвон подключённых: оценка удовлетворённости + проекты ЦАС (Доки).</t>
-        </is>
-      </c>
-      <c r="C63" s="776" t="n"/>
-      <c r="D63" s="752" t="inlineStr">
-        <is>
-          <t>Задача на Сашу Дворяк / Лазарчук — клиенты ЦАС.</t>
-        </is>
-      </c>
-      <c r="E63" s="776" t="n"/>
-      <c r="F63" s="776" t="n"/>
-      <c r="G63" s="776" t="n"/>
-      <c r="H63" s="718" t="n"/>
-      <c r="I63" s="718" t="n"/>
-      <c r="J63" s="718" t="n"/>
-      <c r="K63" s="718" t="n"/>
-      <c r="L63" s="718" t="n"/>
-      <c r="M63" s="718" t="n"/>
-      <c r="N63" s="718" t="n"/>
-      <c r="O63" s="718" t="n"/>
-      <c r="P63" s="718" t="n"/>
-      <c r="Q63" s="718" t="n"/>
-      <c r="R63" s="718" t="n"/>
-      <c r="S63" s="718" t="n"/>
-      <c r="T63" s="718" t="n"/>
-      <c r="U63" s="718" t="n"/>
-      <c r="V63" s="718" t="n"/>
-      <c r="W63" s="718" t="n"/>
-      <c r="X63" s="718" t="n"/>
-      <c r="Y63" s="718" t="n"/>
-      <c r="Z63" s="718" t="n"/>
-      <c r="AA63" s="718" t="n"/>
-      <c r="AB63" s="718" t="n"/>
-      <c r="AC63" s="718" t="n"/>
-      <c r="AD63" s="718" t="n"/>
-      <c r="AE63" s="718" t="n"/>
-    </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="777" t="inlineStr">
-        <is>
-          <t>Корп.
-сегмент</t>
-        </is>
-      </c>
-      <c r="B64" s="735" t="inlineStr">
-        <is>
-          <t>Почему клиенты сбытового офиса не переходят в ЭПД / уходят на СБИС?</t>
-        </is>
-      </c>
-      <c r="C64" s="778" t="n"/>
-      <c r="D64" s="752" t="inlineStr">
-        <is>
-          <t>Взять неуспешные сделки корп. сегмента и предложить Доки в 1-ю неделю сентября (Юлиана).</t>
-        </is>
-      </c>
-      <c r="E64" s="778" t="n"/>
-      <c r="F64" s="778" t="n"/>
-      <c r="G64" s="778" t="n"/>
-      <c r="H64" s="718" t="n"/>
-      <c r="I64" s="718" t="n"/>
-      <c r="J64" s="718" t="n"/>
-      <c r="K64" s="718" t="n"/>
-      <c r="L64" s="718" t="n"/>
-      <c r="M64" s="718" t="n"/>
-      <c r="N64" s="718" t="n"/>
-      <c r="O64" s="718" t="n"/>
-      <c r="P64" s="718" t="n"/>
-      <c r="Q64" s="718" t="n"/>
-      <c r="R64" s="718" t="n"/>
-      <c r="S64" s="718" t="n"/>
-      <c r="T64" s="718" t="n"/>
-      <c r="U64" s="718" t="n"/>
-      <c r="V64" s="718" t="n"/>
-      <c r="W64" s="718" t="n"/>
-      <c r="X64" s="718" t="n"/>
-      <c r="Y64" s="718" t="n"/>
-      <c r="Z64" s="718" t="n"/>
-      <c r="AA64" s="718" t="n"/>
-      <c r="AB64" s="718" t="n"/>
-      <c r="AC64" s="718" t="n"/>
-      <c r="AD64" s="718" t="n"/>
-      <c r="AE64" s="718" t="n"/>
-    </row>
-    <row r="65" ht="48" customHeight="1">
-      <c r="A65" s="764" t="n"/>
-      <c r="B65" s="735" t="inlineStr">
-        <is>
-          <t>Юля: предлагать всем бесплатно Доки (дубль) на 3 мес.; KPI менеджерам на сентябрь.</t>
-        </is>
-      </c>
-      <c r="C65" s="778" t="n"/>
-      <c r="D65" s="778" t="inlineStr">
-        <is>
-          <t>Зафиксировано как предложение.</t>
-        </is>
-      </c>
-      <c r="E65" s="778" t="n"/>
-      <c r="F65" s="778" t="n"/>
-      <c r="G65" s="778" t="n"/>
-      <c r="H65" s="718" t="n"/>
-      <c r="I65" s="718" t="n"/>
-      <c r="J65" s="718" t="n"/>
-      <c r="K65" s="718" t="n"/>
-      <c r="L65" s="718" t="n"/>
-      <c r="M65" s="718" t="n"/>
-      <c r="N65" s="718" t="n"/>
-      <c r="O65" s="718" t="n"/>
-      <c r="P65" s="718" t="n"/>
-      <c r="Q65" s="718" t="n"/>
-      <c r="R65" s="718" t="n"/>
-      <c r="S65" s="718" t="n"/>
-      <c r="T65" s="718" t="n"/>
-      <c r="U65" s="718" t="n"/>
-      <c r="V65" s="718" t="n"/>
-      <c r="W65" s="718" t="n"/>
-      <c r="X65" s="718" t="n"/>
-      <c r="Y65" s="718" t="n"/>
-      <c r="Z65" s="718" t="n"/>
-      <c r="AA65" s="718" t="n"/>
-      <c r="AB65" s="718" t="n"/>
-      <c r="AC65" s="718" t="n"/>
-      <c r="AD65" s="718" t="n"/>
-      <c r="AE65" s="718" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="718" t="n"/>
-      <c r="B66" s="718" t="n"/>
-      <c r="C66" s="718" t="n"/>
-      <c r="D66" s="718" t="n"/>
-      <c r="E66" s="718" t="n"/>
-      <c r="F66" s="718" t="n"/>
-      <c r="G66" s="718" t="n"/>
-      <c r="H66" s="718" t="n"/>
-      <c r="I66" s="718" t="n"/>
-      <c r="J66" s="718" t="n"/>
-      <c r="K66" s="718" t="n"/>
-      <c r="L66" s="718" t="n"/>
-      <c r="M66" s="718" t="n"/>
-      <c r="N66" s="718" t="n"/>
-      <c r="O66" s="718" t="n"/>
-      <c r="P66" s="718" t="n"/>
-      <c r="Q66" s="718" t="n"/>
-      <c r="R66" s="718" t="n"/>
-      <c r="S66" s="718" t="n"/>
-      <c r="T66" s="718" t="n"/>
-      <c r="U66" s="718" t="n"/>
-      <c r="V66" s="718" t="n"/>
-      <c r="W66" s="718" t="n"/>
-      <c r="X66" s="718" t="n"/>
-      <c r="Y66" s="718" t="n"/>
-      <c r="Z66" s="718" t="n"/>
-      <c r="AA66" s="718" t="n"/>
-      <c r="AB66" s="718" t="n"/>
-      <c r="AC66" s="718" t="n"/>
-      <c r="AD66" s="718" t="n"/>
-      <c r="AE66" s="718" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="731" t="inlineStr">
-        <is>
-          <t>Легенда:  оранжевый блок «Решения» = поставленные задачи  ·  жёлтые ячейки = ввод факта  ·  зелёный статус = выполнено/принято  ·  блоки слева = темы обсуждения</t>
-        </is>
-      </c>
-      <c r="H67" s="718" t="n"/>
-      <c r="I67" s="718" t="n"/>
-      <c r="J67" s="718" t="n"/>
-      <c r="K67" s="718" t="n"/>
-      <c r="L67" s="718" t="n"/>
-      <c r="M67" s="718" t="n"/>
-      <c r="N67" s="718" t="n"/>
-      <c r="O67" s="718" t="n"/>
-      <c r="P67" s="718" t="n"/>
-      <c r="Q67" s="718" t="n"/>
-      <c r="R67" s="718" t="n"/>
-      <c r="S67" s="718" t="n"/>
-      <c r="T67" s="718" t="n"/>
-      <c r="U67" s="718" t="n"/>
-      <c r="V67" s="718" t="n"/>
-      <c r="W67" s="718" t="n"/>
-      <c r="X67" s="718" t="n"/>
-      <c r="Y67" s="718" t="n"/>
-      <c r="Z67" s="718" t="n"/>
-      <c r="AA67" s="718" t="n"/>
-      <c r="AB67" s="718" t="n"/>
-      <c r="AC67" s="718" t="n"/>
-      <c r="AD67" s="718" t="n"/>
-      <c r="AE67" s="718" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="718" t="n"/>
-      <c r="B68" s="718" t="n"/>
-      <c r="C68" s="718" t="n"/>
-      <c r="D68" s="718" t="n"/>
-      <c r="E68" s="718" t="n"/>
-      <c r="F68" s="718" t="n"/>
-      <c r="G68" s="718" t="n"/>
-      <c r="H68" s="718" t="n"/>
-      <c r="I68" s="718" t="n"/>
-      <c r="J68" s="718" t="n"/>
-      <c r="K68" s="718" t="n"/>
-      <c r="L68" s="718" t="n"/>
-      <c r="M68" s="718" t="n"/>
-      <c r="N68" s="718" t="n"/>
-      <c r="O68" s="718" t="n"/>
-      <c r="P68" s="718" t="n"/>
-      <c r="Q68" s="718" t="n"/>
-      <c r="R68" s="718" t="n"/>
-      <c r="S68" s="718" t="n"/>
-      <c r="T68" s="718" t="n"/>
-      <c r="U68" s="718" t="n"/>
-      <c r="V68" s="718" t="n"/>
-      <c r="W68" s="718" t="n"/>
-      <c r="X68" s="718" t="n"/>
-      <c r="Y68" s="718" t="n"/>
-      <c r="Z68" s="718" t="n"/>
-      <c r="AA68" s="718" t="n"/>
-      <c r="AB68" s="718" t="n"/>
-      <c r="AC68" s="718" t="n"/>
-      <c r="AD68" s="718" t="n"/>
-      <c r="AE68" s="718" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="718" t="n"/>
-      <c r="B69" s="718" t="n"/>
-      <c r="C69" s="718" t="n"/>
-      <c r="D69" s="718" t="n"/>
-      <c r="E69" s="718" t="n"/>
-      <c r="F69" s="718" t="n"/>
-      <c r="G69" s="718" t="n"/>
-      <c r="H69" s="718" t="n"/>
-      <c r="I69" s="718" t="n"/>
-      <c r="J69" s="718" t="n"/>
-      <c r="K69" s="718" t="n"/>
-      <c r="L69" s="718" t="n"/>
-      <c r="M69" s="718" t="n"/>
-      <c r="N69" s="718" t="n"/>
-      <c r="O69" s="718" t="n"/>
-      <c r="P69" s="718" t="n"/>
-      <c r="Q69" s="718" t="n"/>
-      <c r="R69" s="718" t="n"/>
-      <c r="S69" s="718" t="n"/>
-      <c r="T69" s="718" t="n"/>
-      <c r="U69" s="718" t="n"/>
-      <c r="V69" s="718" t="n"/>
-      <c r="W69" s="718" t="n"/>
-      <c r="X69" s="718" t="n"/>
-      <c r="Y69" s="718" t="n"/>
-      <c r="Z69" s="718" t="n"/>
-      <c r="AA69" s="718" t="n"/>
-      <c r="AB69" s="718" t="n"/>
-      <c r="AC69" s="718" t="n"/>
-      <c r="AD69" s="718" t="n"/>
-      <c r="AE69" s="718" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="718" t="n"/>
-      <c r="B70" s="718" t="n"/>
-      <c r="C70" s="718" t="n"/>
-      <c r="D70" s="718" t="n"/>
-      <c r="E70" s="718" t="n"/>
-      <c r="F70" s="718" t="n"/>
-      <c r="G70" s="718" t="n"/>
-      <c r="H70" s="718" t="n"/>
-      <c r="I70" s="718" t="n"/>
-      <c r="J70" s="718" t="n"/>
-      <c r="K70" s="718" t="n"/>
-      <c r="L70" s="718" t="n"/>
-      <c r="M70" s="718" t="n"/>
-      <c r="N70" s="718" t="n"/>
-      <c r="O70" s="718" t="n"/>
-      <c r="P70" s="718" t="n"/>
-      <c r="Q70" s="718" t="n"/>
-      <c r="R70" s="718" t="n"/>
-      <c r="S70" s="718" t="n"/>
-      <c r="T70" s="718" t="n"/>
-      <c r="U70" s="718" t="n"/>
-      <c r="V70" s="718" t="n"/>
-      <c r="W70" s="718" t="n"/>
-      <c r="X70" s="718" t="n"/>
-      <c r="Y70" s="718" t="n"/>
-      <c r="Z70" s="718" t="n"/>
-      <c r="AA70" s="718" t="n"/>
-      <c r="AB70" s="718" t="n"/>
-      <c r="AC70" s="718" t="n"/>
-      <c r="AD70" s="718" t="n"/>
-      <c r="AE70" s="718" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="718" t="n"/>
-      <c r="B71" s="718" t="n"/>
-      <c r="C71" s="718" t="n"/>
-      <c r="D71" s="718" t="n"/>
-      <c r="E71" s="718" t="n"/>
-      <c r="F71" s="718" t="n"/>
-      <c r="G71" s="718" t="n"/>
-      <c r="H71" s="718" t="n"/>
-      <c r="I71" s="718" t="n"/>
-      <c r="J71" s="718" t="n"/>
-      <c r="K71" s="718" t="n"/>
-      <c r="L71" s="718" t="n"/>
-      <c r="M71" s="718" t="n"/>
-      <c r="N71" s="718" t="n"/>
-      <c r="O71" s="718" t="n"/>
-      <c r="P71" s="718" t="n"/>
-      <c r="Q71" s="718" t="n"/>
-      <c r="R71" s="718" t="n"/>
-      <c r="S71" s="718" t="n"/>
-      <c r="T71" s="718" t="n"/>
-      <c r="U71" s="718" t="n"/>
-      <c r="V71" s="718" t="n"/>
-      <c r="W71" s="718" t="n"/>
-      <c r="X71" s="718" t="n"/>
-      <c r="Y71" s="718" t="n"/>
-      <c r="Z71" s="718" t="n"/>
-      <c r="AA71" s="718" t="n"/>
-      <c r="AB71" s="718" t="n"/>
-      <c r="AC71" s="718" t="n"/>
-      <c r="AD71" s="718" t="n"/>
-      <c r="AE71" s="718" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="718" t="n"/>
-      <c r="B72" s="718" t="n"/>
-      <c r="C72" s="718" t="n"/>
-      <c r="D72" s="718" t="n"/>
-      <c r="E72" s="718" t="n"/>
-      <c r="F72" s="718" t="n"/>
-      <c r="G72" s="718" t="n"/>
-      <c r="H72" s="718" t="n"/>
-      <c r="I72" s="718" t="n"/>
-      <c r="J72" s="718" t="n"/>
-      <c r="K72" s="718" t="n"/>
-      <c r="L72" s="718" t="n"/>
-      <c r="M72" s="718" t="n"/>
-      <c r="N72" s="718" t="n"/>
-      <c r="O72" s="718" t="n"/>
-      <c r="P72" s="718" t="n"/>
-      <c r="Q72" s="718" t="n"/>
-      <c r="R72" s="718" t="n"/>
-      <c r="S72" s="718" t="n"/>
-      <c r="T72" s="718" t="n"/>
-      <c r="U72" s="718" t="n"/>
-      <c r="V72" s="718" t="n"/>
-      <c r="W72" s="718" t="n"/>
-      <c r="X72" s="718" t="n"/>
-      <c r="Y72" s="718" t="n"/>
-      <c r="Z72" s="718" t="n"/>
-      <c r="AA72" s="718" t="n"/>
-      <c r="AB72" s="718" t="n"/>
-      <c r="AC72" s="718" t="n"/>
-      <c r="AD72" s="718" t="n"/>
-      <c r="AE72" s="718" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="718" t="n"/>
-      <c r="B73" s="718" t="n"/>
-      <c r="C73" s="718" t="n"/>
-      <c r="D73" s="718" t="n"/>
-      <c r="E73" s="718" t="n"/>
-      <c r="F73" s="718" t="n"/>
-      <c r="G73" s="718" t="n"/>
-      <c r="H73" s="718" t="n"/>
-      <c r="I73" s="718" t="n"/>
-      <c r="J73" s="718" t="n"/>
-      <c r="K73" s="718" t="n"/>
-      <c r="L73" s="718" t="n"/>
-      <c r="M73" s="718" t="n"/>
-      <c r="N73" s="718" t="n"/>
-      <c r="O73" s="718" t="n"/>
-      <c r="P73" s="718" t="n"/>
-      <c r="Q73" s="718" t="n"/>
-      <c r="R73" s="718" t="n"/>
-      <c r="S73" s="718" t="n"/>
-      <c r="T73" s="718" t="n"/>
-      <c r="U73" s="718" t="n"/>
-      <c r="V73" s="718" t="n"/>
-      <c r="W73" s="718" t="n"/>
-      <c r="X73" s="718" t="n"/>
-      <c r="Y73" s="718" t="n"/>
-      <c r="Z73" s="718" t="n"/>
-      <c r="AA73" s="718" t="n"/>
-      <c r="AB73" s="718" t="n"/>
-      <c r="AC73" s="718" t="n"/>
-      <c r="AD73" s="718" t="n"/>
-      <c r="AE73" s="718" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="718" t="n"/>
-      <c r="B74" s="718" t="n"/>
-      <c r="C74" s="718" t="n"/>
-      <c r="D74" s="718" t="n"/>
-      <c r="E74" s="718" t="n"/>
-      <c r="F74" s="718" t="n"/>
-      <c r="G74" s="718" t="n"/>
-      <c r="H74" s="718" t="n"/>
-      <c r="I74" s="718" t="n"/>
-      <c r="J74" s="718" t="n"/>
-      <c r="K74" s="718" t="n"/>
-      <c r="L74" s="718" t="n"/>
-      <c r="M74" s="718" t="n"/>
-      <c r="N74" s="718" t="n"/>
-      <c r="O74" s="718" t="n"/>
-      <c r="P74" s="718" t="n"/>
-      <c r="Q74" s="718" t="n"/>
-      <c r="R74" s="718" t="n"/>
-      <c r="S74" s="718" t="n"/>
-      <c r="T74" s="718" t="n"/>
-      <c r="U74" s="718" t="n"/>
-      <c r="V74" s="718" t="n"/>
-      <c r="W74" s="718" t="n"/>
-      <c r="X74" s="718" t="n"/>
-      <c r="Y74" s="718" t="n"/>
-      <c r="Z74" s="718" t="n"/>
-      <c r="AA74" s="718" t="n"/>
-      <c r="AB74" s="718" t="n"/>
-      <c r="AC74" s="718" t="n"/>
-      <c r="AD74" s="718" t="n"/>
-      <c r="AE74" s="718" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="718" t="n"/>
-      <c r="B75" s="718" t="n"/>
-      <c r="C75" s="718" t="n"/>
-      <c r="D75" s="718" t="n"/>
-      <c r="E75" s="718" t="n"/>
-      <c r="F75" s="718" t="n"/>
-      <c r="G75" s="718" t="n"/>
-      <c r="H75" s="718" t="n"/>
-      <c r="I75" s="718" t="n"/>
-      <c r="J75" s="718" t="n"/>
-      <c r="K75" s="718" t="n"/>
-      <c r="L75" s="718" t="n"/>
-      <c r="M75" s="718" t="n"/>
-      <c r="N75" s="718" t="n"/>
-      <c r="O75" s="718" t="n"/>
-      <c r="P75" s="718" t="n"/>
-      <c r="Q75" s="718" t="n"/>
-      <c r="R75" s="718" t="n"/>
-      <c r="S75" s="718" t="n"/>
-      <c r="T75" s="718" t="n"/>
-      <c r="U75" s="718" t="n"/>
-      <c r="V75" s="718" t="n"/>
-      <c r="W75" s="718" t="n"/>
-      <c r="X75" s="718" t="n"/>
-      <c r="Y75" s="718" t="n"/>
-      <c r="Z75" s="718" t="n"/>
-      <c r="AA75" s="718" t="n"/>
-      <c r="AB75" s="718" t="n"/>
-      <c r="AC75" s="718" t="n"/>
-      <c r="AD75" s="718" t="n"/>
-      <c r="AE75" s="718" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="718" t="n"/>
-      <c r="B76" s="718" t="n"/>
-      <c r="C76" s="718" t="n"/>
-      <c r="D76" s="718" t="n"/>
-      <c r="E76" s="718" t="n"/>
-      <c r="F76" s="718" t="n"/>
-      <c r="G76" s="718" t="n"/>
-      <c r="H76" s="718" t="n"/>
-      <c r="I76" s="718" t="n"/>
-      <c r="J76" s="718" t="n"/>
-      <c r="K76" s="718" t="n"/>
-      <c r="L76" s="718" t="n"/>
-      <c r="M76" s="718" t="n"/>
-      <c r="N76" s="718" t="n"/>
-      <c r="O76" s="718" t="n"/>
-      <c r="P76" s="718" t="n"/>
-      <c r="Q76" s="718" t="n"/>
-      <c r="R76" s="718" t="n"/>
-      <c r="S76" s="718" t="n"/>
-      <c r="T76" s="718" t="n"/>
-      <c r="U76" s="718" t="n"/>
-      <c r="V76" s="718" t="n"/>
-      <c r="W76" s="718" t="n"/>
-      <c r="X76" s="718" t="n"/>
-      <c r="Y76" s="718" t="n"/>
-      <c r="Z76" s="718" t="n"/>
-      <c r="AA76" s="718" t="n"/>
-      <c r="AB76" s="718" t="n"/>
-      <c r="AC76" s="718" t="n"/>
-      <c r="AD76" s="718" t="n"/>
-      <c r="AE76" s="718" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="718" t="n"/>
-      <c r="B77" s="718" t="n"/>
-      <c r="C77" s="718" t="n"/>
-      <c r="D77" s="718" t="n"/>
-      <c r="E77" s="718" t="n"/>
-      <c r="F77" s="718" t="n"/>
-      <c r="G77" s="718" t="n"/>
-      <c r="H77" s="718" t="n"/>
-      <c r="I77" s="718" t="n"/>
-      <c r="J77" s="718" t="n"/>
-      <c r="K77" s="718" t="n"/>
-      <c r="L77" s="718" t="n"/>
-      <c r="M77" s="718" t="n"/>
-      <c r="N77" s="718" t="n"/>
-      <c r="O77" s="718" t="n"/>
-      <c r="P77" s="718" t="n"/>
-      <c r="Q77" s="718" t="n"/>
-      <c r="R77" s="718" t="n"/>
-      <c r="S77" s="718" t="n"/>
-      <c r="T77" s="718" t="n"/>
-      <c r="U77" s="718" t="n"/>
-      <c r="V77" s="718" t="n"/>
-      <c r="W77" s="718" t="n"/>
-      <c r="X77" s="718" t="n"/>
-      <c r="Y77" s="718" t="n"/>
-      <c r="Z77" s="718" t="n"/>
-      <c r="AA77" s="718" t="n"/>
-      <c r="AB77" s="718" t="n"/>
-      <c r="AC77" s="718" t="n"/>
-      <c r="AD77" s="718" t="n"/>
-      <c r="AE77" s="718" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="95">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F25:G25"/>
-    <mergeCell ref="D55:G55"/>
-    <mergeCell ref="D59:G59"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="D60:G60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="F23:G23"/>
-    <mergeCell ref="A53:A56"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="A50:A52"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D48:G48"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="D56:G56"/>
-    <mergeCell ref="D58:G58"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D64:G64"/>
-    <mergeCell ref="D51:G51"/>
-    <mergeCell ref="I14:K14"/>
-    <mergeCell ref="D50:G50"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="F42:G42"/>
-    <mergeCell ref="I4:K4"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="F31:G31"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="D61:G61"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D47:G47"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="D63:G63"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="D65:G65"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D49:G49"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="F40:G40"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D54:G54"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F41:G41"/>
-    <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F38:G38"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="D57:G57"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="F27:G27"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="F37:G37"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="F44:G44"/>
-  </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="E22:E28 E32:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Статус" error="Выберите статус из списка" type="list">
-      <formula1>"в работе,выполнено,принято,взял на себя,отложено"</formula1>
-    </dataValidation>
-    <dataValidation sqref="E22:E28 E32:E44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Статус" error="Выберите статус из списка" type="list">
-      <formula1>"в работе,выполнено,принято,взял на себя,отложено"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L57"/>
+  <dimension ref="A1:AE57"/>
   <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="8.762" customWidth="1" min="1" max="1"/>
@@ -7355,13 +5206,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="10.35" customHeight="1">
-      <c r="A1" s="779" t="n"/>
-      <c r="B1" s="780" t="n"/>
-      <c r="C1" s="780" t="n"/>
-      <c r="D1" s="780" t="n"/>
-      <c r="E1" s="780" t="n"/>
-      <c r="F1" s="780" t="n"/>
-      <c r="G1" s="781" t="n"/>
+      <c r="A1" s="731" t="n"/>
+      <c r="B1" s="732" t="n"/>
+      <c r="C1" s="732" t="n"/>
+      <c r="D1" s="732" t="n"/>
+      <c r="E1" s="732" t="n"/>
+      <c r="F1" s="732" t="n"/>
+      <c r="G1" s="733" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="588" t="n"/>
@@ -7378,12 +5229,12 @@
           <t>Показатели рекламной кампании</t>
         </is>
       </c>
-      <c r="B3" s="782" t="n"/>
-      <c r="C3" s="782" t="n"/>
-      <c r="D3" s="782" t="n"/>
-      <c r="E3" s="782" t="n"/>
-      <c r="F3" s="782" t="n"/>
-      <c r="G3" s="783" t="n"/>
+      <c r="B3" s="717" t="n"/>
+      <c r="C3" s="717" t="n"/>
+      <c r="D3" s="717" t="n"/>
+      <c r="E3" s="717" t="n"/>
+      <c r="F3" s="717" t="n"/>
+      <c r="G3" s="718" t="n"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="590" t="inlineStr">
@@ -7486,7 +5337,7 @@
           <t>Комментарий</t>
         </is>
       </c>
-      <c r="G6" s="783" t="n"/>
+      <c r="G6" s="718" t="n"/>
       <c r="H6" s="481" t="n"/>
       <c r="I6" s="481" t="n"/>
       <c r="J6" s="481" t="n"/>
@@ -7520,7 +5371,7 @@
           <t>клиента устроила стоимость  взял время подумать , ЭПД 600, сумма 3600</t>
         </is>
       </c>
-      <c r="G7" s="783" t="n"/>
+      <c r="G7" s="718" t="n"/>
       <c r="H7" s="492" t="n"/>
       <c r="I7" s="492" t="n"/>
       <c r="J7" s="482" t="n"/>
@@ -7554,7 +5405,7 @@
           <t xml:space="preserve">клиент отвалился после консультации , далее не вышел на связь </t>
         </is>
       </c>
-      <c r="G8" s="783" t="n"/>
+      <c r="G8" s="718" t="n"/>
       <c r="H8" s="492" t="n"/>
       <c r="I8" s="492" t="n"/>
       <c r="J8" s="482" t="n"/>
@@ -7588,7 +5439,7 @@
           <t>клиент обслуживается у другого партнера, но рассматривает все предложения, сегодня после обеда даст ответ 5000</t>
         </is>
       </c>
-      <c r="G9" s="783" t="n"/>
+      <c r="G9" s="718" t="n"/>
       <c r="H9" s="492" t="n"/>
       <c r="I9" s="492" t="n"/>
       <c r="J9" s="482" t="n"/>
@@ -7602,7 +5453,7 @@
       <c r="D10" s="599" t="n"/>
       <c r="E10" s="594" t="n"/>
       <c r="F10" s="597" t="n"/>
-      <c r="G10" s="783" t="n"/>
+      <c r="G10" s="718" t="n"/>
       <c r="H10" s="492" t="n"/>
       <c r="I10" s="492" t="n"/>
       <c r="J10" s="482" t="n"/>
@@ -7616,7 +5467,7 @@
       <c r="D11" s="599" t="n"/>
       <c r="E11" s="594" t="n"/>
       <c r="F11" s="597" t="n"/>
-      <c r="G11" s="783" t="n"/>
+      <c r="G11" s="718" t="n"/>
       <c r="H11" s="492" t="n"/>
       <c r="I11" s="492" t="n"/>
       <c r="J11" s="482" t="n"/>
@@ -7630,7 +5481,7 @@
       <c r="D12" s="599" t="n"/>
       <c r="E12" s="594" t="n"/>
       <c r="F12" s="597" t="n"/>
-      <c r="G12" s="783" t="n"/>
+      <c r="G12" s="718" t="n"/>
       <c r="H12" s="492" t="n"/>
       <c r="I12" s="492" t="n"/>
       <c r="J12" s="482" t="n"/>
@@ -7644,7 +5495,7 @@
       <c r="D13" s="599" t="n"/>
       <c r="E13" s="594" t="n"/>
       <c r="F13" s="597" t="n"/>
-      <c r="G13" s="783" t="n"/>
+      <c r="G13" s="718" t="n"/>
       <c r="H13" s="492" t="n"/>
       <c r="I13" s="492" t="n"/>
       <c r="J13" s="482" t="n"/>
@@ -7658,7 +5509,7 @@
       <c r="D14" s="599" t="n"/>
       <c r="E14" s="594" t="n"/>
       <c r="F14" s="597" t="n"/>
-      <c r="G14" s="783" t="n"/>
+      <c r="G14" s="718" t="n"/>
       <c r="H14" s="492" t="n"/>
       <c r="I14" s="492" t="n"/>
       <c r="J14" s="482" t="n"/>
@@ -7672,7 +5523,7 @@
       <c r="D15" s="599" t="n"/>
       <c r="E15" s="594" t="n"/>
       <c r="F15" s="597" t="n"/>
-      <c r="G15" s="783" t="n"/>
+      <c r="G15" s="718" t="n"/>
       <c r="H15" s="492" t="n"/>
       <c r="I15" s="492" t="n"/>
       <c r="J15" s="482" t="n"/>
@@ -7686,7 +5537,7 @@
       <c r="D16" s="602" t="n"/>
       <c r="E16" s="594" t="n"/>
       <c r="F16" s="597" t="n"/>
-      <c r="G16" s="783" t="n"/>
+      <c r="G16" s="718" t="n"/>
       <c r="H16" s="492" t="n"/>
       <c r="I16" s="492" t="n"/>
       <c r="J16" s="482" t="n"/>
@@ -7700,7 +5551,7 @@
       <c r="D17" s="604" t="n"/>
       <c r="E17" s="603" t="n"/>
       <c r="F17" s="597" t="n"/>
-      <c r="G17" s="783" t="n"/>
+      <c r="G17" s="718" t="n"/>
       <c r="H17" s="492" t="n"/>
       <c r="I17" s="492" t="n"/>
       <c r="J17" s="482" t="n"/>
@@ -7714,7 +5565,7 @@
       <c r="D18" s="505" t="n"/>
       <c r="E18" s="508" t="n"/>
       <c r="F18" s="597" t="n"/>
-      <c r="G18" s="783" t="n"/>
+      <c r="G18" s="718" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="110" t="n"/>
@@ -7723,7 +5574,7 @@
       <c r="D19" s="184" t="n"/>
       <c r="E19" s="113" t="n"/>
       <c r="F19" s="597" t="n"/>
-      <c r="G19" s="783" t="n"/>
+      <c r="G19" s="718" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="605" t="inlineStr">
@@ -7731,12 +5582,12 @@
           <t>1. Мониторинг предыдущих решений:</t>
         </is>
       </c>
-      <c r="B20" s="782" t="n"/>
-      <c r="C20" s="782" t="n"/>
-      <c r="D20" s="782" t="n"/>
-      <c r="E20" s="782" t="n"/>
-      <c r="F20" s="782" t="n"/>
-      <c r="G20" s="783" t="n"/>
+      <c r="B20" s="717" t="n"/>
+      <c r="C20" s="717" t="n"/>
+      <c r="D20" s="717" t="n"/>
+      <c r="E20" s="717" t="n"/>
+      <c r="F20" s="717" t="n"/>
+      <c r="G20" s="718" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="590" t="inlineStr">
@@ -7769,7 +5620,7 @@
           <t>Комментарии. Выводы</t>
         </is>
       </c>
-      <c r="G21" s="783" t="n"/>
+      <c r="G21" s="718" t="n"/>
     </row>
     <row r="22" ht="53.05" customHeight="1">
       <c r="A22" s="606" t="n"/>
@@ -7798,10 +5649,10 @@
           <t>все ок, принято</t>
         </is>
       </c>
-      <c r="G22" s="783" t="n"/>
+      <c r="G22" s="718" t="n"/>
     </row>
     <row r="23" ht="74.05" customHeight="1">
-      <c r="A23" s="784" t="n">
+      <c r="A23" s="719" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="629" t="inlineStr">
@@ -7829,10 +5680,10 @@
           <t xml:space="preserve">Корнева А. 13.08 : Поговорила  с ЦСВ. Клиентов распределяет Юля Ситникова. В августе таких клиентов не было, все клиенты , что пришли уже были с оформленным сервисом. На будущее решили так: если клиент действующий , то передача менеджеру ЦКС, если клиент без договора то в ЦП. </t>
         </is>
       </c>
-      <c r="G23" s="783" t="n"/>
+      <c r="G23" s="718" t="n"/>
     </row>
     <row r="24" ht="58.25" customHeight="1">
-      <c r="A24" s="785" t="n">
+      <c r="A24" s="720" t="n">
         <v>2</v>
       </c>
       <c r="B24" s="165" t="inlineStr">
@@ -7860,10 +5711,10 @@
           <t>учесть требования вендора, 20.08 обсуждаем ОС. Продлила срок до следующей встречи -27.08</t>
         </is>
       </c>
-      <c r="G24" s="783" t="n"/>
+      <c r="G24" s="718" t="n"/>
     </row>
     <row r="25" ht="34.55" customHeight="1">
-      <c r="A25" s="784" t="n">
+      <c r="A25" s="719" t="n">
         <v>3</v>
       </c>
       <c r="B25" s="618" t="inlineStr">
@@ -7891,10 +5742,10 @@
           <t xml:space="preserve">Список собранный у Юли Степановой по всем МПП ЦКС </t>
         </is>
       </c>
-      <c r="G25" s="783" t="n"/>
+      <c r="G25" s="718" t="n"/>
     </row>
     <row r="26" ht="38.45" customHeight="1">
-      <c r="A26" s="786" t="n">
+      <c r="A26" s="721" t="n">
         <v>4</v>
       </c>
       <c r="B26" s="622" t="inlineStr">
@@ -7922,10 +5773,10 @@
           <t xml:space="preserve">база находится в работе у ТМ , на этой неделе планируют закончить обзвон </t>
         </is>
       </c>
-      <c r="G26" s="783" t="n"/>
+      <c r="G26" s="718" t="n"/>
     </row>
     <row r="27" ht="43.4" customHeight="1">
-      <c r="A27" s="784" t="n">
+      <c r="A27" s="719" t="n">
         <v>5</v>
       </c>
       <c r="B27" s="618" t="inlineStr">
@@ -7949,10 +5800,10 @@
         </is>
       </c>
       <c r="F27" s="620" t="n"/>
-      <c r="G27" s="783" t="n"/>
+      <c r="G27" s="718" t="n"/>
     </row>
     <row r="28" ht="26.95" customHeight="1">
-      <c r="A28" s="786" t="n">
+      <c r="A28" s="721" t="n">
         <v>6</v>
       </c>
       <c r="B28" s="622" t="inlineStr">
@@ -7976,7 +5827,7 @@
         </is>
       </c>
       <c r="F28" s="617" t="n"/>
-      <c r="G28" s="783" t="n"/>
+      <c r="G28" s="718" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="115" t="n"/>
@@ -7985,7 +5836,7 @@
       <c r="D29" s="115" t="n"/>
       <c r="E29" s="624" t="n"/>
       <c r="F29" s="625" t="n"/>
-      <c r="G29" s="783" t="n"/>
+      <c r="G29" s="718" t="n"/>
     </row>
     <row r="30" ht="16.95" customHeight="1">
       <c r="A30" s="502" t="n"/>
@@ -7994,7 +5845,7 @@
       <c r="D30" s="505" t="n"/>
       <c r="E30" s="508" t="n"/>
       <c r="F30" s="507" t="n"/>
-      <c r="G30" s="783" t="n"/>
+      <c r="G30" s="718" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="134" t="n"/>
@@ -8003,7 +5854,7 @@
       <c r="D31" s="135" t="n"/>
       <c r="E31" s="624" t="n"/>
       <c r="F31" s="86" t="n"/>
-      <c r="G31" s="783" t="n"/>
+      <c r="G31" s="718" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="589" t="inlineStr">
@@ -8011,12 +5862,12 @@
           <t>2. Решения текущей встречи:</t>
         </is>
       </c>
-      <c r="B32" s="782" t="n"/>
-      <c r="C32" s="782" t="n"/>
-      <c r="D32" s="782" t="n"/>
-      <c r="E32" s="782" t="n"/>
-      <c r="F32" s="782" t="n"/>
-      <c r="G32" s="783" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="717" t="n"/>
+      <c r="D32" s="717" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="209" t="inlineStr">
@@ -8049,7 +5900,7 @@
           <t>Комментарии. Выводы</t>
         </is>
       </c>
-      <c r="G33" s="783" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="29.25" customHeight="1">
       <c r="A34" s="155" t="n"/>
@@ -8074,7 +5925,7 @@
         </is>
       </c>
       <c r="F34" s="639" t="n"/>
-      <c r="G34" s="783" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="29.25" customHeight="1">
       <c r="A35" s="349" t="n"/>
@@ -8099,7 +5950,7 @@
         </is>
       </c>
       <c r="F35" s="409" t="n"/>
-      <c r="G35" s="783" t="n"/>
+      <c r="G35" s="718" t="n"/>
     </row>
     <row r="36" ht="48" customHeight="1">
       <c r="A36" s="350" t="n"/>
@@ -8124,7 +5975,7 @@
         </is>
       </c>
       <c r="F36" s="405" t="n"/>
-      <c r="G36" s="783" t="n"/>
+      <c r="G36" s="718" t="n"/>
     </row>
     <row r="37" ht="41.25" customHeight="1">
       <c r="A37" s="349" t="n"/>
@@ -8153,7 +6004,7 @@
           <t xml:space="preserve">добавить дополнительное поле </t>
         </is>
       </c>
-      <c r="G37" s="783" t="n"/>
+      <c r="G37" s="718" t="n"/>
     </row>
     <row r="38" ht="31.5" customHeight="1">
       <c r="A38" s="351" t="n"/>
@@ -8182,7 +6033,7 @@
           <t>Коля, после встречи напишет Насте параметры, по которым будем собирать портрет клиента.</t>
         </is>
       </c>
-      <c r="G38" s="783" t="n"/>
+      <c r="G38" s="718" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="352" t="n"/>
@@ -8207,7 +6058,7 @@
         </is>
       </c>
       <c r="F39" s="407" t="n"/>
-      <c r="G39" s="783" t="n"/>
+      <c r="G39" s="718" t="n"/>
     </row>
     <row r="40" ht="19.25" customHeight="1">
       <c r="A40" s="351" t="n"/>
@@ -8216,7 +6067,7 @@
       <c r="D40" s="401" t="n"/>
       <c r="E40" s="675" t="n"/>
       <c r="F40" s="408" t="n"/>
-      <c r="G40" s="783" t="n"/>
+      <c r="G40" s="718" t="n"/>
     </row>
     <row r="41" ht="14.7" customHeight="1">
       <c r="A41" s="352" t="n"/>
@@ -8225,7 +6076,7 @@
       <c r="D41" s="162" t="n"/>
       <c r="E41" s="172" t="n"/>
       <c r="F41" s="409" t="n"/>
-      <c r="G41" s="783" t="n"/>
+      <c r="G41" s="718" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="351" t="n"/>
@@ -8234,7 +6085,7 @@
       <c r="D42" s="401" t="n"/>
       <c r="E42" s="675" t="n"/>
       <c r="F42" s="408" t="n"/>
-      <c r="G42" s="783" t="n"/>
+      <c r="G42" s="718" t="n"/>
     </row>
     <row r="43" ht="14.25" customHeight="1">
       <c r="A43" s="352" t="n"/>
@@ -8243,7 +6094,7 @@
       <c r="D43" s="162" t="n"/>
       <c r="E43" s="172" t="n"/>
       <c r="F43" s="409" t="n"/>
-      <c r="G43" s="783" t="n"/>
+      <c r="G43" s="718" t="n"/>
     </row>
     <row r="44" ht="14.25" customHeight="1">
       <c r="A44" s="351" t="n"/>
@@ -8252,7 +6103,7 @@
       <c r="D44" s="401" t="n"/>
       <c r="E44" s="675" t="n"/>
       <c r="F44" s="408" t="n"/>
-      <c r="G44" s="783" t="n"/>
+      <c r="G44" s="718" t="n"/>
     </row>
     <row r="45" ht="14.25" customHeight="1">
       <c r="A45" s="351" t="n"/>
@@ -8261,7 +6112,7 @@
       <c r="D45" s="304" t="n"/>
       <c r="E45" s="172" t="n"/>
       <c r="F45" s="641" t="n"/>
-      <c r="G45" s="783" t="n"/>
+      <c r="G45" s="718" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="589" t="inlineStr">
@@ -8269,12 +6120,12 @@
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="B46" s="782" t="n"/>
-      <c r="C46" s="782" t="n"/>
-      <c r="D46" s="782" t="n"/>
-      <c r="E46" s="782" t="n"/>
-      <c r="F46" s="782" t="n"/>
-      <c r="G46" s="783" t="n"/>
+      <c r="B46" s="717" t="n"/>
+      <c r="C46" s="717" t="n"/>
+      <c r="D46" s="717" t="n"/>
+      <c r="E46" s="717" t="n"/>
+      <c r="F46" s="717" t="n"/>
+      <c r="G46" s="718" t="n"/>
     </row>
     <row r="47" ht="13.5" customHeight="1">
       <c r="A47" s="299" t="inlineStr">
@@ -8282,16 +6133,16 @@
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B47" s="782" t="n"/>
-      <c r="C47" s="783" t="n"/>
+      <c r="B47" s="717" t="n"/>
+      <c r="C47" s="718" t="n"/>
       <c r="D47" s="299" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E47" s="782" t="n"/>
-      <c r="F47" s="782" t="n"/>
-      <c r="G47" s="783" t="n"/>
+      <c r="E47" s="717" t="n"/>
+      <c r="F47" s="717" t="n"/>
+      <c r="G47" s="718" t="n"/>
     </row>
     <row r="48" ht="15.6" customHeight="1">
       <c r="A48" s="308" t="inlineStr">
@@ -8299,12 +6150,12 @@
           <t xml:space="preserve">Обсудить с ЦСВ трудозатраты на акцию по ЭПД. </t>
         </is>
       </c>
-      <c r="B48" s="782" t="n"/>
-      <c r="C48" s="783" t="n"/>
+      <c r="B48" s="717" t="n"/>
+      <c r="C48" s="718" t="n"/>
       <c r="D48" s="308" t="n"/>
-      <c r="E48" s="782" t="n"/>
-      <c r="F48" s="782" t="n"/>
-      <c r="G48" s="783" t="n"/>
+      <c r="E48" s="717" t="n"/>
+      <c r="F48" s="717" t="n"/>
+      <c r="G48" s="718" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="308" t="inlineStr">
@@ -8312,80 +6163,80 @@
           <t>Канал ЭПД в МАКС, ТГ , ВК. Можем ли прорабатывать этих клиентов силами ЦП и ЦКС? Связать со стратегией и целями, рассмотреть как альтернативный канал привлечения</t>
         </is>
       </c>
-      <c r="B49" s="782" t="n"/>
-      <c r="C49" s="783" t="n"/>
+      <c r="B49" s="717" t="n"/>
+      <c r="C49" s="718" t="n"/>
       <c r="D49" s="308" t="n"/>
-      <c r="E49" s="782" t="n"/>
-      <c r="F49" s="782" t="n"/>
-      <c r="G49" s="783" t="n"/>
+      <c r="E49" s="717" t="n"/>
+      <c r="F49" s="717" t="n"/>
+      <c r="G49" s="718" t="n"/>
     </row>
     <row r="50" ht="15.8" customHeight="1">
       <c r="A50" s="308" t="n"/>
-      <c r="B50" s="782" t="n"/>
-      <c r="C50" s="783" t="n"/>
+      <c r="B50" s="717" t="n"/>
+      <c r="C50" s="718" t="n"/>
       <c r="D50" s="308" t="n"/>
-      <c r="E50" s="782" t="n"/>
-      <c r="F50" s="782" t="n"/>
-      <c r="G50" s="783" t="n"/>
+      <c r="E50" s="717" t="n"/>
+      <c r="F50" s="717" t="n"/>
+      <c r="G50" s="718" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="308" t="n"/>
-      <c r="B51" s="782" t="n"/>
-      <c r="C51" s="783" t="n"/>
+      <c r="B51" s="717" t="n"/>
+      <c r="C51" s="718" t="n"/>
       <c r="D51" s="418" t="n"/>
-      <c r="E51" s="782" t="n"/>
-      <c r="F51" s="782" t="n"/>
-      <c r="G51" s="783" t="n"/>
+      <c r="E51" s="717" t="n"/>
+      <c r="F51" s="717" t="n"/>
+      <c r="G51" s="718" t="n"/>
     </row>
     <row r="52" ht="13.95" customHeight="1">
       <c r="A52" s="308" t="n"/>
-      <c r="B52" s="782" t="n"/>
-      <c r="C52" s="783" t="n"/>
+      <c r="B52" s="717" t="n"/>
+      <c r="C52" s="718" t="n"/>
       <c r="D52" s="289" t="n"/>
-      <c r="E52" s="782" t="n"/>
-      <c r="F52" s="782" t="n"/>
-      <c r="G52" s="783" t="n"/>
+      <c r="E52" s="717" t="n"/>
+      <c r="F52" s="717" t="n"/>
+      <c r="G52" s="718" t="n"/>
     </row>
     <row r="53" ht="15.85" customHeight="1">
       <c r="A53" s="289" t="n"/>
-      <c r="B53" s="782" t="n"/>
-      <c r="C53" s="783" t="n"/>
+      <c r="B53" s="717" t="n"/>
+      <c r="C53" s="718" t="n"/>
       <c r="D53" s="289" t="n"/>
-      <c r="E53" s="782" t="n"/>
-      <c r="F53" s="782" t="n"/>
-      <c r="G53" s="783" t="n"/>
+      <c r="E53" s="717" t="n"/>
+      <c r="F53" s="717" t="n"/>
+      <c r="G53" s="718" t="n"/>
     </row>
     <row r="54" ht="15.5" customHeight="1">
       <c r="A54" s="410" t="n"/>
-      <c r="B54" s="782" t="n"/>
-      <c r="C54" s="783" t="n"/>
+      <c r="B54" s="717" t="n"/>
+      <c r="C54" s="718" t="n"/>
       <c r="D54" s="411" t="n"/>
-      <c r="E54" s="782" t="n"/>
-      <c r="F54" s="782" t="n"/>
-      <c r="G54" s="783" t="n"/>
+      <c r="E54" s="717" t="n"/>
+      <c r="F54" s="717" t="n"/>
+      <c r="G54" s="718" t="n"/>
     </row>
     <row r="55" ht="18.15" customHeight="1">
       <c r="A55" s="410" t="n"/>
-      <c r="B55" s="782" t="n"/>
-      <c r="C55" s="783" t="n"/>
+      <c r="B55" s="717" t="n"/>
+      <c r="C55" s="718" t="n"/>
       <c r="D55" s="411" t="n"/>
-      <c r="E55" s="782" t="n"/>
-      <c r="F55" s="782" t="n"/>
-      <c r="G55" s="783" t="n"/>
+      <c r="E55" s="717" t="n"/>
+      <c r="F55" s="717" t="n"/>
+      <c r="G55" s="718" t="n"/>
     </row>
     <row r="56" ht="12.95" customHeight="1">
       <c r="A56" s="410" t="n"/>
-      <c r="B56" s="782" t="n"/>
-      <c r="C56" s="783" t="n"/>
+      <c r="B56" s="717" t="n"/>
+      <c r="C56" s="718" t="n"/>
       <c r="D56" s="411" t="n"/>
-      <c r="E56" s="782" t="n"/>
-      <c r="F56" s="782" t="n"/>
-      <c r="G56" s="783" t="n"/>
+      <c r="E56" s="717" t="n"/>
+      <c r="F56" s="717" t="n"/>
+      <c r="G56" s="718" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="281" t="n"/>
-      <c r="B57" s="281" t="n"/>
-      <c r="C57" s="281" t="n"/>
+      <c r="A57" s="246" t="n"/>
+      <c r="B57" s="246" t="n"/>
+      <c r="C57" s="246" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="63">
@@ -8401,9 +6252,9 @@
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="F7:G7"/>
@@ -8462,13 +6313,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:AE42"/>
   <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="8.762" customWidth="1" min="1" max="1"/>
@@ -8482,13 +6333,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="779" t="n"/>
-      <c r="B1" s="780" t="n"/>
-      <c r="C1" s="780" t="n"/>
-      <c r="D1" s="780" t="n"/>
-      <c r="E1" s="780" t="n"/>
-      <c r="F1" s="780" t="n"/>
-      <c r="G1" s="781" t="n"/>
+      <c r="A1" s="731" t="n"/>
+      <c r="B1" s="732" t="n"/>
+      <c r="C1" s="732" t="n"/>
+      <c r="D1" s="732" t="n"/>
+      <c r="E1" s="732" t="n"/>
+      <c r="F1" s="732" t="n"/>
+      <c r="G1" s="733" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -8500,17 +6351,17 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="787" t="inlineStr">
+      <c r="A3" s="734" t="inlineStr">
         <is>
           <t>Показатели рекламной кампании</t>
         </is>
       </c>
-      <c r="B3" s="788" t="n"/>
-      <c r="C3" s="788" t="n"/>
-      <c r="D3" s="788" t="n"/>
-      <c r="E3" s="788" t="n"/>
-      <c r="F3" s="788" t="n"/>
-      <c r="G3" s="789" t="n"/>
+      <c r="B3" s="735" t="n"/>
+      <c r="C3" s="735" t="n"/>
+      <c r="D3" s="735" t="n"/>
+      <c r="E3" s="735" t="n"/>
+      <c r="F3" s="735" t="n"/>
+      <c r="G3" s="736" t="n"/>
     </row>
     <row r="4" ht="24" customHeight="1">
       <c r="A4" s="421" t="inlineStr">
@@ -8561,7 +6412,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="423" t="n"/>
-      <c r="B5" s="425" t="n"/>
+      <c r="B5" s="424" t="n"/>
       <c r="C5" s="425" t="inlineStr">
         <is>
           <t xml:space="preserve">Савинская </t>
@@ -8578,17 +6429,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="790" t="inlineStr">
+      <c r="A6" s="737" t="inlineStr">
         <is>
           <t>1. Мониторинг предыдущих решений:</t>
         </is>
       </c>
-      <c r="B6" s="788" t="n"/>
-      <c r="C6" s="788" t="n"/>
-      <c r="D6" s="788" t="n"/>
-      <c r="E6" s="788" t="n"/>
-      <c r="F6" s="788" t="n"/>
-      <c r="G6" s="789" t="n"/>
+      <c r="B6" s="735" t="n"/>
+      <c r="C6" s="735" t="n"/>
+      <c r="D6" s="735" t="n"/>
+      <c r="E6" s="735" t="n"/>
+      <c r="F6" s="735" t="n"/>
+      <c r="G6" s="736" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -8650,7 +6501,7 @@
           <t>вопросы внесены</t>
         </is>
       </c>
-      <c r="G8" s="783" t="n"/>
+      <c r="G8" s="718" t="n"/>
     </row>
     <row r="9" ht="23.25" customHeight="1">
       <c r="A9" s="71" t="n"/>
@@ -8675,7 +6526,7 @@
         </is>
       </c>
       <c r="F9" s="409" t="n"/>
-      <c r="G9" s="783" t="n"/>
+      <c r="G9" s="718" t="n"/>
     </row>
     <row r="10" ht="21.6" customHeight="1">
       <c r="A10" s="303" t="n"/>
@@ -8698,7 +6549,7 @@
         </is>
       </c>
       <c r="F10" s="405" t="n"/>
-      <c r="G10" s="783" t="n"/>
+      <c r="G10" s="718" t="n"/>
     </row>
     <row r="11" ht="35.25" customHeight="1">
       <c r="A11" s="71" t="n"/>
@@ -8723,7 +6574,7 @@
         </is>
       </c>
       <c r="F11" s="409" t="n"/>
-      <c r="G11" s="783" t="n"/>
+      <c r="G11" s="718" t="n"/>
     </row>
     <row r="12" ht="282.583" customHeight="1">
       <c r="A12" s="305" t="n"/>
@@ -8748,7 +6599,7 @@
         </is>
       </c>
       <c r="F12" s="420" t="n"/>
-      <c r="G12" s="783" t="n"/>
+      <c r="G12" s="718" t="n"/>
     </row>
     <row r="13" ht="29.25" customHeight="1">
       <c r="A13" s="122" t="n"/>
@@ -8771,7 +6622,7 @@
         </is>
       </c>
       <c r="F13" s="407" t="n"/>
-      <c r="G13" s="783" t="n"/>
+      <c r="G13" s="718" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="448" t="n"/>
@@ -8779,8 +6630,8 @@
       <c r="C14" s="448" t="n"/>
       <c r="D14" s="448" t="n"/>
       <c r="E14" s="9" t="n"/>
-      <c r="F14" s="791" t="n"/>
-      <c r="G14" s="789" t="n"/>
+      <c r="F14" s="738" t="n"/>
+      <c r="G14" s="736" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="134" t="n"/>
@@ -8788,8 +6639,8 @@
       <c r="C15" s="88" t="n"/>
       <c r="D15" s="302" t="n"/>
       <c r="E15" s="77" t="n"/>
-      <c r="F15" s="792" t="n"/>
-      <c r="G15" s="789" t="n"/>
+      <c r="F15" s="739" t="n"/>
+      <c r="G15" s="736" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="41" t="n"/>
@@ -8797,8 +6648,8 @@
       <c r="C16" s="89" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="67" t="n"/>
-      <c r="F16" s="791" t="n"/>
-      <c r="G16" s="789" t="n"/>
+      <c r="F16" s="738" t="n"/>
+      <c r="G16" s="736" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
       <c r="A17" s="71" t="n"/>
@@ -8806,8 +6657,8 @@
       <c r="C17" s="88" t="n"/>
       <c r="D17" s="73" t="n"/>
       <c r="E17" s="77" t="n"/>
-      <c r="F17" s="792" t="n"/>
-      <c r="G17" s="789" t="n"/>
+      <c r="F17" s="739" t="n"/>
+      <c r="G17" s="736" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="41" t="n"/>
@@ -8815,8 +6666,8 @@
       <c r="C18" s="89" t="n"/>
       <c r="D18" s="15" t="n"/>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="791" t="n"/>
-      <c r="G18" s="789" t="n"/>
+      <c r="F18" s="738" t="n"/>
+      <c r="G18" s="736" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c r="A19" s="2" t="n"/>
@@ -8828,17 +6679,17 @@
       <c r="G19" s="2" t="n"/>
     </row>
     <row r="20" ht="16.95" customHeight="1">
-      <c r="A20" s="787" t="inlineStr">
+      <c r="A20" s="734" t="inlineStr">
         <is>
           <t>2. Решения текущей встречи:</t>
         </is>
       </c>
-      <c r="B20" s="788" t="n"/>
-      <c r="C20" s="788" t="n"/>
-      <c r="D20" s="788" t="n"/>
-      <c r="E20" s="788" t="n"/>
-      <c r="F20" s="788" t="n"/>
-      <c r="G20" s="789" t="n"/>
+      <c r="B20" s="735" t="n"/>
+      <c r="C20" s="735" t="n"/>
+      <c r="D20" s="735" t="n"/>
+      <c r="E20" s="735" t="n"/>
+      <c r="F20" s="735" t="n"/>
+      <c r="G20" s="736" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
       <c r="A21" s="109" t="inlineStr">
@@ -8871,7 +6722,7 @@
           <t>Комментарии. Выводы</t>
         </is>
       </c>
-      <c r="G21" s="793" t="n"/>
+      <c r="G21" s="740" t="n"/>
     </row>
     <row r="22" ht="42.75" customHeight="1">
       <c r="A22" s="155" t="n"/>
@@ -8896,7 +6747,7 @@
         </is>
       </c>
       <c r="F22" s="639" t="n"/>
-      <c r="G22" s="783" t="n"/>
+      <c r="G22" s="718" t="n"/>
     </row>
     <row r="23" ht="42.75" customHeight="1">
       <c r="A23" s="349" t="n">
@@ -8927,7 +6778,7 @@
           <t xml:space="preserve">Корнева А. 13.08 : Поговорила  с ЦСВ. Клиентов распределяет Юля Ситникова. В августе таких клиентов не было, все клиенты , что пришли уже были с оформленным сервисом. На будущее решили так: если клиент действующий , то передача менеджеру ЦКС, если клиент без договора то в ЦП. </t>
         </is>
       </c>
-      <c r="G23" s="783" t="n"/>
+      <c r="G23" s="718" t="n"/>
     </row>
     <row r="24" ht="56.25" customHeight="1">
       <c r="A24" s="350" t="n">
@@ -8958,7 +6809,7 @@
           <t>учесть требования вендора, 20.08 обсуждаем ОС</t>
         </is>
       </c>
-      <c r="G24" s="783" t="n"/>
+      <c r="G24" s="718" t="n"/>
     </row>
     <row r="25" ht="29.25" customHeight="1">
       <c r="A25" s="349" t="n">
@@ -8985,7 +6836,7 @@
         </is>
       </c>
       <c r="F25" s="409" t="n"/>
-      <c r="G25" s="783" t="n"/>
+      <c r="G25" s="718" t="n"/>
     </row>
     <row r="26" ht="26.1" customHeight="1">
       <c r="A26" s="351" t="n">
@@ -9012,7 +6863,7 @@
         </is>
       </c>
       <c r="F26" s="420" t="n"/>
-      <c r="G26" s="783" t="n"/>
+      <c r="G26" s="718" t="n"/>
     </row>
     <row r="27" ht="27.9" customHeight="1">
       <c r="A27" s="352" t="n">
@@ -9039,7 +6890,7 @@
         </is>
       </c>
       <c r="F27" s="407" t="n"/>
-      <c r="G27" s="783" t="n"/>
+      <c r="G27" s="718" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="351" t="n">
@@ -9066,7 +6917,7 @@
         </is>
       </c>
       <c r="F28" s="408" t="n"/>
-      <c r="G28" s="783" t="n"/>
+      <c r="G28" s="718" t="n"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
       <c r="A29" s="352" t="n"/>
@@ -9075,7 +6926,7 @@
       <c r="D29" s="162" t="n"/>
       <c r="E29" s="172" t="n"/>
       <c r="F29" s="409" t="n"/>
-      <c r="G29" s="783" t="n"/>
+      <c r="G29" s="718" t="n"/>
     </row>
     <row r="30" ht="14.25" customHeight="1">
       <c r="A30" s="351" t="n"/>
@@ -9084,15 +6935,15 @@
       <c r="D30" s="401" t="n"/>
       <c r="E30" s="675" t="n"/>
       <c r="F30" s="408" t="n"/>
-      <c r="G30" s="783" t="n"/>
+      <c r="G30" s="718" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="794" t="inlineStr">
+      <c r="A31" s="741" t="inlineStr">
         <is>
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="G31" s="795" t="n"/>
+      <c r="G31" s="742" t="n"/>
     </row>
     <row r="32" ht="13.5" customHeight="1">
       <c r="A32" s="299" t="inlineStr">
@@ -9100,102 +6951,102 @@
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B32" s="782" t="n"/>
-      <c r="C32" s="783" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="718" t="n"/>
       <c r="D32" s="299" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E32" s="782" t="n"/>
-      <c r="F32" s="782" t="n"/>
-      <c r="G32" s="783" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33" ht="32.25" customHeight="1">
       <c r="A33" s="308" t="n"/>
-      <c r="B33" s="782" t="n"/>
-      <c r="C33" s="783" t="n"/>
+      <c r="B33" s="717" t="n"/>
+      <c r="C33" s="718" t="n"/>
       <c r="D33" s="308" t="n"/>
-      <c r="E33" s="782" t="n"/>
-      <c r="F33" s="782" t="n"/>
-      <c r="G33" s="783" t="n"/>
+      <c r="E33" s="717" t="n"/>
+      <c r="F33" s="717" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="30.75" customHeight="1">
       <c r="A34" s="308" t="n"/>
-      <c r="B34" s="782" t="n"/>
-      <c r="C34" s="783" t="n"/>
+      <c r="B34" s="717" t="n"/>
+      <c r="C34" s="718" t="n"/>
       <c r="D34" s="308" t="n"/>
-      <c r="E34" s="782" t="n"/>
-      <c r="F34" s="782" t="n"/>
-      <c r="G34" s="783" t="n"/>
+      <c r="E34" s="717" t="n"/>
+      <c r="F34" s="717" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="38.7" customHeight="1">
       <c r="A35" s="308" t="n"/>
-      <c r="B35" s="782" t="n"/>
-      <c r="C35" s="783" t="n"/>
+      <c r="B35" s="717" t="n"/>
+      <c r="C35" s="718" t="n"/>
       <c r="D35" s="308" t="n"/>
-      <c r="E35" s="782" t="n"/>
-      <c r="F35" s="782" t="n"/>
-      <c r="G35" s="783" t="n"/>
+      <c r="E35" s="717" t="n"/>
+      <c r="F35" s="717" t="n"/>
+      <c r="G35" s="718" t="n"/>
     </row>
     <row r="36" ht="27.9" customHeight="1">
       <c r="A36" s="308" t="n"/>
-      <c r="B36" s="782" t="n"/>
-      <c r="C36" s="783" t="n"/>
+      <c r="B36" s="717" t="n"/>
+      <c r="C36" s="718" t="n"/>
       <c r="D36" s="418" t="n"/>
-      <c r="E36" s="782" t="n"/>
-      <c r="F36" s="782" t="n"/>
-      <c r="G36" s="783" t="n"/>
+      <c r="E36" s="717" t="n"/>
+      <c r="F36" s="717" t="n"/>
+      <c r="G36" s="718" t="n"/>
     </row>
     <row r="37" ht="28.75" customHeight="1">
       <c r="A37" s="308" t="n"/>
-      <c r="B37" s="782" t="n"/>
-      <c r="C37" s="783" t="n"/>
+      <c r="B37" s="717" t="n"/>
+      <c r="C37" s="718" t="n"/>
       <c r="D37" s="289" t="n"/>
-      <c r="E37" s="782" t="n"/>
-      <c r="F37" s="782" t="n"/>
-      <c r="G37" s="783" t="n"/>
+      <c r="E37" s="717" t="n"/>
+      <c r="F37" s="717" t="n"/>
+      <c r="G37" s="718" t="n"/>
     </row>
     <row r="38" ht="25.65" customHeight="1">
       <c r="A38" s="289" t="n"/>
-      <c r="B38" s="782" t="n"/>
-      <c r="C38" s="783" t="n"/>
+      <c r="B38" s="717" t="n"/>
+      <c r="C38" s="718" t="n"/>
       <c r="D38" s="289" t="n"/>
-      <c r="E38" s="782" t="n"/>
-      <c r="F38" s="782" t="n"/>
-      <c r="G38" s="783" t="n"/>
+      <c r="E38" s="717" t="n"/>
+      <c r="F38" s="717" t="n"/>
+      <c r="G38" s="718" t="n"/>
     </row>
     <row r="39" ht="25.45" customHeight="1">
       <c r="A39" s="410" t="n"/>
-      <c r="B39" s="782" t="n"/>
-      <c r="C39" s="783" t="n"/>
+      <c r="B39" s="717" t="n"/>
+      <c r="C39" s="718" t="n"/>
       <c r="D39" s="411" t="n"/>
-      <c r="E39" s="782" t="n"/>
-      <c r="F39" s="782" t="n"/>
-      <c r="G39" s="783" t="n"/>
+      <c r="E39" s="717" t="n"/>
+      <c r="F39" s="717" t="n"/>
+      <c r="G39" s="718" t="n"/>
     </row>
     <row r="40" ht="27.05" customHeight="1">
       <c r="A40" s="410" t="n"/>
-      <c r="B40" s="782" t="n"/>
-      <c r="C40" s="783" t="n"/>
+      <c r="B40" s="717" t="n"/>
+      <c r="C40" s="718" t="n"/>
       <c r="D40" s="411" t="n"/>
-      <c r="E40" s="782" t="n"/>
-      <c r="F40" s="782" t="n"/>
-      <c r="G40" s="783" t="n"/>
+      <c r="E40" s="717" t="n"/>
+      <c r="F40" s="717" t="n"/>
+      <c r="G40" s="718" t="n"/>
     </row>
     <row r="41" ht="21.45" customHeight="1">
       <c r="A41" s="410" t="n"/>
-      <c r="B41" s="782" t="n"/>
-      <c r="C41" s="783" t="n"/>
+      <c r="B41" s="717" t="n"/>
+      <c r="C41" s="718" t="n"/>
       <c r="D41" s="411" t="n"/>
-      <c r="E41" s="782" t="n"/>
-      <c r="F41" s="782" t="n"/>
-      <c r="G41" s="783" t="n"/>
+      <c r="E41" s="717" t="n"/>
+      <c r="F41" s="717" t="n"/>
+      <c r="G41" s="718" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="281" t="n"/>
-      <c r="B42" s="281" t="n"/>
-      <c r="C42" s="281" t="n"/>
+      <c r="A42" s="246" t="n"/>
+      <c r="B42" s="246" t="n"/>
+      <c r="C42" s="246" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -9250,7 +7101,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9269,17 +7120,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="779" t="inlineStr">
+      <c r="A1" s="731" t="inlineStr">
         <is>
           <t>ВСТРЕЧА ЦП-ЦКС-ЦСВ-СМАК</t>
         </is>
       </c>
-      <c r="B1" s="780" t="n"/>
-      <c r="C1" s="780" t="n"/>
-      <c r="D1" s="780" t="n"/>
-      <c r="E1" s="780" t="n"/>
-      <c r="F1" s="780" t="n"/>
-      <c r="G1" s="781" t="n"/>
+      <c r="B1" s="732" t="n"/>
+      <c r="C1" s="732" t="n"/>
+      <c r="D1" s="732" t="n"/>
+      <c r="E1" s="732" t="n"/>
+      <c r="F1" s="732" t="n"/>
+      <c r="G1" s="733" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -9291,17 +7142,17 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="787" t="inlineStr">
+      <c r="A3" s="734" t="inlineStr">
         <is>
           <t>1. Мониторинг предыдущих решений:</t>
         </is>
       </c>
-      <c r="B3" s="788" t="n"/>
-      <c r="C3" s="788" t="n"/>
-      <c r="D3" s="788" t="n"/>
-      <c r="E3" s="788" t="n"/>
-      <c r="F3" s="788" t="n"/>
-      <c r="G3" s="789" t="n"/>
+      <c r="B3" s="735" t="n"/>
+      <c r="C3" s="735" t="n"/>
+      <c r="D3" s="735" t="n"/>
+      <c r="E3" s="735" t="n"/>
+      <c r="F3" s="735" t="n"/>
+      <c r="G3" s="736" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -9343,7 +7194,7 @@
       <c r="D5" s="15" t="n"/>
       <c r="E5" s="79" t="n"/>
       <c r="F5" s="84" t="n"/>
-      <c r="G5" s="783" t="n"/>
+      <c r="G5" s="718" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="71" t="n"/>
@@ -9352,7 +7203,7 @@
       <c r="D6" s="73" t="n"/>
       <c r="E6" s="81" t="n"/>
       <c r="F6" s="86" t="n"/>
-      <c r="G6" s="783" t="n"/>
+      <c r="G6" s="718" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="41" t="n"/>
@@ -9361,7 +7212,7 @@
       <c r="D7" s="15" t="n"/>
       <c r="E7" s="83" t="n"/>
       <c r="F7" s="84" t="n"/>
-      <c r="G7" s="783" t="n"/>
+      <c r="G7" s="718" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="71" t="n"/>
@@ -9370,7 +7221,7 @@
       <c r="D8" s="73" t="n"/>
       <c r="E8" s="81" t="n"/>
       <c r="F8" s="86" t="n"/>
-      <c r="G8" s="783" t="n"/>
+      <c r="G8" s="718" t="n"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="41" t="n"/>
@@ -9379,7 +7230,7 @@
       <c r="D9" s="15" t="n"/>
       <c r="E9" s="79" t="n"/>
       <c r="F9" s="84" t="n"/>
-      <c r="G9" s="783" t="n"/>
+      <c r="G9" s="718" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="71" t="n"/>
@@ -9387,8 +7238,8 @@
       <c r="C10" s="88" t="n"/>
       <c r="D10" s="73" t="n"/>
       <c r="E10" s="33" t="n"/>
-      <c r="F10" s="792" t="n"/>
-      <c r="G10" s="789" t="n"/>
+      <c r="F10" s="739" t="n"/>
+      <c r="G10" s="736" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="41" t="n"/>
@@ -9396,8 +7247,8 @@
       <c r="C11" s="89" t="n"/>
       <c r="D11" s="15" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="791" t="n"/>
-      <c r="G11" s="789" t="n"/>
+      <c r="F11" s="738" t="n"/>
+      <c r="G11" s="736" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="71" t="n"/>
@@ -9405,8 +7256,8 @@
       <c r="C12" s="88" t="n"/>
       <c r="D12" s="73" t="n"/>
       <c r="E12" s="77" t="n"/>
-      <c r="F12" s="792" t="n"/>
-      <c r="G12" s="789" t="n"/>
+      <c r="F12" s="739" t="n"/>
+      <c r="G12" s="736" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="41" t="n"/>
@@ -9414,8 +7265,8 @@
       <c r="C13" s="89" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="67" t="n"/>
-      <c r="F13" s="791" t="n"/>
-      <c r="G13" s="789" t="n"/>
+      <c r="F13" s="738" t="n"/>
+      <c r="G13" s="736" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="71" t="n"/>
@@ -9423,8 +7274,8 @@
       <c r="C14" s="88" t="n"/>
       <c r="D14" s="73" t="n"/>
       <c r="E14" s="77" t="n"/>
-      <c r="F14" s="792" t="n"/>
-      <c r="G14" s="789" t="n"/>
+      <c r="F14" s="739" t="n"/>
+      <c r="G14" s="736" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="41" t="n"/>
@@ -9432,8 +7283,8 @@
       <c r="C15" s="89" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="791" t="n"/>
-      <c r="G15" s="789" t="n"/>
+      <c r="F15" s="738" t="n"/>
+      <c r="G15" s="736" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="n"/>
@@ -9445,17 +7296,17 @@
       <c r="G16" s="2" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="787" t="inlineStr">
+      <c r="A17" s="734" t="inlineStr">
         <is>
           <t>2. Решения текущей встречи:</t>
         </is>
       </c>
-      <c r="B17" s="788" t="n"/>
-      <c r="C17" s="788" t="n"/>
-      <c r="D17" s="788" t="n"/>
-      <c r="E17" s="788" t="n"/>
-      <c r="F17" s="788" t="n"/>
-      <c r="G17" s="789" t="n"/>
+      <c r="B17" s="735" t="n"/>
+      <c r="C17" s="735" t="n"/>
+      <c r="D17" s="735" t="n"/>
+      <c r="E17" s="735" t="n"/>
+      <c r="F17" s="735" t="n"/>
+      <c r="G17" s="736" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="109" t="inlineStr">
@@ -9666,17 +7517,17 @@
       <c r="G27" s="170" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="796" t="inlineStr">
+      <c r="A28" s="743" t="inlineStr">
         <is>
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="B28" s="797" t="n"/>
-      <c r="C28" s="797" t="n"/>
-      <c r="D28" s="797" t="n"/>
-      <c r="E28" s="797" t="n"/>
-      <c r="F28" s="797" t="n"/>
-      <c r="G28" s="793" t="n"/>
+      <c r="B28" s="744" t="n"/>
+      <c r="C28" s="744" t="n"/>
+      <c r="D28" s="744" t="n"/>
+      <c r="E28" s="744" t="n"/>
+      <c r="F28" s="744" t="n"/>
+      <c r="G28" s="740" t="n"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
       <c r="A29" s="299" t="inlineStr">
@@ -9684,16 +7535,16 @@
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B29" s="782" t="n"/>
-      <c r="C29" s="783" t="n"/>
+      <c r="B29" s="717" t="n"/>
+      <c r="C29" s="718" t="n"/>
       <c r="D29" s="299" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E29" s="782" t="n"/>
-      <c r="F29" s="782" t="n"/>
-      <c r="G29" s="783" t="n"/>
+      <c r="E29" s="717" t="n"/>
+      <c r="F29" s="717" t="n"/>
+      <c r="G29" s="718" t="n"/>
     </row>
     <row r="30" ht="102" customHeight="1">
       <c r="A30" s="289" t="inlineStr">
@@ -9705,8 +7556,8 @@
 - Общая выручка по направлению ЭПД в июле (по данным Оксаны) – 64 000 ₽ (с учётом услуг и титулов)</t>
         </is>
       </c>
-      <c r="B30" s="782" t="n"/>
-      <c r="C30" s="783" t="n"/>
+      <c r="B30" s="717" t="n"/>
+      <c r="C30" s="718" t="n"/>
       <c r="D30" s="289" t="inlineStr">
         <is>
           <t>- Конверсия признана удовлетворительной, но основной тормоз – отчётный период у бухгалтеров (клиенты просят связаться после 27‑го числа).
@@ -9714,9 +7565,9 @@
 - Валидность лидов выше 50%, большинство сделок в работе – это позитивный сигнал.</t>
         </is>
       </c>
-      <c r="E30" s="782" t="n"/>
-      <c r="F30" s="782" t="n"/>
-      <c r="G30" s="783" t="n"/>
+      <c r="E30" s="717" t="n"/>
+      <c r="F30" s="717" t="n"/>
+      <c r="G30" s="718" t="n"/>
     </row>
     <row r="31" ht="72" customHeight="1">
       <c r="A31" s="289" t="inlineStr">
@@ -9726,8 +7577,8 @@
 - Возник вопрос: делить ли бюджет между ЦП и ЦКС?</t>
         </is>
       </c>
-      <c r="B31" s="782" t="n"/>
-      <c r="C31" s="783" t="n"/>
+      <c r="B31" s="717" t="n"/>
+      <c r="C31" s="718" t="n"/>
       <c r="D31" s="289" t="inlineStr">
         <is>
           <t>Принято решение: не делить бюджет между подразделениями, а рассматривать его как общий котёл направления ЭПД.
@@ -9735,9 +7586,9 @@
 - Для обоснования бюджета необходимо построить финансовую модель направления с учётом всех затрат и прогноза доходов (задача на команду).</t>
         </is>
       </c>
-      <c r="E31" s="782" t="n"/>
-      <c r="F31" s="782" t="n"/>
-      <c r="G31" s="783" t="n"/>
+      <c r="E31" s="717" t="n"/>
+      <c r="F31" s="717" t="n"/>
+      <c r="G31" s="718" t="n"/>
     </row>
     <row r="32" ht="69" customHeight="1">
       <c r="A32" s="289" t="inlineStr">
@@ -9748,8 +7599,8 @@
 - База обширна и может быть использована для целенаправленных обзвонов.</t>
         </is>
       </c>
-      <c r="B32" s="782" t="n"/>
-      <c r="C32" s="783" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="718" t="n"/>
       <c r="D32" s="289" t="inlineStr">
         <is>
           <t>- Данная база – бесплатный канал, который сейчас используется не в полной мере.
@@ -9757,9 +7608,9 @@
 - Работа с текущей базой – приоритетное направление для быстрого увеличения продаж без дополнительных затрат на рекламу.</t>
         </is>
       </c>
-      <c r="E32" s="782" t="n"/>
-      <c r="F32" s="782" t="n"/>
-      <c r="G32" s="783" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33" ht="98.25" customHeight="1">
       <c r="A33" s="289" t="inlineStr">
@@ -9771,8 +7622,8 @@
 - Оксана отметила, что направление ЭПД пока убыточно (три сотрудника с зарплатами, большие минусы), но это инвестиции в захват рынка.</t>
         </is>
       </c>
-      <c r="B33" s="782" t="n"/>
-      <c r="C33" s="783" t="n"/>
+      <c r="B33" s="717" t="n"/>
+      <c r="C33" s="718" t="n"/>
       <c r="D33" s="289" t="inlineStr">
         <is>
           <t>- Единогласно признана необходимость стратегической сессии с участием всех подразделений (очный формат).
@@ -9783,9 +7634,9 @@
 - Финансовая модель должна быть построена после определения стратегии, чтобы отражать реальные планы.</t>
         </is>
       </c>
-      <c r="E33" s="782" t="n"/>
-      <c r="F33" s="782" t="n"/>
-      <c r="G33" s="783" t="n"/>
+      <c r="E33" s="717" t="n"/>
+      <c r="F33" s="717" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="48.75" customHeight="1">
       <c r="A34" s="289" t="inlineStr">
@@ -9794,8 +7645,8 @@
 Оксана предложила активно «отъедать» клиентов у партнёров, особенно тех, кто не занимается ЭПД (например, партнёры, продающие УАД).</t>
         </is>
       </c>
-      <c r="B34" s="782" t="n"/>
-      <c r="C34" s="783" t="n"/>
+      <c r="B34" s="717" t="n"/>
+      <c r="C34" s="718" t="n"/>
       <c r="D34" s="289" t="inlineStr">
         <is>
           <t>Взять в проработку:
@@ -9803,9 +7654,9 @@
 - Эта работа требует отдельного плана и ресурсов – обсудить на стратег‑сессии.</t>
         </is>
       </c>
-      <c r="E34" s="782" t="n"/>
-      <c r="F34" s="782" t="n"/>
-      <c r="G34" s="783" t="n"/>
+      <c r="E34" s="717" t="n"/>
+      <c r="F34" s="717" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="47.25" customHeight="1">
       <c r="A35" s="289" t="inlineStr">
@@ -9814,8 +7665,8 @@
 Анна отметила, что данные по лидам и сделкам поступают с задержкой, что мешает оперативной корректировке рекламы.</t>
         </is>
       </c>
-      <c r="B35" s="782" t="n"/>
-      <c r="C35" s="783" t="n"/>
+      <c r="B35" s="717" t="n"/>
+      <c r="C35" s="718" t="n"/>
       <c r="D35" s="289" t="inlineStr">
         <is>
           <t>Договорились:
@@ -9823,9 +7674,9 @@
 - Оксана ежемесячно кидает данные по ДДС направления (общая выручка).</t>
         </is>
       </c>
-      <c r="E35" s="782" t="n"/>
-      <c r="F35" s="782" t="n"/>
-      <c r="G35" s="783" t="n"/>
+      <c r="E35" s="717" t="n"/>
+      <c r="F35" s="717" t="n"/>
+      <c r="G35" s="718" t="n"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="235" t="n"/>
@@ -9840,9 +7691,9 @@
       <c r="D38" s="242" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="281" t="n"/>
-      <c r="B39" s="281" t="n"/>
-      <c r="C39" s="281" t="n"/>
+      <c r="A39" s="246" t="n"/>
+      <c r="B39" s="246" t="n"/>
+      <c r="C39" s="246" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -9886,7 +7737,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9905,13 +7756,13 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="779" t="n"/>
-      <c r="B1" s="780" t="n"/>
-      <c r="C1" s="780" t="n"/>
-      <c r="D1" s="780" t="n"/>
-      <c r="E1" s="780" t="n"/>
-      <c r="F1" s="780" t="n"/>
-      <c r="G1" s="781" t="n"/>
+      <c r="A1" s="731" t="n"/>
+      <c r="B1" s="732" t="n"/>
+      <c r="C1" s="732" t="n"/>
+      <c r="D1" s="732" t="n"/>
+      <c r="E1" s="732" t="n"/>
+      <c r="F1" s="732" t="n"/>
+      <c r="G1" s="733" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -9923,17 +7774,17 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="787" t="inlineStr">
+      <c r="A3" s="734" t="inlineStr">
         <is>
           <t>1. Мониторинг предыдущих решений:</t>
         </is>
       </c>
-      <c r="B3" s="788" t="n"/>
-      <c r="C3" s="788" t="n"/>
-      <c r="D3" s="788" t="n"/>
-      <c r="E3" s="788" t="n"/>
-      <c r="F3" s="788" t="n"/>
-      <c r="G3" s="789" t="n"/>
+      <c r="B3" s="735" t="n"/>
+      <c r="C3" s="735" t="n"/>
+      <c r="D3" s="735" t="n"/>
+      <c r="E3" s="735" t="n"/>
+      <c r="F3" s="735" t="n"/>
+      <c r="G3" s="736" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -9988,12 +7839,12 @@
           <t xml:space="preserve">в работе </t>
         </is>
       </c>
-      <c r="F5" s="798" t="inlineStr">
+      <c r="F5" s="745" t="inlineStr">
         <is>
           <t>уточнить по поводу внесены ли вопросы МПП для создания базы знаний</t>
         </is>
       </c>
-      <c r="G5" s="781" t="n"/>
+      <c r="G5" s="733" t="n"/>
     </row>
     <row r="6" ht="23.25" customHeight="1">
       <c r="A6" s="71" t="n"/>
@@ -10015,12 +7866,12 @@
           <t>в работе</t>
         </is>
       </c>
-      <c r="F6" s="520" t="inlineStr">
+      <c r="F6" s="356" t="inlineStr">
         <is>
           <t xml:space="preserve">ОС в чате ЭПД стратегия будет </t>
         </is>
       </c>
-      <c r="G6" s="781" t="n"/>
+      <c r="G6" s="733" t="n"/>
     </row>
     <row r="7" ht="112.5" customHeight="1">
       <c r="A7" s="303" t="n"/>
@@ -10042,7 +7893,7 @@
           <t>выполнено</t>
         </is>
       </c>
-      <c r="F7" s="798" t="inlineStr">
+      <c r="F7" s="745" t="inlineStr">
         <is>
           <t xml:space="preserve">Отвалы Группа продуктвого запуска за июль: 12
 уже решили вопрос - 4
@@ -10052,7 +7903,7 @@
 другое -1 </t>
         </is>
       </c>
-      <c r="G7" s="781" t="n"/>
+      <c r="G7" s="733" t="n"/>
     </row>
     <row r="8" ht="35.25" customHeight="1">
       <c r="A8" s="71" t="n"/>
@@ -10072,12 +7923,12 @@
         </is>
       </c>
       <c r="E8" s="393" t="n"/>
-      <c r="F8" s="799" t="inlineStr">
+      <c r="F8" s="746" t="inlineStr">
         <is>
           <t>у меня нет старых чатов, вопрос - требуются ли нам чаты по  PR и ИМ отдельные?</t>
         </is>
       </c>
-      <c r="G8" s="781" t="n"/>
+      <c r="G8" s="733" t="n"/>
     </row>
     <row r="9" ht="37.35" customHeight="1">
       <c r="A9" s="305" t="n"/>
@@ -10097,12 +7948,12 @@
           <t>приостановлено</t>
         </is>
       </c>
-      <c r="F9" s="800" t="inlineStr">
+      <c r="F9" s="747" t="inlineStr">
         <is>
           <t>ПР снято с поддержки, 06.08 -встреча с коллегами из Калуги.Астрал по обсуждению проектного решения от Доки</t>
         </is>
       </c>
-      <c r="G9" s="781" t="n"/>
+      <c r="G9" s="733" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="122" t="n"/>
@@ -10125,7 +7976,7 @@
         </is>
       </c>
       <c r="F10" s="366" t="n"/>
-      <c r="G10" s="781" t="n"/>
+      <c r="G10" s="733" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="448" t="n"/>
@@ -10133,8 +7984,8 @@
       <c r="C11" s="448" t="n"/>
       <c r="D11" s="448" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="791" t="n"/>
-      <c r="G11" s="789" t="n"/>
+      <c r="F11" s="738" t="n"/>
+      <c r="G11" s="736" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="134" t="n"/>
@@ -10142,8 +7993,8 @@
       <c r="C12" s="88" t="n"/>
       <c r="D12" s="302" t="n"/>
       <c r="E12" s="77" t="n"/>
-      <c r="F12" s="792" t="n"/>
-      <c r="G12" s="789" t="n"/>
+      <c r="F12" s="739" t="n"/>
+      <c r="G12" s="736" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="41" t="n"/>
@@ -10151,8 +8002,8 @@
       <c r="C13" s="89" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="67" t="n"/>
-      <c r="F13" s="791" t="n"/>
-      <c r="G13" s="789" t="n"/>
+      <c r="F13" s="738" t="n"/>
+      <c r="G13" s="736" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="71" t="n"/>
@@ -10160,8 +8011,8 @@
       <c r="C14" s="88" t="n"/>
       <c r="D14" s="73" t="n"/>
       <c r="E14" s="77" t="n"/>
-      <c r="F14" s="792" t="n"/>
-      <c r="G14" s="789" t="n"/>
+      <c r="F14" s="739" t="n"/>
+      <c r="G14" s="736" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="41" t="n"/>
@@ -10169,8 +8020,8 @@
       <c r="C15" s="89" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="791" t="n"/>
-      <c r="G15" s="789" t="n"/>
+      <c r="F15" s="738" t="n"/>
+      <c r="G15" s="736" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="n"/>
@@ -10182,17 +8033,17 @@
       <c r="G16" s="2" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="787" t="inlineStr">
+      <c r="A17" s="734" t="inlineStr">
         <is>
           <t>2. Решения текущей встречи:</t>
         </is>
       </c>
-      <c r="B17" s="788" t="n"/>
-      <c r="C17" s="788" t="n"/>
-      <c r="D17" s="788" t="n"/>
-      <c r="E17" s="788" t="n"/>
-      <c r="F17" s="788" t="n"/>
-      <c r="G17" s="789" t="n"/>
+      <c r="B17" s="735" t="n"/>
+      <c r="C17" s="735" t="n"/>
+      <c r="D17" s="735" t="n"/>
+      <c r="E17" s="735" t="n"/>
+      <c r="F17" s="735" t="n"/>
+      <c r="G17" s="736" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="109" t="inlineStr">
@@ -10225,7 +8076,7 @@
           <t>Комментарии. Выводы</t>
         </is>
       </c>
-      <c r="G18" s="793" t="n"/>
+      <c r="G18" s="740" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="155" t="n"/>
@@ -10250,7 +8101,7 @@
         </is>
       </c>
       <c r="F19" s="639" t="n"/>
-      <c r="G19" s="783" t="n"/>
+      <c r="G19" s="718" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="349" t="n">
@@ -10277,7 +8128,7 @@
         </is>
       </c>
       <c r="F20" s="409" t="n"/>
-      <c r="G20" s="783" t="n"/>
+      <c r="G20" s="718" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="350" t="n">
@@ -10302,7 +8153,7 @@
         </is>
       </c>
       <c r="F21" s="405" t="n"/>
-      <c r="G21" s="783" t="n"/>
+      <c r="G21" s="718" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="349" t="n">
@@ -10329,7 +8180,7 @@
         </is>
       </c>
       <c r="F22" s="409" t="n"/>
-      <c r="G22" s="783" t="n"/>
+      <c r="G22" s="718" t="n"/>
     </row>
     <row r="23" ht="252.75" customHeight="1">
       <c r="A23" s="351" t="n">
@@ -10370,7 +8221,7 @@
 Деменская:</t>
         </is>
       </c>
-      <c r="G23" s="783" t="n"/>
+      <c r="G23" s="718" t="n"/>
     </row>
     <row r="24" ht="15.95" customHeight="1">
       <c r="A24" s="352" t="n">
@@ -10395,7 +8246,7 @@
         </is>
       </c>
       <c r="F24" s="407" t="n"/>
-      <c r="G24" s="783" t="n"/>
+      <c r="G24" s="718" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="351" t="n">
@@ -10406,7 +8257,7 @@
       <c r="D25" s="401" t="n"/>
       <c r="E25" s="675" t="n"/>
       <c r="F25" s="408" t="n"/>
-      <c r="G25" s="783" t="n"/>
+      <c r="G25" s="718" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="352" t="n"/>
@@ -10415,7 +8266,7 @@
       <c r="D26" s="162" t="n"/>
       <c r="E26" s="172" t="n"/>
       <c r="F26" s="409" t="n"/>
-      <c r="G26" s="783" t="n"/>
+      <c r="G26" s="718" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="351" t="n"/>
@@ -10424,15 +8275,15 @@
       <c r="D27" s="401" t="n"/>
       <c r="E27" s="675" t="n"/>
       <c r="F27" s="408" t="n"/>
-      <c r="G27" s="783" t="n"/>
+      <c r="G27" s="718" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="794" t="inlineStr">
+      <c r="A28" s="741" t="inlineStr">
         <is>
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="G28" s="795" t="n"/>
+      <c r="G28" s="742" t="n"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
       <c r="A29" s="299" t="inlineStr">
@@ -10440,16 +8291,16 @@
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B29" s="782" t="n"/>
-      <c r="C29" s="783" t="n"/>
+      <c r="B29" s="717" t="n"/>
+      <c r="C29" s="718" t="n"/>
       <c r="D29" s="299" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E29" s="782" t="n"/>
-      <c r="F29" s="782" t="n"/>
-      <c r="G29" s="783" t="n"/>
+      <c r="E29" s="717" t="n"/>
+      <c r="F29" s="717" t="n"/>
+      <c r="G29" s="718" t="n"/>
     </row>
     <row r="30" ht="32.25" customHeight="1">
       <c r="A30" s="308" t="inlineStr">
@@ -10457,16 +8308,16 @@
           <t xml:space="preserve"> Прошу включить тему регистрации проданных ЭПД и ДОКИ за Форусом. Сейчас нет ответственного. часть оплативших клиентов не закреплены за форусом (Антон Гурков)</t>
         </is>
       </c>
-      <c r="B30" s="782" t="n"/>
-      <c r="C30" s="783" t="n"/>
+      <c r="B30" s="717" t="n"/>
+      <c r="C30" s="718" t="n"/>
       <c r="D30" s="308" t="inlineStr">
         <is>
           <t xml:space="preserve">ознакомиться с протоколом в чате Стратегия ЭПД  (Процесс привязки клиента), оставляем вопрос до следующей встречи. Вопросы МПП можно адресовать Антону </t>
         </is>
       </c>
-      <c r="E30" s="782" t="n"/>
-      <c r="F30" s="782" t="n"/>
-      <c r="G30" s="783" t="n"/>
+      <c r="E30" s="717" t="n"/>
+      <c r="F30" s="717" t="n"/>
+      <c r="G30" s="718" t="n"/>
     </row>
     <row r="31" ht="30.75" customHeight="1">
       <c r="A31" s="308" t="inlineStr">
@@ -10474,16 +8325,16 @@
           <t>Акция от Калуги - закрепление действий</t>
         </is>
       </c>
-      <c r="B31" s="782" t="n"/>
-      <c r="C31" s="783" t="n"/>
+      <c r="B31" s="717" t="n"/>
+      <c r="C31" s="718" t="n"/>
       <c r="D31" s="308" t="inlineStr">
         <is>
           <t xml:space="preserve">Лиза планирует собрать ОС от партнеров, акция уже закончилась </t>
         </is>
       </c>
-      <c r="E31" s="782" t="n"/>
-      <c r="F31" s="782" t="n"/>
-      <c r="G31" s="783" t="n"/>
+      <c r="E31" s="717" t="n"/>
+      <c r="F31" s="717" t="n"/>
+      <c r="G31" s="718" t="n"/>
     </row>
     <row r="32" ht="38.7" customHeight="1">
       <c r="A32" s="308" t="inlineStr">
@@ -10491,16 +8342,16 @@
           <t xml:space="preserve">Мастерская по ЭПД + Доки </t>
         </is>
       </c>
-      <c r="B32" s="782" t="n"/>
-      <c r="C32" s="783" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="718" t="n"/>
       <c r="D32" s="308" t="inlineStr">
         <is>
           <t>13 августа будет мероприятие, идет запись МПП и подготовка вопросов. Лиза отправит Маше (в копию О. Костюкову) вопросы МПП до конца дня понедельника 10.08</t>
         </is>
       </c>
-      <c r="E32" s="782" t="n"/>
-      <c r="F32" s="782" t="n"/>
-      <c r="G32" s="783" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33" ht="54" customHeight="1">
       <c r="A33" s="308" t="inlineStr">
@@ -10508,16 +8359,16 @@
           <t>Обучение от Калуги.Астрал - не открывается для менеджеров, долгая проверка ИНН</t>
         </is>
       </c>
-      <c r="B33" s="782" t="n"/>
-      <c r="C33" s="783" t="n"/>
+      <c r="B33" s="717" t="n"/>
+      <c r="C33" s="718" t="n"/>
       <c r="D33" s="418" t="inlineStr">
         <is>
           <t>отправить Маше информацию по МПП, которые зарегались на портале Астрала, но не могут получить доступ к курску</t>
         </is>
       </c>
-      <c r="E33" s="782" t="n"/>
-      <c r="F33" s="782" t="n"/>
-      <c r="G33" s="783" t="n"/>
+      <c r="E33" s="717" t="n"/>
+      <c r="F33" s="717" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="28.75" customHeight="1">
       <c r="A34" s="308" t="inlineStr">
@@ -10525,57 +8376,57 @@
           <t>КЦР - статистика продаж/интересов, кому предлагаем, как работаем</t>
         </is>
       </c>
-      <c r="B34" s="782" t="n"/>
-      <c r="C34" s="783" t="n"/>
+      <c r="B34" s="717" t="n"/>
+      <c r="C34" s="718" t="n"/>
       <c r="D34" s="289" t="inlineStr">
         <is>
           <t xml:space="preserve">Лизой составляется регламент работы по продаже КЦР, какие линии использовать? Маша подтвердила, что КЦР можно ставить на линию ЭПД, КЦР не обслуживаем, но подготовят инструкции и специалистов. Если КЦР вне рамок ЭПД - и клиенты готовы платить, то можно подумать о линии. Если Маша найдет запись встречи от 1С , то направит нам </t>
         </is>
       </c>
-      <c r="E34" s="782" t="n"/>
-      <c r="F34" s="782" t="n"/>
-      <c r="G34" s="783" t="n"/>
+      <c r="E34" s="717" t="n"/>
+      <c r="F34" s="717" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="25.65" customHeight="1">
       <c r="A35" s="289" t="n"/>
-      <c r="B35" s="782" t="n"/>
-      <c r="C35" s="783" t="n"/>
+      <c r="B35" s="717" t="n"/>
+      <c r="C35" s="718" t="n"/>
       <c r="D35" s="289" t="n"/>
-      <c r="E35" s="782" t="n"/>
-      <c r="F35" s="782" t="n"/>
-      <c r="G35" s="783" t="n"/>
+      <c r="E35" s="717" t="n"/>
+      <c r="F35" s="717" t="n"/>
+      <c r="G35" s="718" t="n"/>
     </row>
     <row r="36" ht="25.45" customHeight="1">
       <c r="A36" s="410" t="n"/>
-      <c r="B36" s="782" t="n"/>
-      <c r="C36" s="783" t="n"/>
+      <c r="B36" s="717" t="n"/>
+      <c r="C36" s="718" t="n"/>
       <c r="D36" s="411" t="n"/>
-      <c r="E36" s="782" t="n"/>
-      <c r="F36" s="782" t="n"/>
-      <c r="G36" s="783" t="n"/>
+      <c r="E36" s="717" t="n"/>
+      <c r="F36" s="717" t="n"/>
+      <c r="G36" s="718" t="n"/>
     </row>
     <row r="37" ht="27.05" customHeight="1">
       <c r="A37" s="410" t="n"/>
-      <c r="B37" s="782" t="n"/>
-      <c r="C37" s="783" t="n"/>
+      <c r="B37" s="717" t="n"/>
+      <c r="C37" s="718" t="n"/>
       <c r="D37" s="411" t="n"/>
-      <c r="E37" s="782" t="n"/>
-      <c r="F37" s="782" t="n"/>
-      <c r="G37" s="783" t="n"/>
+      <c r="E37" s="717" t="n"/>
+      <c r="F37" s="717" t="n"/>
+      <c r="G37" s="718" t="n"/>
     </row>
     <row r="38" ht="21.45" customHeight="1">
       <c r="A38" s="410" t="n"/>
-      <c r="B38" s="782" t="n"/>
-      <c r="C38" s="783" t="n"/>
+      <c r="B38" s="717" t="n"/>
+      <c r="C38" s="718" t="n"/>
       <c r="D38" s="411" t="n"/>
-      <c r="E38" s="782" t="n"/>
-      <c r="F38" s="782" t="n"/>
-      <c r="G38" s="783" t="n"/>
+      <c r="E38" s="717" t="n"/>
+      <c r="F38" s="717" t="n"/>
+      <c r="G38" s="718" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="281" t="n"/>
-      <c r="B39" s="281" t="n"/>
-      <c r="C39" s="281" t="n"/>
+      <c r="A39" s="246" t="n"/>
+      <c r="B39" s="246" t="n"/>
+      <c r="C39" s="246" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -10629,7 +8480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10648,17 +8499,17 @@
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1">
-      <c r="A1" s="779" t="inlineStr">
+      <c r="A1" s="731" t="inlineStr">
         <is>
           <t>ВСТРЕЧА ЦП-ЦКС-ЦСВ-СМАК</t>
         </is>
       </c>
-      <c r="B1" s="780" t="n"/>
-      <c r="C1" s="780" t="n"/>
-      <c r="D1" s="780" t="n"/>
-      <c r="E1" s="780" t="n"/>
-      <c r="F1" s="780" t="n"/>
-      <c r="G1" s="781" t="n"/>
+      <c r="B1" s="732" t="n"/>
+      <c r="C1" s="732" t="n"/>
+      <c r="D1" s="732" t="n"/>
+      <c r="E1" s="732" t="n"/>
+      <c r="F1" s="732" t="n"/>
+      <c r="G1" s="733" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -10670,17 +8521,17 @@
       <c r="G2" s="2" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="787" t="inlineStr">
+      <c r="A3" s="734" t="inlineStr">
         <is>
           <t>1. Мониторинг предыдущих решений:</t>
         </is>
       </c>
-      <c r="B3" s="788" t="n"/>
-      <c r="C3" s="788" t="n"/>
-      <c r="D3" s="788" t="n"/>
-      <c r="E3" s="788" t="n"/>
-      <c r="F3" s="788" t="n"/>
-      <c r="G3" s="789" t="n"/>
+      <c r="B3" s="735" t="n"/>
+      <c r="C3" s="735" t="n"/>
+      <c r="D3" s="735" t="n"/>
+      <c r="E3" s="735" t="n"/>
+      <c r="F3" s="735" t="n"/>
+      <c r="G3" s="736" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -10753,7 +8604,7 @@
 итого оплат: 9 шт</t>
         </is>
       </c>
-      <c r="G5" s="783" t="n"/>
+      <c r="G5" s="718" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="71" t="n"/>
@@ -10776,7 +8627,7 @@
         </is>
       </c>
       <c r="F6" s="86" t="n"/>
-      <c r="G6" s="783" t="n"/>
+      <c r="G6" s="718" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="303" t="n"/>
@@ -10785,7 +8636,7 @@
       <c r="D7" s="169" t="n"/>
       <c r="E7" s="83" t="n"/>
       <c r="F7" s="84" t="n"/>
-      <c r="G7" s="783" t="n"/>
+      <c r="G7" s="718" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="71" t="n"/>
@@ -10794,7 +8645,7 @@
       <c r="D8" s="166" t="n"/>
       <c r="E8" s="81" t="n"/>
       <c r="F8" s="86" t="n"/>
-      <c r="G8" s="783" t="n"/>
+      <c r="G8" s="718" t="n"/>
     </row>
     <row r="9" ht="14.25" customHeight="1">
       <c r="A9" s="305" t="n"/>
@@ -10803,7 +8654,7 @@
       <c r="D9" s="306" t="n"/>
       <c r="E9" s="79" t="n"/>
       <c r="F9" s="84" t="n"/>
-      <c r="G9" s="783" t="n"/>
+      <c r="G9" s="718" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="122" t="n"/>
@@ -10811,8 +8662,8 @@
       <c r="C10" s="124" t="n"/>
       <c r="D10" s="124" t="n"/>
       <c r="E10" s="33" t="n"/>
-      <c r="F10" s="792" t="n"/>
-      <c r="G10" s="789" t="n"/>
+      <c r="F10" s="739" t="n"/>
+      <c r="G10" s="736" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="448" t="n"/>
@@ -10820,8 +8671,8 @@
       <c r="C11" s="448" t="n"/>
       <c r="D11" s="448" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="791" t="n"/>
-      <c r="G11" s="789" t="n"/>
+      <c r="F11" s="738" t="n"/>
+      <c r="G11" s="736" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="134" t="n"/>
@@ -10829,8 +8680,8 @@
       <c r="C12" s="88" t="n"/>
       <c r="D12" s="302" t="n"/>
       <c r="E12" s="77" t="n"/>
-      <c r="F12" s="792" t="n"/>
-      <c r="G12" s="789" t="n"/>
+      <c r="F12" s="739" t="n"/>
+      <c r="G12" s="736" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="41" t="n"/>
@@ -10838,8 +8689,8 @@
       <c r="C13" s="89" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="67" t="n"/>
-      <c r="F13" s="791" t="n"/>
-      <c r="G13" s="789" t="n"/>
+      <c r="F13" s="738" t="n"/>
+      <c r="G13" s="736" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="71" t="n"/>
@@ -10847,8 +8698,8 @@
       <c r="C14" s="88" t="n"/>
       <c r="D14" s="73" t="n"/>
       <c r="E14" s="77" t="n"/>
-      <c r="F14" s="792" t="n"/>
-      <c r="G14" s="789" t="n"/>
+      <c r="F14" s="739" t="n"/>
+      <c r="G14" s="736" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
       <c r="A15" s="41" t="n"/>
@@ -10856,8 +8707,8 @@
       <c r="C15" s="89" t="n"/>
       <c r="D15" s="15" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="791" t="n"/>
-      <c r="G15" s="789" t="n"/>
+      <c r="F15" s="738" t="n"/>
+      <c r="G15" s="736" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
       <c r="A16" s="2" t="n"/>
@@ -10869,17 +8720,17 @@
       <c r="G16" s="2" t="n"/>
     </row>
     <row r="17" ht="14.25" customHeight="1">
-      <c r="A17" s="787" t="inlineStr">
+      <c r="A17" s="734" t="inlineStr">
         <is>
           <t>2. Решения текущей встречи:</t>
         </is>
       </c>
-      <c r="B17" s="788" t="n"/>
-      <c r="C17" s="788" t="n"/>
-      <c r="D17" s="788" t="n"/>
-      <c r="E17" s="788" t="n"/>
-      <c r="F17" s="788" t="n"/>
-      <c r="G17" s="789" t="n"/>
+      <c r="B17" s="735" t="n"/>
+      <c r="C17" s="735" t="n"/>
+      <c r="D17" s="735" t="n"/>
+      <c r="E17" s="735" t="n"/>
+      <c r="F17" s="735" t="n"/>
+      <c r="G17" s="736" t="n"/>
     </row>
     <row r="18" ht="14.25" customHeight="1">
       <c r="A18" s="109" t="inlineStr">
@@ -10912,7 +8763,7 @@
           <t>Комментарии. Выводы</t>
         </is>
       </c>
-      <c r="G18" s="793" t="n"/>
+      <c r="G18" s="740" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="155" t="n"/>
@@ -10933,7 +8784,7 @@
       </c>
       <c r="E19" s="159" t="n"/>
       <c r="F19" s="639" t="n"/>
-      <c r="G19" s="783" t="n"/>
+      <c r="G19" s="718" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="349" t="n">
@@ -10954,7 +8805,7 @@
       </c>
       <c r="E20" s="164" t="n"/>
       <c r="F20" s="405" t="n"/>
-      <c r="G20" s="783" t="n"/>
+      <c r="G20" s="718" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="350" t="n">
@@ -10979,7 +8830,7 @@
           <t>Уточнить информацию у ЦРД</t>
         </is>
       </c>
-      <c r="G21" s="783" t="n"/>
+      <c r="G21" s="718" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="349" t="n">
@@ -11004,7 +8855,7 @@
           <t>+ корректирующие действия</t>
         </is>
       </c>
-      <c r="G22" s="783" t="n"/>
+      <c r="G22" s="718" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="351" t="n">
@@ -11031,7 +8882,7 @@
           <t>лишние назвать Старыми</t>
         </is>
       </c>
-      <c r="G23" s="783" t="n"/>
+      <c r="G23" s="718" t="n"/>
     </row>
     <row r="24" ht="52.5" customHeight="1">
       <c r="A24" s="352" t="n">
@@ -11054,7 +8905,7 @@
           <t xml:space="preserve">нужен список; скрипт; если это проект, то как работаем с ЦСВ - если проект, то сразу встреча включаться будет Оксана и Маша. Первичный этап с Антоном. </t>
         </is>
       </c>
-      <c r="G24" s="783" t="n"/>
+      <c r="G24" s="718" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="351" t="n">
@@ -11074,8 +8925,8 @@
         <v>46206</v>
       </c>
       <c r="E25" s="170" t="n"/>
-      <c r="F25" s="801" t="n"/>
-      <c r="G25" s="783" t="n"/>
+      <c r="F25" s="748" t="n"/>
+      <c r="G25" s="718" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
       <c r="A26" s="352" t="n"/>
@@ -11083,8 +8934,8 @@
       <c r="C26" s="161" t="n"/>
       <c r="D26" s="162" t="n"/>
       <c r="E26" s="172" t="n"/>
-      <c r="F26" s="801" t="n"/>
-      <c r="G26" s="783" t="n"/>
+      <c r="F26" s="748" t="n"/>
+      <c r="G26" s="718" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
       <c r="A27" s="351" t="n"/>
@@ -11092,16 +8943,16 @@
       <c r="C27" s="168" t="n"/>
       <c r="D27" s="173" t="n"/>
       <c r="E27" s="170" t="n"/>
-      <c r="F27" s="801" t="n"/>
-      <c r="G27" s="783" t="n"/>
+      <c r="F27" s="748" t="n"/>
+      <c r="G27" s="718" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="794" t="inlineStr">
+      <c r="A28" s="741" t="inlineStr">
         <is>
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="G28" s="795" t="n"/>
+      <c r="G28" s="742" t="n"/>
     </row>
     <row r="29" ht="13.5" customHeight="1">
       <c r="A29" s="299" t="inlineStr">
@@ -11109,16 +8960,16 @@
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B29" s="782" t="n"/>
-      <c r="C29" s="783" t="n"/>
+      <c r="B29" s="717" t="n"/>
+      <c r="C29" s="718" t="n"/>
       <c r="D29" s="299" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E29" s="782" t="n"/>
-      <c r="F29" s="782" t="n"/>
-      <c r="G29" s="783" t="n"/>
+      <c r="E29" s="717" t="n"/>
+      <c r="F29" s="717" t="n"/>
+      <c r="G29" s="718" t="n"/>
     </row>
     <row r="30" ht="32.25" customHeight="1">
       <c r="A30" s="308" t="inlineStr">
@@ -11126,16 +8977,16 @@
           <t>1. Оставляем ли акцию "При покупке пакета титулов от 1 000 штук - бесплатная настройка рабочего места"</t>
         </is>
       </c>
-      <c r="B30" s="782" t="n"/>
-      <c r="C30" s="783" t="n"/>
+      <c r="B30" s="717" t="n"/>
+      <c r="C30" s="718" t="n"/>
       <c r="D30" s="308" t="inlineStr">
         <is>
           <t>Акцию необходимо продолжить и оставить до 30 августа, от нее идет хороший трафик</t>
         </is>
       </c>
-      <c r="E30" s="782" t="n"/>
-      <c r="F30" s="782" t="n"/>
-      <c r="G30" s="783" t="n"/>
+      <c r="E30" s="717" t="n"/>
+      <c r="F30" s="717" t="n"/>
+      <c r="G30" s="718" t="n"/>
     </row>
     <row r="31" ht="30.75" customHeight="1">
       <c r="A31" s="308" t="inlineStr">
@@ -11143,12 +8994,12 @@
           <t>2. Рекламная кампания - запускаем ли мы её с августа?</t>
         </is>
       </c>
-      <c r="B31" s="782" t="n"/>
-      <c r="C31" s="783" t="n"/>
+      <c r="B31" s="717" t="n"/>
+      <c r="C31" s="718" t="n"/>
       <c r="D31" s="308" t="n"/>
-      <c r="E31" s="782" t="n"/>
-      <c r="F31" s="782" t="n"/>
-      <c r="G31" s="783" t="n"/>
+      <c r="E31" s="717" t="n"/>
+      <c r="F31" s="717" t="n"/>
+      <c r="G31" s="718" t="n"/>
     </row>
     <row r="32" ht="62.25" customHeight="1">
       <c r="A32" s="308" t="inlineStr">
@@ -11156,8 +9007,8 @@
           <t>3. Участие в акции от Калуги: вопросы и решения</t>
         </is>
       </c>
-      <c r="B32" s="782" t="n"/>
-      <c r="C32" s="783" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="718" t="n"/>
       <c r="D32" s="308" t="inlineStr">
         <is>
           <t>1. Четко под запись узнать у Калуги: "Как все это работает", иначе - риск потери клиентов, 
@@ -11165,9 +9016,9 @@
 3. При регистрации клиента по реферальной ссылке, они падают в ?таблицу?, в которую мы можем перейти по ссылке, спустя какое время они передаются на другого партнера? как работает механизм?</t>
         </is>
       </c>
-      <c r="E32" s="782" t="n"/>
-      <c r="F32" s="782" t="n"/>
-      <c r="G32" s="783" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33" ht="27.75" customHeight="1">
       <c r="A33" s="308" t="inlineStr">
@@ -11175,16 +9026,16 @@
           <t>4.Судьба решений по проектным решениям</t>
         </is>
       </c>
-      <c r="B33" s="782" t="n"/>
-      <c r="C33" s="783" t="n"/>
+      <c r="B33" s="717" t="n"/>
+      <c r="C33" s="718" t="n"/>
       <c r="D33" s="308" t="inlineStr">
         <is>
           <t>на след неделе должне стартануть обзвон, будет первая статистика</t>
         </is>
       </c>
-      <c r="E33" s="782" t="n"/>
-      <c r="F33" s="782" t="n"/>
-      <c r="G33" s="783" t="n"/>
+      <c r="E33" s="717" t="n"/>
+      <c r="F33" s="717" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="48.75" customHeight="1">
       <c r="A34" s="289" t="inlineStr">
@@ -11192,21 +9043,21 @@
           <t>5. прошу включить тему регистрации проданных ЭПД и ДОКи за форусом. Сейчас нет ответственного. часть оплативших клиентов не закреплены за форусом</t>
         </is>
       </c>
-      <c r="B34" s="782" t="n"/>
-      <c r="C34" s="783" t="n"/>
+      <c r="B34" s="717" t="n"/>
+      <c r="C34" s="718" t="n"/>
       <c r="D34" s="289" t="n"/>
-      <c r="E34" s="782" t="n"/>
-      <c r="F34" s="782" t="n"/>
-      <c r="G34" s="783" t="n"/>
+      <c r="E34" s="717" t="n"/>
+      <c r="F34" s="717" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="47.25" customHeight="1">
       <c r="A35" s="289" t="n"/>
-      <c r="B35" s="782" t="n"/>
-      <c r="C35" s="783" t="n"/>
+      <c r="B35" s="717" t="n"/>
+      <c r="C35" s="718" t="n"/>
       <c r="D35" s="289" t="n"/>
-      <c r="E35" s="782" t="n"/>
-      <c r="F35" s="782" t="n"/>
-      <c r="G35" s="783" t="n"/>
+      <c r="E35" s="717" t="n"/>
+      <c r="F35" s="717" t="n"/>
+      <c r="G35" s="718" t="n"/>
     </row>
     <row r="36" ht="14.25" customHeight="1">
       <c r="A36" s="235" t="n"/>
@@ -11221,9 +9072,9 @@
       <c r="D38" s="242" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="281" t="n"/>
-      <c r="B39" s="281" t="n"/>
-      <c r="C39" s="281" t="n"/>
+      <c r="A39" s="246" t="n"/>
+      <c r="B39" s="246" t="n"/>
+      <c r="C39" s="246" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">

--- a/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
+++ b/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3160" yWindow="2260" windowWidth="28240" windowHeight="17240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="27.08.2026" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="20.08.2026" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="13.08.2026 (2)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="24.07.2026" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="06.082026" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="30.07.2026" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="27.08.2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="20.08.2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13.08.2026 (2)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24.07.2026" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06.082026" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="30.07.2026" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -1571,21 +1571,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1799,36 +1793,24 @@
     <xf numFmtId="1" fontId="8" fillId="12" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1850,15 +1832,11 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -1909,15 +1887,11 @@
     <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -2036,9 +2010,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2195,9 +2167,7 @@
     <xf numFmtId="1" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -2222,9 +2192,7 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -3110,7 +3078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE102"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="8.762" customWidth="1" min="1" max="1"/>
@@ -3131,12 +3099,12 @@
           <t>ВСТРЕЧА ЦП-ЦКС-ЦСВ-СМАК</t>
         </is>
       </c>
-      <c r="B1" s="698" t="n"/>
-      <c r="C1" s="698" t="n"/>
-      <c r="D1" s="698" t="n"/>
-      <c r="E1" s="698" t="n"/>
-      <c r="F1" s="698" t="n"/>
-      <c r="G1" s="698" t="n"/>
+      <c r="B1" s="717" t="n"/>
+      <c r="C1" s="717" t="n"/>
+      <c r="D1" s="717" t="n"/>
+      <c r="E1" s="717" t="n"/>
+      <c r="F1" s="717" t="n"/>
+      <c r="G1" s="718" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="588" t="n"/>
@@ -3153,19 +3121,19 @@
           <t>План по ЭПД</t>
         </is>
       </c>
-      <c r="B3" s="699" t="n"/>
-      <c r="C3" s="699" t="n"/>
-      <c r="D3" s="699" t="n"/>
-      <c r="E3" s="699" t="n"/>
-      <c r="F3" s="699" t="n"/>
-      <c r="G3" s="699" t="n"/>
+      <c r="B3" s="717" t="n"/>
+      <c r="C3" s="717" t="n"/>
+      <c r="D3" s="717" t="n"/>
+      <c r="E3" s="717" t="n"/>
+      <c r="F3" s="717" t="n"/>
+      <c r="G3" s="718" t="n"/>
       <c r="I3" s="700" t="inlineStr">
         <is>
           <t>Соотношение к прошлому периоду</t>
         </is>
       </c>
-      <c r="J3" s="701" t="n"/>
-      <c r="K3" s="701" t="n"/>
+      <c r="J3" s="717" t="n"/>
+      <c r="K3" s="718" t="n"/>
     </row>
     <row r="4" ht="14.25" customHeight="1">
       <c r="A4" s="702" t="inlineStr">
@@ -3173,19 +3141,19 @@
           <t>План</t>
         </is>
       </c>
-      <c r="B4" s="702" t="n"/>
+      <c r="B4" s="718" t="n"/>
       <c r="C4" s="702" t="inlineStr">
         <is>
           <t>Текущее значение</t>
         </is>
       </c>
-      <c r="D4" s="702" t="n"/>
+      <c r="D4" s="718" t="n"/>
       <c r="E4" s="702" t="inlineStr">
         <is>
           <t>Итого до плана</t>
         </is>
       </c>
-      <c r="F4" s="702" t="n"/>
+      <c r="F4" s="718" t="n"/>
       <c r="G4" s="702" t="inlineStr">
         <is>
           <t>% выполнения плана</t>
@@ -3211,17 +3179,17 @@
       <c r="A5" s="703" t="n">
         <v>500</v>
       </c>
-      <c r="B5" s="704" t="n"/>
+      <c r="B5" s="718" t="n"/>
       <c r="C5" s="705">
         <f>E9+E10+E11</f>
         <v/>
       </c>
-      <c r="D5" s="706" t="n"/>
+      <c r="D5" s="718" t="n"/>
       <c r="E5" s="703">
         <f>A5-C5</f>
         <v/>
       </c>
-      <c r="F5" s="704" t="n"/>
+      <c r="F5" s="718" t="n"/>
       <c r="G5" s="707">
         <f>IF(A5=0,"—",C5/A5)</f>
         <v/>
@@ -3231,9 +3199,8 @@
           <t>27.08.2026</t>
         </is>
       </c>
-      <c r="J5" s="709">
-        <f>C5</f>
-        <v/>
+      <c r="J5" s="711" t="n">
+        <v>150</v>
       </c>
       <c r="K5" s="708" t="inlineStr">
         <is>
@@ -3244,25 +3211,25 @@
     <row r="6" ht="14.25" customHeight="1">
       <c r="A6" s="710" t="inlineStr">
         <is>
-          <t>«Текущее значение» = сумма ячеек «Факт» по отделам (ниже). Жёлтые ячейки — для ввода.</t>
-        </is>
-      </c>
-      <c r="B6" s="698" t="n"/>
-      <c r="C6" s="698" t="n"/>
-      <c r="D6" s="698" t="n"/>
-      <c r="E6" s="698" t="n"/>
-      <c r="F6" s="698" t="n"/>
-      <c r="G6" s="698" t="n"/>
+          <t>«Текущее значение» плана = сумма «Факт» по отделам. Таблица периодов справа заполняется отдельно (жёлтые ячейки).</t>
+        </is>
+      </c>
+      <c r="B6" s="717" t="n"/>
+      <c r="C6" s="717" t="n"/>
+      <c r="D6" s="717" t="n"/>
+      <c r="E6" s="717" t="n"/>
+      <c r="F6" s="717" t="n"/>
+      <c r="G6" s="718" t="n"/>
       <c r="I6" s="708" t="inlineStr">
         <is>
-          <t>03.09.2026</t>
+          <t>02.09.2026</t>
         </is>
       </c>
       <c r="J6" s="711" t="n">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="K6" s="712">
-        <f>IF(OR(J5="",J5=0,J6=""),"—",IF(J6&gt;=J5,"увеличилось на "&amp;TEXT((J6-J5)/J5,"0.0%"),"уменьшилось на "&amp;TEXT((J5-J6)/J5,"0.0%")))</f>
+        <f>IF(OR(J5="",J6="",NOT(ISNUMBER(J5)),NOT(ISNUMBER(J6))),"",IF(J5=0,"",IF(J6&gt;J5,"увеличилось на "&amp;ROUND((J6-J5)/J5*100,1)&amp;"%",IF(J6&lt;J5,"уменьшилось на "&amp;ROUND((J5-J6)/J5*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3272,12 +3239,12 @@
           <t>План на МПП в месяц — по отделам</t>
         </is>
       </c>
-      <c r="B7" s="701" t="n"/>
-      <c r="C7" s="701" t="n"/>
-      <c r="D7" s="701" t="n"/>
-      <c r="E7" s="701" t="n"/>
-      <c r="F7" s="701" t="n"/>
-      <c r="G7" s="701" t="n"/>
+      <c r="B7" s="717" t="n"/>
+      <c r="C7" s="717" t="n"/>
+      <c r="D7" s="717" t="n"/>
+      <c r="E7" s="717" t="n"/>
+      <c r="F7" s="717" t="n"/>
+      <c r="G7" s="718" t="n"/>
       <c r="I7" s="708" t="inlineStr">
         <is>
           <t>10.09.2026</t>
@@ -3287,7 +3254,7 @@
         <v>250</v>
       </c>
       <c r="K7" s="712">
-        <f>IF(OR(J6="",J6=0,J7=""),"—",IF(J7&gt;=J6,"увеличилось на "&amp;TEXT((J7-J6)/J6,"0.0%"),"уменьшилось на "&amp;TEXT((J6-J7)/J6,"0.0%")))</f>
+        <f>IF(OR(J6="",J7="",NOT(ISNUMBER(J6)),NOT(ISNUMBER(J7))),"",IF(J6=0,"",IF(J7&gt;J6,"увеличилось на "&amp;ROUND((J7-J6)/J6*100,1)&amp;"%",IF(J7&lt;J6,"уменьшилось на "&amp;ROUND((J6-J7)/J6*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3297,13 +3264,13 @@
           <t>Отдел / группа</t>
         </is>
       </c>
-      <c r="B8" s="713" t="n"/>
+      <c r="B8" s="718" t="n"/>
       <c r="C8" s="702" t="inlineStr">
         <is>
           <t>План на МПП в мес</t>
         </is>
       </c>
-      <c r="D8" s="713" t="n"/>
+      <c r="D8" s="718" t="n"/>
       <c r="E8" s="702" t="inlineStr">
         <is>
           <t>Факт</t>
@@ -3314,11 +3281,11 @@
           <t>% выполнения плана</t>
         </is>
       </c>
-      <c r="G8" s="713" t="n"/>
+      <c r="G8" s="718" t="n"/>
       <c r="I8" s="708" t="n"/>
       <c r="J8" s="711" t="n"/>
       <c r="K8" s="712">
-        <f>IF(OR(J7="",J7=0,J8=""),"—",IF(J8&gt;=J7,"увеличилось на "&amp;TEXT((J8-J7)/J7,"0.0%"),"уменьшилось на "&amp;TEXT((J7-J8)/J7,"0.0%")))</f>
+        <f>IF(OR(J7="",J8="",NOT(ISNUMBER(J7)),NOT(ISNUMBER(J8))),"",IF(J7=0,"",IF(J8&gt;J7,"увеличилось на "&amp;ROUND((J8-J7)/J7*100,1)&amp;"%",IF(J8&lt;J7,"уменьшилось на "&amp;ROUND((J7-J8)/J7*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3328,11 +3295,11 @@
           <t>Группа «Новые деньги»</t>
         </is>
       </c>
-      <c r="B9" s="704" t="n"/>
+      <c r="B9" s="718" t="n"/>
       <c r="C9" s="714" t="n">
         <v>75</v>
       </c>
-      <c r="D9" s="704" t="n"/>
+      <c r="D9" s="718" t="n"/>
       <c r="E9" s="711" t="n">
         <v>90</v>
       </c>
@@ -3340,11 +3307,11 @@
         <f>IF(OR(C9="",C9=0),"—",E9/C9)</f>
         <v/>
       </c>
-      <c r="G9" s="706" t="n"/>
+      <c r="G9" s="718" t="n"/>
       <c r="I9" s="708" t="n"/>
       <c r="J9" s="711" t="n"/>
       <c r="K9" s="712">
-        <f>IF(OR(J8="",J8=0,J9=""),"—",IF(J9&gt;=J8,"увеличилось на "&amp;TEXT((J9-J8)/J8,"0.0%"),"уменьшилось на "&amp;TEXT((J8-J9)/J8,"0.0%")))</f>
+        <f>IF(OR(J8="",J9="",NOT(ISNUMBER(J8)),NOT(ISNUMBER(J9))),"",IF(J8=0,"",IF(J9&gt;J8,"увеличилось на "&amp;ROUND((J9-J8)/J8*100,1)&amp;"%",IF(J9&lt;J8,"уменьшилось на "&amp;ROUND((J8-J9)/J8*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3354,11 +3321,11 @@
           <t>Группа продуктового запуска</t>
         </is>
       </c>
-      <c r="B10" s="704" t="n"/>
+      <c r="B10" s="718" t="n"/>
       <c r="C10" s="714" t="n">
         <v>25</v>
       </c>
-      <c r="D10" s="704" t="n"/>
+      <c r="D10" s="718" t="n"/>
       <c r="E10" s="711" t="n">
         <v>40</v>
       </c>
@@ -3366,11 +3333,11 @@
         <f>IF(OR(C10="",C10=0),"—",E10/C10)</f>
         <v/>
       </c>
-      <c r="G10" s="706" t="n"/>
+      <c r="G10" s="718" t="n"/>
       <c r="I10" s="708" t="n"/>
       <c r="J10" s="711" t="n"/>
       <c r="K10" s="712">
-        <f>IF(OR(J9="",J9=0,J10=""),"—",IF(J10&gt;=J9,"увеличилось на "&amp;TEXT((J10-J9)/J9,"0.0%"),"уменьшилось на "&amp;TEXT((J9-J10)/J9,"0.0%")))</f>
+        <f>IF(OR(J9="",J10="",NOT(ISNUMBER(J9)),NOT(ISNUMBER(J10))),"",IF(J9=0,"",IF(J10&gt;J9,"увеличилось на "&amp;ROUND((J10-J9)/J9*100,1)&amp;"%",IF(J10&lt;J9,"уменьшилось на "&amp;ROUND((J9-J10)/J9*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3380,9 +3347,9 @@
           <t>ЦКС</t>
         </is>
       </c>
-      <c r="B11" s="704" t="n"/>
+      <c r="B11" s="718" t="n"/>
       <c r="C11" s="716" t="n"/>
-      <c r="D11" s="698" t="n"/>
+      <c r="D11" s="718" t="n"/>
       <c r="E11" s="711" t="n">
         <v>20</v>
       </c>
@@ -3390,11 +3357,11 @@
         <f>IF(OR(C11="",C11=0),"—",E11/C11)</f>
         <v/>
       </c>
-      <c r="G11" s="706" t="n"/>
+      <c r="G11" s="718" t="n"/>
       <c r="I11" s="708" t="n"/>
       <c r="J11" s="711" t="n"/>
       <c r="K11" s="712">
-        <f>IF(OR(J10="",J10=0,J11=""),"—",IF(J11&gt;=J10,"увеличилось на "&amp;TEXT((J11-J10)/J10,"0.0%"),"уменьшилось на "&amp;TEXT((J10-J11)/J10,"0.0%")))</f>
+        <f>IF(OR(J10="",J11="",NOT(ISNUMBER(J10)),NOT(ISNUMBER(J11))),"",IF(J10=0,"",IF(J11&gt;J10,"увеличилось на "&amp;ROUND((J11-J10)/J10*100,1)&amp;"%",IF(J11&lt;J10,"уменьшилось на "&amp;ROUND((J10-J11)/J10*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
@@ -3402,22 +3369,27 @@
       <c r="I12" s="708" t="n"/>
       <c r="J12" s="711" t="n"/>
       <c r="K12" s="712">
-        <f>IF(OR(J11="",J11=0,J12=""),"—",IF(J12&gt;=J11,"увеличилось на "&amp;TEXT((J12-J11)/J11,"0.0%"),"уменьшилось на "&amp;TEXT((J11-J12)/J11,"0.0%")))</f>
+        <f>IF(OR(J11="",J12="",NOT(ISNUMBER(J11)),NOT(ISNUMBER(J12))),"",IF(J11=0,"",IF(J12&gt;J11,"увеличилось на "&amp;ROUND((J12-J11)/J11*100,1)&amp;"%",IF(J12&lt;J11,"уменьшилось на "&amp;ROUND((J11-J12)/J11*100,1)&amp;"%","без изменений"))))</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="14.95" customHeight="1">
       <c r="I13" s="710" t="inlineStr">
         <is>
-          <t>Строка 27.08 подтягивает текущее значение. Новые даты — в жёлтые ячейки «Клиенты».</t>
-        </is>
-      </c>
-      <c r="J13" s="698" t="n"/>
-      <c r="K13" s="698" t="n"/>
-    </row>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
+          <t>Жёлтые ячейки «Клиенты» — вводите числа вручную. «Изменение» пересчитается само (например 150→160 = увеличилось на 6,7%).</t>
+        </is>
+      </c>
+      <c r="J13" s="717" t="n"/>
+      <c r="K13" s="718" t="n"/>
+    </row>
+    <row r="14">
+      <c r="I14" s="708" t="n"/>
+      <c r="J14" s="711" t="n"/>
+      <c r="K14" s="712">
+        <f>IF(OR(J13="",J14="",NOT(ISNUMBER(J13)),NOT(ISNUMBER(J14))),"",IF(J13=0,"",IF(J14&gt;J13,"увеличилось на "&amp;ROUND((J14-J13)/J13*100,1)&amp;"%",IF(J14&lt;J13,"уменьшилось на "&amp;ROUND((J13-J14)/J13*100,1)&amp;"%","без изменений"))))</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" s="589" t="inlineStr">
         <is>
@@ -3552,7 +3524,7 @@
       <c r="D21" s="596" t="n"/>
       <c r="E21" s="448" t="n"/>
       <c r="F21" s="496" t="n"/>
-      <c r="G21" s="496" t="n"/>
+      <c r="G21" s="718" t="n"/>
       <c r="H21" s="492" t="n"/>
       <c r="I21" s="492" t="n"/>
       <c r="J21" s="482" t="n"/>
@@ -3566,7 +3538,7 @@
       <c r="D22" s="596" t="n"/>
       <c r="E22" s="594" t="n"/>
       <c r="F22" s="496" t="n"/>
-      <c r="G22" s="496" t="n"/>
+      <c r="G22" s="718" t="n"/>
       <c r="H22" s="492" t="n"/>
       <c r="I22" s="492" t="n"/>
       <c r="J22" s="482" t="n"/>
@@ -3580,7 +3552,7 @@
       <c r="D23" s="599" t="n"/>
       <c r="E23" s="594" t="n"/>
       <c r="F23" s="632" t="n"/>
-      <c r="G23" s="632" t="n"/>
+      <c r="G23" s="718" t="n"/>
       <c r="H23" s="492" t="n"/>
       <c r="I23" s="492" t="n"/>
       <c r="J23" s="482" t="n"/>
@@ -3594,7 +3566,7 @@
       <c r="D24" s="599" t="n"/>
       <c r="E24" s="594" t="n"/>
       <c r="F24" s="496" t="n"/>
-      <c r="G24" s="496" t="n"/>
+      <c r="G24" s="718" t="n"/>
       <c r="H24" s="492" t="n"/>
       <c r="I24" s="492" t="n"/>
       <c r="J24" s="482" t="n"/>
@@ -3608,7 +3580,7 @@
       <c r="D25" s="599" t="n"/>
       <c r="E25" s="594" t="n"/>
       <c r="F25" s="496" t="n"/>
-      <c r="G25" s="496" t="n"/>
+      <c r="G25" s="718" t="n"/>
       <c r="H25" s="492" t="n"/>
       <c r="I25" s="492" t="n"/>
       <c r="J25" s="482" t="n"/>
@@ -3622,7 +3594,7 @@
       <c r="D26" s="599" t="n"/>
       <c r="E26" s="594" t="n"/>
       <c r="F26" s="496" t="n"/>
-      <c r="G26" s="496" t="n"/>
+      <c r="G26" s="718" t="n"/>
       <c r="H26" s="492" t="n"/>
       <c r="I26" s="492" t="n"/>
       <c r="J26" s="482" t="n"/>
@@ -3636,7 +3608,7 @@
       <c r="D27" s="599" t="n"/>
       <c r="E27" s="594" t="n"/>
       <c r="F27" s="496" t="n"/>
-      <c r="G27" s="496" t="n"/>
+      <c r="G27" s="718" t="n"/>
       <c r="H27" s="492" t="n"/>
       <c r="I27" s="492" t="n"/>
       <c r="J27" s="482" t="n"/>
@@ -3650,7 +3622,7 @@
       <c r="D28" s="599" t="n"/>
       <c r="E28" s="594" t="n"/>
       <c r="F28" s="496" t="n"/>
-      <c r="G28" s="496" t="n"/>
+      <c r="G28" s="718" t="n"/>
       <c r="H28" s="492" t="n"/>
       <c r="I28" s="492" t="n"/>
       <c r="J28" s="482" t="n"/>
@@ -3664,7 +3636,7 @@
       <c r="D29" s="599" t="n"/>
       <c r="E29" s="594" t="n"/>
       <c r="F29" s="496" t="n"/>
-      <c r="G29" s="496" t="n"/>
+      <c r="G29" s="718" t="n"/>
       <c r="H29" s="492" t="n"/>
       <c r="I29" s="492" t="n"/>
       <c r="J29" s="482" t="n"/>
@@ -3678,7 +3650,7 @@
       <c r="D30" s="602" t="n"/>
       <c r="E30" s="594" t="n"/>
       <c r="F30" s="496" t="n"/>
-      <c r="G30" s="496" t="n"/>
+      <c r="G30" s="718" t="n"/>
       <c r="H30" s="492" t="n"/>
       <c r="I30" s="492" t="n"/>
       <c r="J30" s="482" t="n"/>
@@ -3692,7 +3664,7 @@
       <c r="D31" s="604" t="n"/>
       <c r="E31" s="603" t="n"/>
       <c r="F31" s="496" t="n"/>
-      <c r="G31" s="496" t="n"/>
+      <c r="G31" s="718" t="n"/>
       <c r="H31" s="492" t="n"/>
       <c r="I31" s="492" t="n"/>
       <c r="J31" s="482" t="n"/>
@@ -3701,12 +3673,12 @@
     </row>
     <row r="32">
       <c r="A32" s="502" t="n"/>
-      <c r="B32" s="503" t="n"/>
-      <c r="C32" s="504" t="n"/>
-      <c r="D32" s="505" t="n"/>
-      <c r="E32" s="508" t="n"/>
-      <c r="F32" s="496" t="n"/>
-      <c r="G32" s="496" t="n"/>
+      <c r="B32" s="717" t="n"/>
+      <c r="C32" s="717" t="n"/>
+      <c r="D32" s="717" t="n"/>
+      <c r="E32" s="717" t="n"/>
+      <c r="F32" s="717" t="n"/>
+      <c r="G32" s="718" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="110" t="n"/>
@@ -3715,7 +3687,7 @@
       <c r="D33" s="184" t="n"/>
       <c r="E33" s="113" t="n"/>
       <c r="F33" s="496" t="n"/>
-      <c r="G33" s="496" t="n"/>
+      <c r="G33" s="718" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="672" t="inlineStr">
@@ -3728,7 +3700,7 @@
       <c r="D34" s="672" t="n"/>
       <c r="E34" s="672" t="n"/>
       <c r="F34" s="672" t="n"/>
-      <c r="G34" s="672" t="n"/>
+      <c r="G34" s="718" t="n"/>
     </row>
     <row r="35" ht="14.25" customHeight="1">
       <c r="A35" s="590" t="inlineStr">
@@ -4049,7 +4021,7 @@
           <t>9000 ед. в охвате — уточнить: подключение или предоплаченные пакеты? Цифры расходятся с Калугой.</t>
         </is>
       </c>
-      <c r="G48" s="704" t="n"/>
+      <c r="G48" s="718" t="n"/>
     </row>
     <row r="49" ht="36" customHeight="1">
       <c r="A49" s="714" t="n">
@@ -4080,7 +4052,7 @@
           <t>Крупные производители задают правила → возможность выхода на контрагентов.</t>
         </is>
       </c>
-      <c r="G49" s="704" t="n"/>
+      <c r="G49" s="718" t="n"/>
     </row>
     <row r="50" ht="36" customHeight="1">
       <c r="A50" s="714" t="n">
@@ -4111,7 +4083,7 @@
           <t>Задача О. Ремез — прописать подробнее после пересмотра встречи.</t>
         </is>
       </c>
-      <c r="G50" s="704" t="n"/>
+      <c r="G50" s="718" t="n"/>
     </row>
     <row r="51" ht="36" customHeight="1">
       <c r="A51" s="714" t="n">
@@ -4138,7 +4110,7 @@
         </is>
       </c>
       <c r="F51" s="724" t="inlineStr"/>
-      <c r="G51" s="704" t="n"/>
+      <c r="G51" s="718" t="n"/>
     </row>
     <row r="52" ht="36" customHeight="1">
       <c r="A52" s="714" t="n">
@@ -4169,7 +4141,7 @@
           <t>Саша спросит.</t>
         </is>
       </c>
-      <c r="G52" s="704" t="n"/>
+      <c r="G52" s="718" t="n"/>
     </row>
     <row r="53" ht="36" customHeight="1">
       <c r="A53" s="714" t="n">
@@ -4200,7 +4172,7 @@
           <t>С 01.10 демо = 14 дней; до 01.10 — 3 месяца бесплатно.</t>
         </is>
       </c>
-      <c r="G53" s="704" t="n"/>
+      <c r="G53" s="718" t="n"/>
     </row>
     <row r="54" ht="36" customHeight="1">
       <c r="A54" s="714" t="n">
@@ -4231,7 +4203,7 @@
           <t>Обсуждали накануне лектория с 1С.</t>
         </is>
       </c>
-      <c r="G54" s="704" t="n"/>
+      <c r="G54" s="718" t="n"/>
     </row>
     <row r="55" ht="36" customHeight="1">
       <c r="A55" s="714" t="n">
@@ -4258,7 +4230,7 @@
         </is>
       </c>
       <c r="F55" s="724" t="inlineStr"/>
-      <c r="G55" s="704" t="n"/>
+      <c r="G55" s="718" t="n"/>
     </row>
     <row r="56" ht="36" customHeight="1">
       <c r="A56" s="714" t="n">
@@ -4289,7 +4261,7 @@
           <t>Начать с крупных. Корп. сегмент продавал ЭПД даже в малом объёме.</t>
         </is>
       </c>
-      <c r="G56" s="704" t="n"/>
+      <c r="G56" s="718" t="n"/>
     </row>
     <row r="57" ht="36" customHeight="1">
       <c r="A57" s="714" t="n">
@@ -4320,7 +4292,7 @@
           <t>Задача по клиентам ЦАС (Доки).</t>
         </is>
       </c>
-      <c r="G57" s="704" t="n"/>
+      <c r="G57" s="718" t="n"/>
     </row>
     <row r="58" ht="36" customHeight="1">
       <c r="A58" s="714" t="n">
@@ -4351,7 +4323,7 @@
           <t>Клиенты сбытового офиса уходят на СБИС — разобрать причины.</t>
         </is>
       </c>
-      <c r="G58" s="704" t="n"/>
+      <c r="G58" s="718" t="n"/>
     </row>
     <row r="59" ht="36" customHeight="1">
       <c r="A59" s="714" t="n">
@@ -4382,7 +4354,7 @@
           <t>Связать со стратегией и целями.</t>
         </is>
       </c>
-      <c r="G59" s="704" t="n"/>
+      <c r="G59" s="718" t="n"/>
     </row>
     <row r="60" ht="36" customHeight="1">
       <c r="A60" s="714" t="n">
@@ -4413,672 +4385,1004 @@
           <t>Приоритет — количество клиентов, не сумма выручки на старте.</t>
         </is>
       </c>
-      <c r="G60" s="704" t="n"/>
-    </row>
-    <row r="61" ht="34.15" customHeight="1">
-      <c r="A61" s="589" t="inlineStr">
+      <c r="G60" s="718" t="n"/>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="714" t="n">
+        <v>14</v>
+      </c>
+      <c r="B61" s="712" t="inlineStr">
+        <is>
+          <t>Разобрать дубли тарифов у одного клиента (несколько мелких пакетов вместо одного крупного) и скорректировать скрипт</t>
+        </is>
+      </c>
+      <c r="C61" s="708" t="inlineStr">
+        <is>
+          <t>ЦКС / ЦП</t>
+        </is>
+      </c>
+      <c r="D61" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E61" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F61" s="724" t="inlineStr">
+        <is>
+          <t>Пример из статистики 1С — «Пчёлы свободные».</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="714" t="n">
+        <v>15</v>
+      </c>
+      <c r="B62" s="712" t="inlineStr">
+        <is>
+          <t>Уточнить целевое % соотношение базы: крупные / средние / мелкие (в т.ч. вариант 10/30/60) на основе анализа текущей базы</t>
+        </is>
+      </c>
+      <c r="C62" s="708" t="inlineStr">
+        <is>
+          <t>Все участники</t>
+        </is>
+      </c>
+      <c r="D62" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E62" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F62" s="724" t="inlineStr">
+        <is>
+          <t>Крупный = ещё и генератор трафика. Сейчас: 1 крупный, 8 средних.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="714" t="n">
+        <v>16</v>
+      </c>
+      <c r="B63" s="712" t="inlineStr">
+        <is>
+          <t>Проработать модель центра компетенций / аккаунтинга ЭПД (админ + продажи + забота/продление) и зону ЦКС vs ЦП</t>
+        </is>
+      </c>
+      <c r="C63" s="708" t="inlineStr">
+        <is>
+          <t>ЦКС / ЦП</t>
+        </is>
+      </c>
+      <c r="D63" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E63" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F63" s="724" t="inlineStr">
+        <is>
+          <t>Цель: пользование сервисом + своевременное пополнение баланса; допродажа УАТ — по выгрузке ЦП.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="714" t="n">
+        <v>17</v>
+      </c>
+      <c r="B64" s="712" t="inlineStr">
+        <is>
+          <t>Зафиксировать сценарий выхаживания демо-клиентов (еженедельный контроль активности / звонки раз в 2 недели)</t>
+        </is>
+      </c>
+      <c r="C64" s="708" t="inlineStr">
+        <is>
+          <t>ЦКС / ответственный</t>
+        </is>
+      </c>
+      <c r="D64" s="722" t="inlineStr">
+        <is>
+          <t>до след. встречи</t>
+        </is>
+      </c>
+      <c r="E64" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F64" s="724" t="inlineStr">
+        <is>
+          <t>Определить, кто выхаживает: МПП, ЦКС или выделенный человек.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="714" t="n">
+        <v>18</v>
+      </c>
+      <c r="B65" s="712" t="inlineStr">
+        <is>
+          <t>SMM/PR: системный план до конца года — статьи/SEO, вебинары с 1С/Калугой раз в месяц, кейсы и CTA в постах</t>
+        </is>
+      </c>
+      <c r="C65" s="708" t="inlineStr">
+        <is>
+          <t>PR / ЦСВ</t>
+        </is>
+      </c>
+      <c r="D65" s="722" t="inlineStr">
+        <is>
+          <t>сентябрь–декабрь</t>
+        </is>
+      </c>
+      <c r="E65" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F65" s="724" t="inlineStr">
+        <is>
+          <t>Точечные запросы контента — Вике. Материалы для менеджеров на сентябрь.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="714" t="n">
+        <v>19</v>
+      </c>
+      <c r="B66" s="712" t="inlineStr">
+        <is>
+          <t>Доработать и запустить сентябрьскую акцию «экстренное подключение» (механика, каналы, материалы)</t>
+        </is>
+      </c>
+      <c r="C66" s="708" t="inlineStr">
+        <is>
+          <t>PR / ЦП</t>
+        </is>
+      </c>
+      <c r="D66" s="722" t="inlineStr">
+        <is>
+          <t>начало сентября</t>
+        </is>
+      </c>
+      <c r="E66" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F66" s="724" t="inlineStr">
+        <is>
+          <t>Соцсети + рассылка + менеджеры. Если к 01.09 — готовить сразу.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="714" t="n">
+        <v>20</v>
+      </c>
+      <c r="B67" s="712" t="inlineStr">
+        <is>
+          <t>Проверить статус партнёра по ЭПД; отобрать внедрённые решения для публикации + оценка удовлетворённости по базе ~143</t>
+        </is>
+      </c>
+      <c r="C67" s="708" t="inlineStr">
+        <is>
+          <t>Юля / PR</t>
+        </is>
+      </c>
+      <c r="D67" s="722" t="inlineStr">
+        <is>
+          <t>сентябрь</t>
+        </is>
+      </c>
+      <c r="E67" s="723" t="inlineStr">
+        <is>
+          <t>в работе</t>
+        </is>
+      </c>
+      <c r="F67" s="724" t="inlineStr">
+        <is>
+          <t>Статус — инфоповод для контента.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="48" customHeight="1">
+      <c r="A68" s="589" t="inlineStr">
         <is>
           <t>3. Обсуждаемые темы и выводы:</t>
         </is>
       </c>
-      <c r="B61" s="717" t="n"/>
-      <c r="C61" s="717" t="n"/>
-      <c r="D61" s="717" t="n"/>
-      <c r="E61" s="717" t="n"/>
-      <c r="F61" s="717" t="n"/>
-      <c r="G61" s="718" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="726" t="inlineStr">
+      <c r="B68" s="717" t="n"/>
+      <c r="C68" s="718" t="n"/>
+      <c r="D68" s="717" t="n"/>
+      <c r="E68" s="717" t="n"/>
+      <c r="F68" s="717" t="n"/>
+      <c r="G68" s="718" t="n"/>
+    </row>
+    <row r="69" ht="48" customHeight="1">
+      <c r="A69" s="726" t="inlineStr">
         <is>
           <t>Обсуждаемая тема (проблема)</t>
         </is>
       </c>
-      <c r="B62" s="713" t="n"/>
-      <c r="C62" s="713" t="n"/>
-      <c r="D62" s="726" t="inlineStr">
+      <c r="B69" s="717" t="n"/>
+      <c r="C69" s="718" t="n"/>
+      <c r="D69" s="726" t="inlineStr">
         <is>
           <t>Выводы и решения</t>
         </is>
       </c>
-      <c r="E62" s="713" t="n"/>
-      <c r="F62" s="713" t="n"/>
-      <c r="G62" s="713" t="n"/>
-      <c r="H62" s="727" t="n"/>
-      <c r="I62" s="727" t="n"/>
-    </row>
-    <row r="63" ht="18" customHeight="1">
-      <c r="A63" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Акция и ЦСВ</t>
-        </is>
-      </c>
-      <c r="B63" s="698" t="n"/>
-      <c r="C63" s="698" t="n"/>
-      <c r="D63" s="698" t="n"/>
-      <c r="E63" s="698" t="n"/>
-      <c r="F63" s="698" t="n"/>
-      <c r="G63" s="698" t="n"/>
-      <c r="H63" s="727" t="n"/>
-      <c r="I63" s="727" t="n"/>
-    </row>
-    <row r="64" ht="48" customHeight="1">
-      <c r="A64" s="724" t="inlineStr">
-        <is>
-          <t>Обсудить с ЦСВ трудозатраты на акцию по ЭПД.</t>
-        </is>
-      </c>
-      <c r="B64" s="704" t="n"/>
-      <c r="C64" s="704" t="n"/>
-      <c r="D64" s="724" t="inlineStr">
-        <is>
-          <t>Оксана: уточнить адресата вопроса. Акцию продлили до 30.09.</t>
-        </is>
-      </c>
-      <c r="E64" s="704" t="n"/>
-      <c r="F64" s="704" t="n"/>
-      <c r="G64" s="704" t="n"/>
-      <c r="H64" s="727" t="n"/>
-      <c r="I64" s="727" t="n"/>
-    </row>
-    <row r="65" ht="18" customHeight="1">
-      <c r="A65" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Каналы МАКС / ТГ / ВК</t>
-        </is>
-      </c>
-      <c r="B65" s="698" t="n"/>
-      <c r="C65" s="698" t="n"/>
-      <c r="D65" s="698" t="n"/>
-      <c r="E65" s="698" t="n"/>
-      <c r="F65" s="698" t="n"/>
-      <c r="G65" s="698" t="n"/>
-      <c r="H65" s="727" t="n"/>
-      <c r="I65" s="727" t="n"/>
-    </row>
-    <row r="66" ht="48" customHeight="1">
-      <c r="A66" s="724" t="inlineStr">
-        <is>
-          <t>Канал ЭПД в МАКС, ТГ, ВК. Можем ли прорабатывать этих клиентов силами ЦП и ЦКС? Связать со стратегией; альтернативный канал привлечения.</t>
-        </is>
-      </c>
-      <c r="B66" s="704" t="n"/>
-      <c r="C66" s="704" t="n"/>
-      <c r="D66" s="724" t="inlineStr">
-        <is>
-          <t>Проверить из базы: подключён клиент к каналу или нет. Идея — просить менеджеров подключать клиентов (вопрос мотивации клиента открыт).</t>
-        </is>
-      </c>
-      <c r="E66" s="704" t="n"/>
-      <c r="F66" s="704" t="n"/>
-      <c r="G66" s="704" t="n"/>
-      <c r="H66" s="727" t="n"/>
-      <c r="I66" s="727" t="n"/>
-    </row>
-    <row r="67" ht="18" customHeight="1">
-      <c r="A67" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Стратегия и сегментация</t>
-        </is>
-      </c>
-      <c r="B67" s="698" t="n"/>
-      <c r="C67" s="698" t="n"/>
-      <c r="D67" s="698" t="n"/>
-      <c r="E67" s="698" t="n"/>
-      <c r="F67" s="698" t="n"/>
-      <c r="G67" s="698" t="n"/>
-      <c r="H67" s="727" t="n"/>
-      <c r="I67" s="727" t="n"/>
-    </row>
-    <row r="68" ht="48" customHeight="1">
-      <c r="A68" s="724" t="inlineStr">
-        <is>
-          <t>Заход в Элиттрейд (таблица А. Дворяк) — выход к контрагентам. Предложение Гуркова: сегментировать охваченных на крупных / средних / мелких.</t>
-        </is>
-      </c>
-      <c r="B68" s="704" t="n"/>
-      <c r="C68" s="704" t="n"/>
-      <c r="D68" s="729" t="inlineStr">
-        <is>
-          <t>Производители (крупные) задают правила для перевозчиков → те для получателей. Лиза уточнит у Суворовой статус Элиттрейд; можно предложить акцию 3 мес. Доки.</t>
-        </is>
-      </c>
-      <c r="E68" s="730" t="n"/>
-      <c r="F68" s="730" t="n"/>
-      <c r="G68" s="730" t="n"/>
-      <c r="H68" s="727" t="n"/>
-      <c r="I68" s="727" t="n"/>
-    </row>
-    <row r="69" ht="48" customHeight="1">
-      <c r="A69" s="724" t="inlineStr">
-        <is>
-          <t>К признаку «крупный» добавить: является ли клиент генератором трафика (привлечение контрагентов).</t>
-        </is>
-      </c>
-      <c r="B69" s="704" t="n"/>
-      <c r="C69" s="704" t="n"/>
-      <c r="D69" s="724" t="inlineStr">
-        <is>
-          <t>По соотношению базы (крупные / средние / мелкие) пришли к соглашению по процентам.</t>
-        </is>
-      </c>
-      <c r="E69" s="704" t="n"/>
-      <c r="F69" s="704" t="n"/>
-      <c r="G69" s="704" t="n"/>
+      <c r="E69" s="717" t="n"/>
+      <c r="F69" s="717" t="n"/>
+      <c r="G69" s="718" t="n"/>
       <c r="H69" s="727" t="n"/>
       <c r="I69" s="727" t="n"/>
     </row>
     <row r="70" ht="48" customHeight="1">
-      <c r="A70" s="724" t="inlineStr">
-        <is>
-          <t>Приоритет — количество привлечённых клиентов, а не сумма заработка. Выстроить цепочку «закрепления» и почкования с одного пакета на новых клиентов.</t>
-        </is>
-      </c>
-      <c r="B70" s="704" t="n"/>
-      <c r="C70" s="704" t="n"/>
-      <c r="D70" s="729" t="inlineStr">
-        <is>
-          <t>ПЛАН: 500 клиентов до конца 2026 → 50 крупных + 300 средних + 150 мелких.</t>
-        </is>
-      </c>
-      <c r="E70" s="730" t="n"/>
-      <c r="F70" s="730" t="n"/>
-      <c r="G70" s="730" t="n"/>
+      <c r="A70" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Акция и ЦСВ</t>
+        </is>
+      </c>
+      <c r="B70" s="717" t="n"/>
+      <c r="C70" s="717" t="n"/>
+      <c r="D70" s="717" t="n"/>
+      <c r="E70" s="717" t="n"/>
+      <c r="F70" s="717" t="n"/>
+      <c r="G70" s="718" t="n"/>
       <c r="H70" s="727" t="n"/>
       <c r="I70" s="727" t="n"/>
     </row>
     <row r="71" ht="18" customHeight="1">
-      <c r="A71" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Доки.Логистика и охват</t>
-        </is>
-      </c>
-      <c r="B71" s="698" t="n"/>
-      <c r="C71" s="698" t="n"/>
-      <c r="D71" s="698" t="n"/>
-      <c r="E71" s="698" t="n"/>
-      <c r="F71" s="698" t="n"/>
-      <c r="G71" s="698" t="n"/>
+      <c r="A71" s="724" t="inlineStr">
+        <is>
+          <t>Обсудить с ЦСВ трудозатраты на акцию по ЭПД.</t>
+        </is>
+      </c>
+      <c r="B71" s="717" t="n"/>
+      <c r="C71" s="718" t="n"/>
+      <c r="D71" s="724" t="inlineStr">
+        <is>
+          <t>Оксана: уточнить адресата вопроса. Акцию продлили до 30.09.</t>
+        </is>
+      </c>
+      <c r="E71" s="717" t="n"/>
+      <c r="F71" s="717" t="n"/>
+      <c r="G71" s="718" t="n"/>
       <c r="H71" s="727" t="n"/>
       <c r="I71" s="727" t="n"/>
     </row>
     <row r="72" ht="48" customHeight="1">
-      <c r="A72" s="724" t="inlineStr">
-        <is>
-          <t>Задача по Доки.Логистика (Оксана Ремез) — прописать подробнее после пересмотра встречи.</t>
-        </is>
-      </c>
-      <c r="B72" s="704" t="n"/>
-      <c r="C72" s="704" t="n"/>
-      <c r="D72" s="729" t="inlineStr">
-        <is>
-          <t>Подключить Антона Гуркова к изучению привязки клиента. Антон взял на себя.</t>
-        </is>
-      </c>
-      <c r="E72" s="730" t="n"/>
-      <c r="F72" s="730" t="n"/>
-      <c r="G72" s="730" t="n"/>
+      <c r="A72" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Каналы МАКС / ТГ / ВК</t>
+        </is>
+      </c>
+      <c r="B72" s="717" t="n"/>
+      <c r="C72" s="717" t="n"/>
+      <c r="D72" s="717" t="n"/>
+      <c r="E72" s="717" t="n"/>
+      <c r="F72" s="717" t="n"/>
+      <c r="G72" s="718" t="n"/>
       <c r="H72" s="727" t="n"/>
       <c r="I72" s="727" t="n"/>
     </row>
     <row r="73" ht="48" customHeight="1">
       <c r="A73" s="724" t="inlineStr">
         <is>
-          <t>Можем ли отследить активность клиента в сервисе Доки? (вопрос Калуге)</t>
-        </is>
-      </c>
-      <c r="B73" s="704" t="n"/>
-      <c r="C73" s="704" t="n"/>
-      <c r="D73" s="729" t="inlineStr">
-        <is>
-          <t>Маша Дивакова выяснит.</t>
-        </is>
-      </c>
-      <c r="E73" s="730" t="n"/>
-      <c r="F73" s="730" t="n"/>
-      <c r="G73" s="730" t="n"/>
+          <t>Канал ЭПД в МАКС, ТГ, ВК. Можем ли прорабатывать этих клиентов силами ЦП и ЦКС? Связать со стратегией; альтернативный канал привлечения.</t>
+        </is>
+      </c>
+      <c r="B73" s="717" t="n"/>
+      <c r="C73" s="718" t="n"/>
+      <c r="D73" s="724" t="inlineStr">
+        <is>
+          <t>Проверить из базы: подключён клиент к каналу или нет. Идея — просить менеджеров подключать клиентов (вопрос мотивации клиента открыт).</t>
+        </is>
+      </c>
+      <c r="E73" s="717" t="n"/>
+      <c r="F73" s="717" t="n"/>
+      <c r="G73" s="718" t="n"/>
       <c r="H73" s="727" t="n"/>
       <c r="I73" s="727" t="n"/>
     </row>
     <row r="74" ht="48" customHeight="1">
-      <c r="A74" s="724" t="inlineStr">
-        <is>
-          <t>Считается ли Доки в охват сервисами ЭПД?</t>
-        </is>
-      </c>
-      <c r="B74" s="704" t="n"/>
-      <c r="C74" s="704" t="n"/>
-      <c r="D74" s="729" t="inlineStr">
-        <is>
-          <t>Вопрос Никитченко — Саша спросит. Цифры расходятся с Калугой; проблемы с закреплением.</t>
-        </is>
-      </c>
-      <c r="E74" s="730" t="n"/>
-      <c r="F74" s="730" t="n"/>
-      <c r="G74" s="730" t="n"/>
+      <c r="A74" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Стратегия и сегментация</t>
+        </is>
+      </c>
+      <c r="B74" s="717" t="n"/>
+      <c r="C74" s="717" t="n"/>
+      <c r="D74" s="717" t="n"/>
+      <c r="E74" s="717" t="n"/>
+      <c r="F74" s="717" t="n"/>
+      <c r="G74" s="718" t="n"/>
       <c r="H74" s="727" t="n"/>
       <c r="I74" s="727" t="n"/>
     </row>
     <row r="75" ht="48" customHeight="1">
       <c r="A75" s="724" t="inlineStr">
         <is>
-          <t>Все проданные ЭПД: центр компетенции изучает — всё ли продано, подключились ли.</t>
-        </is>
-      </c>
-      <c r="B75" s="704" t="n"/>
-      <c r="C75" s="704" t="n"/>
-      <c r="D75" s="724" t="inlineStr">
-        <is>
-          <t>Трафик не видим → не квалифицируем активность пользования пакетом. 1С обещают данные в сентябре.</t>
-        </is>
-      </c>
-      <c r="E75" s="704" t="n"/>
-      <c r="F75" s="704" t="n"/>
-      <c r="G75" s="704" t="n"/>
+          <t>Заход в Элиттрейд (таблица А. Дворяк) — выход к контрагентам. Предложение Гуркова: сегментировать охваченных на крупных / средних / мелких.</t>
+        </is>
+      </c>
+      <c r="B75" s="717" t="n"/>
+      <c r="C75" s="718" t="n"/>
+      <c r="D75" s="729" t="inlineStr">
+        <is>
+          <t>Производители (крупные) задают правила для перевозчиков → те для получателей. Лиза уточнит у Суворовой статус Элиттрейд; можно предложить акцию 3 мес. Доки.</t>
+        </is>
+      </c>
+      <c r="E75" s="717" t="n"/>
+      <c r="F75" s="717" t="n"/>
+      <c r="G75" s="718" t="n"/>
       <c r="H75" s="727" t="n"/>
       <c r="I75" s="727" t="n"/>
     </row>
     <row r="76" ht="18" customHeight="1">
-      <c r="A76" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Демо и прогрев (СМАК)</t>
-        </is>
-      </c>
-      <c r="B76" s="698" t="n"/>
-      <c r="C76" s="698" t="n"/>
-      <c r="D76" s="698" t="n"/>
-      <c r="E76" s="698" t="n"/>
-      <c r="F76" s="698" t="n"/>
-      <c r="G76" s="698" t="n"/>
+      <c r="A76" s="724" t="inlineStr">
+        <is>
+          <t>К признаку «крупный» добавить: является ли клиент генератором трафика (привлечение контрагентов).</t>
+        </is>
+      </c>
+      <c r="B76" s="717" t="n"/>
+      <c r="C76" s="718" t="n"/>
+      <c r="D76" s="724" t="inlineStr">
+        <is>
+          <t>По соотношению базы (крупные / средние / мелкие) пришли к соглашению по процентам.</t>
+        </is>
+      </c>
+      <c r="E76" s="717" t="n"/>
+      <c r="F76" s="717" t="n"/>
+      <c r="G76" s="718" t="n"/>
       <c r="H76" s="727" t="n"/>
       <c r="I76" s="727" t="n"/>
     </row>
     <row r="77" ht="48" customHeight="1">
       <c r="A77" s="724" t="inlineStr">
         <is>
-          <t>Со СМАК подготовить материалы для прогрева клиента во время демо-доступа.</t>
-        </is>
-      </c>
-      <c r="B77" s="704" t="n"/>
-      <c r="C77" s="704" t="n"/>
-      <c r="D77" s="724" t="inlineStr">
-        <is>
-          <t>С 01.10 — 14 дней демо; до 01.10 — 3 месяца бесплатно.</t>
-        </is>
-      </c>
-      <c r="E77" s="704" t="n"/>
-      <c r="F77" s="704" t="n"/>
-      <c r="G77" s="704" t="n"/>
+          <t>Приоритет — количество привлечённых клиентов, а не сумма заработка. Выстроить цепочку «закрепления» и почкования с одного пакета на новых клиентов.</t>
+        </is>
+      </c>
+      <c r="B77" s="717" t="n"/>
+      <c r="C77" s="718" t="n"/>
+      <c r="D77" s="729" t="inlineStr">
+        <is>
+          <t>ПЛАН: 500 клиентов до конца 2026 → 50 крупных + 300 средних + 150 мелких.</t>
+        </is>
+      </c>
+      <c r="E77" s="717" t="n"/>
+      <c r="F77" s="717" t="n"/>
+      <c r="G77" s="718" t="n"/>
       <c r="H77" s="727" t="n"/>
       <c r="I77" s="727" t="n"/>
     </row>
     <row r="78" ht="18" customHeight="1">
       <c r="A78" s="728" t="inlineStr">
         <is>
-          <t>Блок: Сопровождение МПП / ЦКС</t>
-        </is>
-      </c>
-      <c r="B78" s="698" t="n"/>
-      <c r="C78" s="698" t="n"/>
-      <c r="D78" s="698" t="n"/>
-      <c r="E78" s="698" t="n"/>
-      <c r="F78" s="698" t="n"/>
-      <c r="G78" s="698" t="n"/>
+          <t>Блок: Доки.Логистика и охват</t>
+        </is>
+      </c>
+      <c r="B78" s="717" t="n"/>
+      <c r="C78" s="717" t="n"/>
+      <c r="D78" s="717" t="n"/>
+      <c r="E78" s="717" t="n"/>
+      <c r="F78" s="717" t="n"/>
+      <c r="G78" s="718" t="n"/>
       <c r="H78" s="727" t="n"/>
       <c r="I78" s="727" t="n"/>
     </row>
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="724" t="inlineStr">
         <is>
-          <t>План для МПП: платные / бесплатные клиенты; «выхаживать» может другой человек (идея — Антон Гурков).</t>
-        </is>
-      </c>
-      <c r="B79" s="704" t="n"/>
-      <c r="C79" s="704" t="n"/>
-      <c r="D79" s="724" t="inlineStr">
-        <is>
-          <t>Если есть ИТС — менеджер ЦКС смотрит динамику расхода ЭПД/Доки. Трафика пока нет; можно писать в Калугу с перечнем ИНН. Риск: кто выхаживает — текущие менеджеры или новый человек?</t>
-        </is>
-      </c>
-      <c r="E79" s="704" t="n"/>
-      <c r="F79" s="704" t="n"/>
-      <c r="G79" s="704" t="n"/>
+          <t>Задача по Доки.Логистика (Оксана Ремез) — прописать подробнее после пересмотра встречи.</t>
+        </is>
+      </c>
+      <c r="B79" s="717" t="n"/>
+      <c r="C79" s="718" t="n"/>
+      <c r="D79" s="729" t="inlineStr">
+        <is>
+          <t>Подключить Антона Гуркова к изучению привязки клиента. Антон взял на себя.</t>
+        </is>
+      </c>
+      <c r="E79" s="717" t="n"/>
+      <c r="F79" s="717" t="n"/>
+      <c r="G79" s="718" t="n"/>
       <c r="H79" s="727" t="n"/>
       <c r="I79" s="727" t="n"/>
     </row>
     <row r="80" ht="48" customHeight="1">
       <c r="A80" s="724" t="inlineStr">
         <is>
-          <t>Клиенту продают минимальный пакет («пока не понятно»). Кто ведёт дальше при продлении? Получают ли ЦКС сигнал о дозакупке титулов?</t>
-        </is>
-      </c>
-      <c r="B80" s="704" t="n"/>
-      <c r="C80" s="704" t="n"/>
-      <c r="D80" s="724" t="inlineStr">
-        <is>
-          <t>По логике — ЦКС. Нужен калькулятор — Вика с Машей обсуждали накануне лектория с 1С.</t>
-        </is>
-      </c>
-      <c r="E80" s="704" t="n"/>
-      <c r="F80" s="704" t="n"/>
-      <c r="G80" s="704" t="n"/>
+          <t>Можем ли отследить активность клиента в сервисе Доки? (вопрос Калуге)</t>
+        </is>
+      </c>
+      <c r="B80" s="717" t="n"/>
+      <c r="C80" s="718" t="n"/>
+      <c r="D80" s="729" t="inlineStr">
+        <is>
+          <t>Маша Дивакова выяснит.</t>
+        </is>
+      </c>
+      <c r="E80" s="717" t="n"/>
+      <c r="F80" s="717" t="n"/>
+      <c r="G80" s="718" t="n"/>
       <c r="H80" s="727" t="n"/>
       <c r="I80" s="727" t="n"/>
     </row>
     <row r="81" ht="48" customHeight="1">
       <c r="A81" s="724" t="inlineStr">
         <is>
-          <t>Ожидание: ЦКС категоризирует клиента по кол-ву титулов / УАТ и своевременно пополняет баланс.</t>
-        </is>
-      </c>
-      <c r="B81" s="704" t="n"/>
-      <c r="C81" s="704" t="n"/>
-      <c r="D81" s="724" t="inlineStr">
-        <is>
-          <t>Зафиксировано как рабочий процесс.</t>
-        </is>
-      </c>
-      <c r="E81" s="704" t="n"/>
-      <c r="F81" s="704" t="n"/>
-      <c r="G81" s="704" t="n"/>
+          <t>Считается ли Доки в охват сервисами ЭПД?</t>
+        </is>
+      </c>
+      <c r="B81" s="717" t="n"/>
+      <c r="C81" s="718" t="n"/>
+      <c r="D81" s="729" t="inlineStr">
+        <is>
+          <t>Вопрос Никитченко — Саша спросит. Цифры расходятся с Калугой; проблемы с закреплением.</t>
+        </is>
+      </c>
+      <c r="E81" s="717" t="n"/>
+      <c r="F81" s="717" t="n"/>
+      <c r="G81" s="718" t="n"/>
       <c r="H81" s="727" t="n"/>
       <c r="I81" s="727" t="n"/>
     </row>
     <row r="82" ht="18" customHeight="1">
-      <c r="A82" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Тандем и обзвоны</t>
-        </is>
-      </c>
-      <c r="B82" s="698" t="n"/>
-      <c r="C82" s="698" t="n"/>
-      <c r="D82" s="698" t="n"/>
-      <c r="E82" s="698" t="n"/>
-      <c r="F82" s="698" t="n"/>
-      <c r="G82" s="698" t="n"/>
+      <c r="A82" s="724" t="inlineStr">
+        <is>
+          <t>Все проданные ЭПД: центр компетенции изучает — всё ли продано, подключились ли.</t>
+        </is>
+      </c>
+      <c r="B82" s="717" t="n"/>
+      <c r="C82" s="718" t="n"/>
+      <c r="D82" s="724" t="inlineStr">
+        <is>
+          <t>Трафик не видим → не квалифицируем активность пользования пакетом. 1С обещают данные в сентябре.</t>
+        </is>
+      </c>
+      <c r="E82" s="717" t="n"/>
+      <c r="F82" s="717" t="n"/>
+      <c r="G82" s="718" t="n"/>
       <c r="H82" s="727" t="n"/>
       <c r="I82" s="727" t="n"/>
     </row>
     <row r="83" ht="48" customHeight="1">
-      <c r="A83" s="724" t="inlineStr">
-        <is>
-          <t>Рассылка по клиентам: «проверьте своего контрагента и впишите в тандем».</t>
-        </is>
-      </c>
-      <c r="B83" s="704" t="n"/>
-      <c r="C83" s="704" t="n"/>
-      <c r="D83" s="729" t="inlineStr">
-        <is>
-          <t>Лиза — когда и какой текст.</t>
-        </is>
-      </c>
-      <c r="E83" s="730" t="n"/>
-      <c r="F83" s="730" t="n"/>
-      <c r="G83" s="730" t="n"/>
+      <c r="A83" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Демо и прогрев (СМАК)</t>
+        </is>
+      </c>
+      <c r="B83" s="717" t="n"/>
+      <c r="C83" s="717" t="n"/>
+      <c r="D83" s="717" t="n"/>
+      <c r="E83" s="717" t="n"/>
+      <c r="F83" s="717" t="n"/>
+      <c r="G83" s="718" t="n"/>
       <c r="H83" s="727" t="n"/>
       <c r="I83" s="727" t="n"/>
     </row>
     <row r="84" ht="48" customHeight="1">
       <c r="A84" s="724" t="inlineStr">
         <is>
-          <t>Начать с крупных клиентов: прозвонить и предложить подключить контрагента в ЭПД ТАНДЕМ.</t>
-        </is>
-      </c>
-      <c r="B84" s="704" t="n"/>
-      <c r="C84" s="704" t="n"/>
+          <t>Со СМАК подготовить материалы для прогрева клиента во время демо-доступа.</t>
+        </is>
+      </c>
+      <c r="B84" s="717" t="n"/>
+      <c r="C84" s="718" t="n"/>
       <c r="D84" s="724" t="inlineStr">
         <is>
-          <t>Крупные = от 2000 титулов. Корп. клиенты продавали ЭПД даже в малом объёме.</t>
-        </is>
-      </c>
-      <c r="E84" s="704" t="n"/>
-      <c r="F84" s="704" t="n"/>
-      <c r="G84" s="704" t="n"/>
+          <t>С 01.10 — 14 дней демо; до 01.10 — 3 месяца бесплатно.</t>
+        </is>
+      </c>
+      <c r="E84" s="717" t="n"/>
+      <c r="F84" s="717" t="n"/>
+      <c r="G84" s="718" t="n"/>
       <c r="H84" s="727" t="n"/>
       <c r="I84" s="727" t="n"/>
     </row>
     <row r="85" ht="48" customHeight="1">
-      <c r="A85" s="724" t="inlineStr">
-        <is>
-          <t>Обзвон подключённых клиентов: оценка удовлетворённости + проекты ЦАС (Доки).</t>
-        </is>
-      </c>
-      <c r="B85" s="704" t="n"/>
-      <c r="C85" s="704" t="n"/>
-      <c r="D85" s="729" t="inlineStr">
-        <is>
-          <t>Задача на Сашу Дворяк / Лазарчук — клиенты ЦАС.</t>
-        </is>
-      </c>
-      <c r="E85" s="730" t="n"/>
-      <c r="F85" s="730" t="n"/>
-      <c r="G85" s="730" t="n"/>
+      <c r="A85" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Сопровождение МПП / ЦКС</t>
+        </is>
+      </c>
+      <c r="B85" s="717" t="n"/>
+      <c r="C85" s="717" t="n"/>
+      <c r="D85" s="717" t="n"/>
+      <c r="E85" s="717" t="n"/>
+      <c r="F85" s="717" t="n"/>
+      <c r="G85" s="718" t="n"/>
       <c r="H85" s="727" t="n"/>
       <c r="I85" s="727" t="n"/>
     </row>
     <row r="86" ht="18" customHeight="1">
-      <c r="A86" s="728" t="inlineStr">
-        <is>
-          <t>Блок: Корп. сегмент / сбытовой офис</t>
-        </is>
-      </c>
-      <c r="B86" s="698" t="n"/>
-      <c r="C86" s="698" t="n"/>
-      <c r="D86" s="698" t="n"/>
-      <c r="E86" s="698" t="n"/>
-      <c r="F86" s="698" t="n"/>
-      <c r="G86" s="698" t="n"/>
+      <c r="A86" s="724" t="inlineStr">
+        <is>
+          <t>План для МПП: платные / бесплатные клиенты; «выхаживать» может другой человек (идея — Антон Гурков).</t>
+        </is>
+      </c>
+      <c r="B86" s="717" t="n"/>
+      <c r="C86" s="718" t="n"/>
+      <c r="D86" s="724" t="inlineStr">
+        <is>
+          <t>Если есть ИТС — менеджер ЦКС смотрит динамику расхода ЭПД/Доки. Трафика пока нет; можно писать в Калугу с перечнем ИНН. Риск: кто выхаживает — текущие менеджеры или новый человек?</t>
+        </is>
+      </c>
+      <c r="E86" s="717" t="n"/>
+      <c r="F86" s="717" t="n"/>
+      <c r="G86" s="718" t="n"/>
       <c r="H86" s="727" t="n"/>
       <c r="I86" s="727" t="n"/>
     </row>
     <row r="87" ht="48" customHeight="1">
       <c r="A87" s="724" t="inlineStr">
         <is>
-          <t>Почему клиенты сбытового офиса не переходят в ЭПД / уходят на СБИС?</t>
-        </is>
-      </c>
-      <c r="B87" s="704" t="n"/>
-      <c r="C87" s="704" t="n"/>
-      <c r="D87" s="729" t="inlineStr">
-        <is>
-          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в 1-ю неделю сентября (Юлиана).</t>
-        </is>
-      </c>
-      <c r="E87" s="730" t="n"/>
-      <c r="F87" s="730" t="n"/>
-      <c r="G87" s="730" t="n"/>
+          <t>Клиенту продают минимальный пакет («пока не понятно»). Кто ведёт дальше при продлении? Получают ли ЦКС сигнал о дозакупке титулов?</t>
+        </is>
+      </c>
+      <c r="B87" s="717" t="n"/>
+      <c r="C87" s="718" t="n"/>
+      <c r="D87" s="724" t="inlineStr">
+        <is>
+          <t>По логике — ЦКС. Нужен калькулятор — Вика с Машей обсуждали накануне лектория с 1С.</t>
+        </is>
+      </c>
+      <c r="E87" s="717" t="n"/>
+      <c r="F87" s="717" t="n"/>
+      <c r="G87" s="718" t="n"/>
       <c r="H87" s="727" t="n"/>
       <c r="I87" s="727" t="n"/>
     </row>
     <row r="88" ht="48" customHeight="1">
       <c r="A88" s="724" t="inlineStr">
         <is>
-          <t>Юля: предлагать всем клиентам бесплатно Доки (дублирующий сервис) на 3 мес.; KPI менеджерам на сентябрь.</t>
-        </is>
-      </c>
-      <c r="B88" s="704" t="n"/>
-      <c r="C88" s="704" t="n"/>
+          <t>Ожидание: ЦКС категоризирует клиента по кол-ву титулов / УАТ и своевременно пополняет баланс.</t>
+        </is>
+      </c>
+      <c r="B88" s="717" t="n"/>
+      <c r="C88" s="718" t="n"/>
       <c r="D88" s="724" t="inlineStr">
         <is>
-          <t>Зафиксировано как предложение.</t>
-        </is>
-      </c>
-      <c r="E88" s="704" t="n"/>
-      <c r="F88" s="704" t="n"/>
-      <c r="G88" s="704" t="n"/>
+          <t>Зафиксировано как рабочий процесс.</t>
+        </is>
+      </c>
+      <c r="E88" s="717" t="n"/>
+      <c r="F88" s="717" t="n"/>
+      <c r="G88" s="718" t="n"/>
       <c r="H88" s="727" t="n"/>
       <c r="I88" s="727" t="n"/>
     </row>
-    <row r="89">
-      <c r="A89" s="710" t="inlineStr">
-        <is>
-          <t>Подсветка выводов: строки с поручениями/задачами выделены мягким оранжевым. Поставленные задачи продублированы в блоке «2. Решения текущей встречи».</t>
-        </is>
-      </c>
-      <c r="B89" s="698" t="n"/>
-      <c r="C89" s="698" t="n"/>
-      <c r="D89" s="698" t="n"/>
-      <c r="E89" s="698" t="n"/>
-      <c r="F89" s="698" t="n"/>
-      <c r="G89" s="698" t="n"/>
+    <row r="89" ht="18" customHeight="1">
+      <c r="A89" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Тандем и обзвоны</t>
+        </is>
+      </c>
+      <c r="B89" s="717" t="n"/>
+      <c r="C89" s="717" t="n"/>
+      <c r="D89" s="717" t="n"/>
+      <c r="E89" s="717" t="n"/>
+      <c r="F89" s="717" t="n"/>
+      <c r="G89" s="718" t="n"/>
       <c r="H89" s="727" t="n"/>
       <c r="I89" s="727" t="n"/>
     </row>
-    <row r="90">
-      <c r="A90" s="727" t="n"/>
+    <row r="90" ht="52" customHeight="1">
+      <c r="A90" s="724" t="inlineStr">
+        <is>
+          <t>Рассылка по клиентам: «проверьте своего контрагента и впишите в тандем».</t>
+        </is>
+      </c>
       <c r="B90" s="717" t="n"/>
       <c r="C90" s="718" t="n"/>
-      <c r="D90" s="727" t="n"/>
-      <c r="E90" s="727" t="n"/>
-      <c r="F90" s="727" t="n"/>
-      <c r="G90" s="727" t="n"/>
+      <c r="D90" s="729" t="inlineStr">
+        <is>
+          <t>Лиза — когда и какой текст.</t>
+        </is>
+      </c>
+      <c r="E90" s="717" t="n"/>
+      <c r="F90" s="717" t="n"/>
+      <c r="G90" s="718" t="n"/>
       <c r="H90" s="727" t="n"/>
       <c r="I90" s="727" t="n"/>
     </row>
-    <row r="91">
-      <c r="A91" s="727" t="n"/>
+    <row r="91" ht="52" customHeight="1">
+      <c r="A91" s="724" t="inlineStr">
+        <is>
+          <t>Начать с крупных клиентов: прозвонить и предложить подключить контрагента в ЭПД ТАНДЕМ.</t>
+        </is>
+      </c>
       <c r="B91" s="717" t="n"/>
       <c r="C91" s="718" t="n"/>
-      <c r="D91" s="727" t="n"/>
-      <c r="E91" s="727" t="n"/>
-      <c r="F91" s="727" t="n"/>
-      <c r="G91" s="727" t="n"/>
+      <c r="D91" s="724" t="inlineStr">
+        <is>
+          <t>Крупные = от 2000 титулов. Корп. клиенты продавали ЭПД даже в малом объёме.</t>
+        </is>
+      </c>
+      <c r="E91" s="717" t="n"/>
+      <c r="F91" s="717" t="n"/>
+      <c r="G91" s="718" t="n"/>
       <c r="H91" s="727" t="n"/>
       <c r="I91" s="727" t="n"/>
     </row>
-    <row r="92">
-      <c r="A92" s="727" t="n"/>
+    <row r="92" ht="18" customHeight="1">
+      <c r="A92" s="724" t="inlineStr">
+        <is>
+          <t>Обзвон подключённых клиентов: оценка удовлетворённости + проекты ЦАС (Доки).</t>
+        </is>
+      </c>
       <c r="B92" s="717" t="n"/>
       <c r="C92" s="718" t="n"/>
-      <c r="D92" s="727" t="n"/>
-      <c r="E92" s="727" t="n"/>
-      <c r="F92" s="727" t="n"/>
-      <c r="G92" s="727" t="n"/>
+      <c r="D92" s="729" t="inlineStr">
+        <is>
+          <t>Задача на Сашу Дворяк / Лазарчук — клиенты ЦАС.</t>
+        </is>
+      </c>
+      <c r="E92" s="717" t="n"/>
+      <c r="F92" s="717" t="n"/>
+      <c r="G92" s="718" t="n"/>
       <c r="H92" s="727" t="n"/>
       <c r="I92" s="727" t="n"/>
     </row>
-    <row r="93">
-      <c r="A93" s="727" t="n"/>
-      <c r="B93" s="727" t="n"/>
-      <c r="C93" s="727" t="n"/>
-      <c r="D93" s="727" t="n"/>
-      <c r="E93" s="727" t="n"/>
-      <c r="F93" s="727" t="n"/>
-      <c r="G93" s="727" t="n"/>
+    <row r="93" ht="52" customHeight="1">
+      <c r="A93" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Корп. сегмент / сбытовой офис</t>
+        </is>
+      </c>
+      <c r="B93" s="717" t="n"/>
+      <c r="C93" s="717" t="n"/>
+      <c r="D93" s="717" t="n"/>
+      <c r="E93" s="717" t="n"/>
+      <c r="F93" s="717" t="n"/>
+      <c r="G93" s="718" t="n"/>
       <c r="H93" s="727" t="n"/>
       <c r="I93" s="727" t="n"/>
     </row>
-    <row r="94">
-      <c r="A94" s="727" t="n"/>
-      <c r="B94" s="727" t="n"/>
-      <c r="C94" s="727" t="n"/>
-      <c r="D94" s="727" t="n"/>
-      <c r="E94" s="727" t="n"/>
-      <c r="F94" s="727" t="n"/>
-      <c r="G94" s="727" t="n"/>
+    <row r="94" ht="18" customHeight="1">
+      <c r="A94" s="724" t="inlineStr">
+        <is>
+          <t>Почему клиенты сбытового офиса не переходят в ЭПД / уходят на СБИС?</t>
+        </is>
+      </c>
+      <c r="B94" s="717" t="n"/>
+      <c r="C94" s="718" t="n"/>
+      <c r="D94" s="729" t="inlineStr">
+        <is>
+          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в 1-ю неделю сентября (Юлиана).</t>
+        </is>
+      </c>
+      <c r="E94" s="717" t="n"/>
+      <c r="F94" s="717" t="n"/>
+      <c r="G94" s="718" t="n"/>
       <c r="H94" s="727" t="n"/>
       <c r="I94" s="727" t="n"/>
     </row>
-    <row r="95">
-      <c r="A95" s="727" t="n"/>
-      <c r="B95" s="727" t="n"/>
-      <c r="C95" s="727" t="n"/>
-      <c r="D95" s="727" t="n"/>
-      <c r="E95" s="727" t="n"/>
-      <c r="F95" s="727" t="n"/>
-      <c r="G95" s="727" t="n"/>
+    <row r="95" ht="52" customHeight="1">
+      <c r="A95" s="724" t="inlineStr">
+        <is>
+          <t>Юля: предлагать всем клиентам бесплатно Доки (дублирующий сервис) на 3 мес.; KPI менеджерам на сентябрь.</t>
+        </is>
+      </c>
+      <c r="B95" s="717" t="n"/>
+      <c r="C95" s="718" t="n"/>
+      <c r="D95" s="724" t="inlineStr">
+        <is>
+          <t>Зафиксировано как предложение.</t>
+        </is>
+      </c>
+      <c r="E95" s="717" t="n"/>
+      <c r="F95" s="717" t="n"/>
+      <c r="G95" s="718" t="n"/>
       <c r="H95" s="727" t="n"/>
       <c r="I95" s="727" t="n"/>
     </row>
-    <row r="96">
-      <c r="A96" s="727" t="n"/>
-      <c r="B96" s="727" t="n"/>
-      <c r="C96" s="727" t="n"/>
-      <c r="D96" s="727" t="n"/>
-      <c r="E96" s="727" t="n"/>
-      <c r="F96" s="727" t="n"/>
-      <c r="G96" s="727" t="n"/>
-      <c r="H96" s="727" t="n"/>
-      <c r="I96" s="727" t="n"/>
-    </row>
-    <row r="97">
-      <c r="A97" s="727" t="n"/>
-      <c r="B97" s="727" t="n"/>
-      <c r="C97" s="727" t="n"/>
-      <c r="D97" s="727" t="n"/>
-      <c r="E97" s="727" t="n"/>
-      <c r="F97" s="727" t="n"/>
-      <c r="G97" s="727" t="n"/>
-      <c r="H97" s="727" t="n"/>
-      <c r="I97" s="727" t="n"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="727" t="n"/>
-      <c r="B98" s="727" t="n"/>
-      <c r="C98" s="727" t="n"/>
-      <c r="D98" s="727" t="n"/>
-      <c r="E98" s="727" t="n"/>
-      <c r="F98" s="727" t="n"/>
-      <c r="G98" s="727" t="n"/>
-      <c r="H98" s="727" t="n"/>
-      <c r="I98" s="727" t="n"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="727" t="n"/>
-      <c r="B99" s="727" t="n"/>
-      <c r="C99" s="727" t="n"/>
-      <c r="D99" s="727" t="n"/>
-      <c r="E99" s="727" t="n"/>
-      <c r="F99" s="727" t="n"/>
-      <c r="G99" s="727" t="n"/>
-      <c r="H99" s="727" t="n"/>
-      <c r="I99" s="727" t="n"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="727" t="n"/>
-      <c r="B100" s="727" t="n"/>
-      <c r="C100" s="727" t="n"/>
-      <c r="D100" s="727" t="n"/>
-      <c r="E100" s="727" t="n"/>
-      <c r="F100" s="727" t="n"/>
-      <c r="G100" s="727" t="n"/>
-      <c r="H100" s="727" t="n"/>
-      <c r="I100" s="727" t="n"/>
+    <row r="96" ht="52" customHeight="1">
+      <c r="A96" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Статистика продаж и расхождения</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="18" customHeight="1">
+      <c r="A97" s="724" t="inlineStr">
+        <is>
+          <t>Статистика 1С: оформленные тарифы (не клиенты). На текущий момент 143 тарифа; в августе уже ~87 подключений. УТ и 1С могут расходиться.</t>
+        </is>
+      </c>
+      <c r="D97" s="729" t="inlineStr">
+        <is>
+          <t>Фиксировать динамику тарифов. Разобрать расхождения УТ ↔ 1С и клиентов, не попавших в отчёты. По запросу — финансовая статистика помесячно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="52" customHeight="1">
+      <c r="A98" s="724" t="inlineStr">
+        <is>
+          <t>Дубли тарифов у одного клиента в одном периоде (пример «Пчёлы свободные»: две по 600 вместо одной 1000).</t>
+        </is>
+      </c>
+      <c r="D98" s="729" t="inlineStr">
+        <is>
+          <t>Разобрать кейсы дублей: почему не предложили больший пакет; скорректировать скрипт продажи.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="52" customHeight="1">
+      <c r="A99" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Состав базы (крупные / средние / мелкие)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="52" customHeight="1">
+      <c r="A100" s="724" t="inlineStr">
+        <is>
+          <t>Как сегментировать план 500: крупные ≥10 000 титулов, средние 2 000–10 000, мелкие &lt;2 000. Сейчас по факту: 1 крупный, 8 средних, остальное мелкие.</t>
+        </is>
+      </c>
+      <c r="D100" s="729" t="inlineStr">
+        <is>
+          <t>Обсудили альтернативу: ~10% крупных / 30% средних / 60% мелких (более достижимо по количеству). Признак «генератор трафика» обязателен для крупных. Уточнить целевые % после анализа базы.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
-      <c r="A101" s="727" t="n"/>
-      <c r="B101" s="727" t="n"/>
-      <c r="C101" s="727" t="n"/>
-      <c r="D101" s="727" t="n"/>
-      <c r="E101" s="727" t="n"/>
-      <c r="F101" s="727" t="n"/>
-      <c r="G101" s="727" t="n"/>
-      <c r="H101" s="727" t="n"/>
-      <c r="I101" s="727" t="n"/>
+      <c r="A101" s="728" t="inlineStr">
+        <is>
+          <t>Блок: Центр компетенций и аккаунтинг</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="727" t="n"/>
-      <c r="B102" s="727" t="n"/>
-      <c r="C102" s="727" t="n"/>
-      <c r="D102" s="727" t="n"/>
-      <c r="E102" s="727" t="n"/>
-      <c r="F102" s="727" t="n"/>
-      <c r="G102" s="727" t="n"/>
-      <c r="H102" s="727" t="n"/>
-      <c r="I102" s="727" t="n"/>
+      <c r="A102" s="724" t="inlineStr">
+        <is>
+          <t>Нужен центр компетенций по ЭПД: все проданные в компании ЭПД изучать — объём, пользование, допродажи, продление. Идея ролей: администратор (операционка/чек-лист в Битрикс) + менеджер продаж + менеджер заботы/продлений.</t>
+        </is>
+      </c>
+      <c r="D102" s="729" t="inlineStr">
+        <is>
+          <t>Цель: клиент начал пользоваться и вовремя пополнил баланс. Ожидание — зона ответственности ЦКС; допродажи УАТ/смежного — ЦП по выгрузке после продажи ЭПД. Проработать модель и нагрузку при росте до ~120–130 клиентов/мес.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="724" t="inlineStr">
+        <is>
+          <t>Сценарий выхаживания на демо: раз в неделю смотреть активность (если доступно); если нет динамики — звонок; минимум раз в 2 недели контакт + проверка, что клиент в чате.</t>
+        </is>
+      </c>
+      <c r="D103" s="729" t="inlineStr">
+        <is>
+          <t>Зафиксировать сценарий. Риск: кто выхаживает — МПП, ЦКС или выделенный человек (в т.ч. идея с Антоном / отдельными ролями в ЦП и ЦКС).</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="728" t="inlineStr">
+        <is>
+          <t>Блок: PR, контент и соцсети</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="724" t="inlineStr">
+        <is>
+          <t>Соцсети ЭПД: ВК, МАКС, Telegram. Контент должен закрывать этапы воронки: выбор решения → выбор компании → покупка. Не хватает кейсов, отзывов, CTA на консультацию в каждом посте.</t>
+        </is>
+      </c>
+      <c r="D105" s="729" t="inlineStr">
+        <is>
+          <t>До конца года: системно — SEO/статьи (в т.ч. внешние площадки, РБК), вебинары с 1С/Калугой раз в месяц + соло-вебинары, усиление постов/акций. Помощь ЦСВ по экспертным материалам. Точечные запросы контента — Вике.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="724" t="inlineStr">
+        <is>
+          <t>Идея сентябрьской акции «экстренное подключение» (бесплатно / пакет поддержки) + горячая линия (Олимпиада/Антон) для экспертизы.</t>
+        </is>
+      </c>
+      <c r="D106" s="729" t="inlineStr">
+        <is>
+          <t>Механику доработать (срок акции, цена/бесплатность, каналы: соцсети + рассылка + материалы менеджерам). Если к 01.09 — готовить оперативно.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="724" t="inlineStr">
+        <is>
+          <t>Статус партнёра по ЭПД / внедрённые решения: проверить отображение статуса; использовать как инфоповод («единственные в регионе»). По ~143 клиентам — отобрать кейсы для публикации + оценка удовлетворённости.</t>
+        </is>
+      </c>
+      <c r="D107" s="729" t="inlineStr">
+        <is>
+          <t>Проверить статус заявки; нарастить число опубликованных внедрённых решений (Юля / команда).</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="710" t="inlineStr">
+        <is>
+          <t>Подсветка выводов: строки с поручениями/задачами выделены мягким оранжевым. Поставленные задачи продублированы в блоке «2. Решения текущей встречи».</t>
+        </is>
+      </c>
+      <c r="H108" s="727" t="n"/>
+      <c r="I108" s="727" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="727" t="n"/>
+      <c r="B109" s="717" t="n"/>
+      <c r="C109" s="718" t="n"/>
+      <c r="D109" s="727" t="n"/>
+      <c r="E109" s="727" t="n"/>
+      <c r="F109" s="727" t="n"/>
+      <c r="G109" s="727" t="n"/>
+      <c r="H109" s="727" t="n"/>
+      <c r="I109" s="727" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="727" t="n"/>
+      <c r="B110" s="717" t="n"/>
+      <c r="C110" s="718" t="n"/>
+      <c r="D110" s="727" t="n"/>
+      <c r="E110" s="727" t="n"/>
+      <c r="F110" s="727" t="n"/>
+      <c r="G110" s="727" t="n"/>
+      <c r="H110" s="727" t="n"/>
+      <c r="I110" s="727" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="727" t="n"/>
+      <c r="B111" s="717" t="n"/>
+      <c r="C111" s="718" t="n"/>
+      <c r="D111" s="727" t="n"/>
+      <c r="E111" s="727" t="n"/>
+      <c r="F111" s="727" t="n"/>
+      <c r="G111" s="727" t="n"/>
+      <c r="H111" s="727" t="n"/>
+      <c r="I111" s="727" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="727" t="n"/>
+      <c r="B112" s="727" t="n"/>
+      <c r="C112" s="727" t="n"/>
+      <c r="D112" s="727" t="n"/>
+      <c r="E112" s="727" t="n"/>
+      <c r="F112" s="727" t="n"/>
+      <c r="G112" s="727" t="n"/>
+      <c r="H112" s="727" t="n"/>
+      <c r="I112" s="727" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="727" t="n"/>
+      <c r="B113" s="727" t="n"/>
+      <c r="C113" s="727" t="n"/>
+      <c r="D113" s="727" t="n"/>
+      <c r="E113" s="727" t="n"/>
+      <c r="F113" s="727" t="n"/>
+      <c r="G113" s="727" t="n"/>
+      <c r="H113" s="727" t="n"/>
+      <c r="I113" s="727" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="727" t="n"/>
+      <c r="B114" s="727" t="n"/>
+      <c r="C114" s="727" t="n"/>
+      <c r="D114" s="727" t="n"/>
+      <c r="E114" s="727" t="n"/>
+      <c r="F114" s="727" t="n"/>
+      <c r="G114" s="727" t="n"/>
+      <c r="H114" s="727" t="n"/>
+      <c r="I114" s="727" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="727" t="n"/>
+      <c r="B115" s="727" t="n"/>
+      <c r="C115" s="727" t="n"/>
+      <c r="D115" s="727" t="n"/>
+      <c r="E115" s="727" t="n"/>
+      <c r="F115" s="727" t="n"/>
+      <c r="G115" s="727" t="n"/>
+      <c r="H115" s="727" t="n"/>
+      <c r="I115" s="727" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="727" t="n"/>
+      <c r="B116" s="727" t="n"/>
+      <c r="C116" s="727" t="n"/>
+      <c r="D116" s="727" t="n"/>
+      <c r="E116" s="727" t="n"/>
+      <c r="F116" s="727" t="n"/>
+      <c r="G116" s="727" t="n"/>
+      <c r="H116" s="727" t="n"/>
+      <c r="I116" s="727" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="727" t="n"/>
+      <c r="B117" s="727" t="n"/>
+      <c r="C117" s="727" t="n"/>
+      <c r="D117" s="727" t="n"/>
+      <c r="E117" s="727" t="n"/>
+      <c r="F117" s="727" t="n"/>
+      <c r="G117" s="727" t="n"/>
+      <c r="H117" s="727" t="n"/>
+      <c r="I117" s="727" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="727" t="n"/>
+      <c r="B118" s="727" t="n"/>
+      <c r="C118" s="727" t="n"/>
+      <c r="D118" s="727" t="n"/>
+      <c r="E118" s="727" t="n"/>
+      <c r="F118" s="727" t="n"/>
+      <c r="G118" s="727" t="n"/>
+      <c r="H118" s="727" t="n"/>
+      <c r="I118" s="727" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="727" t="n"/>
+      <c r="B119" s="727" t="n"/>
+      <c r="C119" s="727" t="n"/>
+      <c r="D119" s="727" t="n"/>
+      <c r="E119" s="727" t="n"/>
+      <c r="F119" s="727" t="n"/>
+      <c r="G119" s="727" t="n"/>
+      <c r="H119" s="727" t="n"/>
+      <c r="I119" s="727" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="727" t="n"/>
+      <c r="B120" s="727" t="n"/>
+      <c r="C120" s="727" t="n"/>
+      <c r="D120" s="727" t="n"/>
+      <c r="E120" s="727" t="n"/>
+      <c r="F120" s="727" t="n"/>
+      <c r="G120" s="727" t="n"/>
+      <c r="H120" s="727" t="n"/>
+      <c r="I120" s="727" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="727" t="n"/>
+      <c r="B121" s="727" t="n"/>
+      <c r="C121" s="727" t="n"/>
+      <c r="D121" s="727" t="n"/>
+      <c r="E121" s="727" t="n"/>
+      <c r="F121" s="727" t="n"/>
+      <c r="G121" s="727" t="n"/>
+      <c r="H121" s="727" t="n"/>
+      <c r="I121" s="727" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="112">
+  <mergeCells count="128">
     <mergeCell ref="F29:G29"/>
     <mergeCell ref="A80:C80"/>
     <mergeCell ref="F25:G25"/>
     <mergeCell ref="D74:G74"/>
     <mergeCell ref="D68:G68"/>
+    <mergeCell ref="D100:G100"/>
+    <mergeCell ref="A91:C91"/>
     <mergeCell ref="D84:G84"/>
+    <mergeCell ref="A93:C93"/>
     <mergeCell ref="F23:G23"/>
     <mergeCell ref="D77:G77"/>
     <mergeCell ref="A77:C77"/>
     <mergeCell ref="A83:C83"/>
+    <mergeCell ref="D95:G95"/>
     <mergeCell ref="F56:G56"/>
     <mergeCell ref="A46:G46"/>
     <mergeCell ref="F43:G43"/>
@@ -5086,53 +5390,60 @@
     <mergeCell ref="A89:G89"/>
     <mergeCell ref="D72:G72"/>
     <mergeCell ref="A69:C69"/>
+    <mergeCell ref="D87:G87"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="D87:G87"/>
     <mergeCell ref="A71:G71"/>
     <mergeCell ref="F57:G57"/>
-    <mergeCell ref="D62:G62"/>
-    <mergeCell ref="A66:C66"/>
     <mergeCell ref="A75:C75"/>
     <mergeCell ref="F10:G10"/>
     <mergeCell ref="F54:G54"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="F63:G63"/>
     <mergeCell ref="F34:G34"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="E5:F5"/>
-    <mergeCell ref="D64:G64"/>
+    <mergeCell ref="D98:G98"/>
     <mergeCell ref="D73:G73"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A95:C95"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="D88:G88"/>
     <mergeCell ref="F30:G30"/>
     <mergeCell ref="F33:G33"/>
     <mergeCell ref="F45:G45"/>
+    <mergeCell ref="A92:G92"/>
     <mergeCell ref="F42:G42"/>
+    <mergeCell ref="D90:G90"/>
     <mergeCell ref="A81:C81"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="D99:G99"/>
+    <mergeCell ref="F66:G66"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="F47:G47"/>
+    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="F62:G62"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="A78:G78"/>
     <mergeCell ref="F28:G28"/>
-    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A73:C73"/>
     <mergeCell ref="C8:D8"/>
-    <mergeCell ref="A73:C73"/>
     <mergeCell ref="F9:G9"/>
+    <mergeCell ref="F61:G61"/>
     <mergeCell ref="F39:G39"/>
     <mergeCell ref="F48:G48"/>
     <mergeCell ref="D75:G75"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A10:B10"/>
+    <mergeCell ref="F64:G64"/>
     <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A97:G97"/>
     <mergeCell ref="A84:C84"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D79:G79"/>
     <mergeCell ref="F53:G53"/>
-    <mergeCell ref="D79:G79"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A62:C62"/>
     <mergeCell ref="F36:G36"/>
     <mergeCell ref="A82:G82"/>
     <mergeCell ref="F50:G50"/>
@@ -5143,17 +5454,19 @@
     <mergeCell ref="A6:G6"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A64:C64"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D66:G66"/>
+    <mergeCell ref="A98:C98"/>
+    <mergeCell ref="D91:G91"/>
     <mergeCell ref="A79:C79"/>
-    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A88:C88"/>
     <mergeCell ref="A70:C70"/>
     <mergeCell ref="F49:G49"/>
     <mergeCell ref="A86:G86"/>
+    <mergeCell ref="D93:G93"/>
     <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A90:C90"/>
     <mergeCell ref="D83:G83"/>
+    <mergeCell ref="F65:G65"/>
     <mergeCell ref="A74:C74"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="D85:G85"/>
@@ -5164,6 +5477,7 @@
     <mergeCell ref="A85:C85"/>
     <mergeCell ref="D69:G69"/>
     <mergeCell ref="F51:G51"/>
+    <mergeCell ref="A100:C100"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="F26:G26"/>
     <mergeCell ref="F41:G41"/>
@@ -5172,10 +5486,12 @@
     <mergeCell ref="A68:C68"/>
     <mergeCell ref="F38:G38"/>
     <mergeCell ref="C11:D11"/>
+    <mergeCell ref="D96:G96"/>
     <mergeCell ref="A7:G7"/>
     <mergeCell ref="F58:G58"/>
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="F52:G52"/>
+    <mergeCell ref="F67:G67"/>
     <mergeCell ref="F37:G37"/>
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="A87:C87"/>
@@ -5192,7 +5508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE57"/>
+  <dimension ref="A1:L57"/>
   <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="8.762" customWidth="1" min="1" max="1"/>
@@ -6234,9 +6550,9 @@
       <c r="G56" s="718" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="246" t="n"/>
-      <c r="B57" s="246" t="n"/>
-      <c r="C57" s="246" t="n"/>
+      <c r="A57" s="281" t="n"/>
+      <c r="B57" s="281" t="n"/>
+      <c r="C57" s="281" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="63">
@@ -6252,9 +6568,9 @@
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="A50:C50"/>
-    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="F7:G7"/>
@@ -6319,7 +6635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE42"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="13" defaultColWidth="13.4" defaultRowHeight="14.25" customHeight="1"/>
   <cols>
     <col width="8.762" customWidth="1" min="1" max="1"/>
@@ -6412,7 +6728,7 @@
     </row>
     <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="423" t="n"/>
-      <c r="B5" s="424" t="n"/>
+      <c r="B5" s="425" t="n"/>
       <c r="C5" s="425" t="inlineStr">
         <is>
           <t xml:space="preserve">Савинская </t>
@@ -7044,9 +7360,9 @@
       <c r="G41" s="718" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="246" t="n"/>
-      <c r="B42" s="246" t="n"/>
-      <c r="C42" s="246" t="n"/>
+      <c r="A42" s="281" t="n"/>
+      <c r="B42" s="281" t="n"/>
+      <c r="C42" s="281" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="46">
@@ -7691,9 +8007,9 @@
       <c r="D38" s="242" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="246" t="n"/>
-      <c r="B39" s="246" t="n"/>
-      <c r="C39" s="246" t="n"/>
+      <c r="A39" s="281" t="n"/>
+      <c r="B39" s="281" t="n"/>
+      <c r="C39" s="281" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="35">
@@ -7866,7 +8182,7 @@
           <t>в работе</t>
         </is>
       </c>
-      <c r="F6" s="356" t="inlineStr">
+      <c r="F6" s="520" t="inlineStr">
         <is>
           <t xml:space="preserve">ОС в чате ЭПД стратегия будет </t>
         </is>
@@ -8424,9 +8740,9 @@
       <c r="G38" s="718" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="246" t="n"/>
-      <c r="B39" s="246" t="n"/>
-      <c r="C39" s="246" t="n"/>
+      <c r="A39" s="281" t="n"/>
+      <c r="B39" s="281" t="n"/>
+      <c r="C39" s="281" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -9072,9 +9388,9 @@
       <c r="D38" s="242" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="246" t="n"/>
-      <c r="B39" s="246" t="n"/>
-      <c r="C39" s="246" t="n"/>
+      <c r="A39" s="281" t="n"/>
+      <c r="B39" s="281" t="n"/>
+      <c r="C39" s="281" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="45">

--- a/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
+++ b/Протокол встреч по проекту ЭПД  ЦП-ЦКС-ЦСВ.xlsx
@@ -3250,9 +3250,7 @@
           <t>10.09.2026</t>
         </is>
       </c>
-      <c r="J7" s="711" t="n">
-        <v>250</v>
-      </c>
+      <c r="J7" s="711" t="n"/>
       <c r="K7" s="712">
         <f>IF(OR(J6="",J7="",NOT(ISNUMBER(J6)),NOT(ISNUMBER(J7))),"",IF(J6=0,"",IF(J7&gt;J6,"увеличилось на "&amp;ROUND((J7-J6)/J6*100,1)&amp;"%",IF(J7&lt;J6,"уменьшилось на "&amp;ROUND((J6-J7)/J6*100,1)&amp;"%","без изменений"))))</f>
         <v/>
@@ -4416,6 +4414,7 @@
           <t>Пример из статистики 1С — «Пчёлы свободные».</t>
         </is>
       </c>
+      <c r="G61" s="718" t="n"/>
     </row>
     <row r="62" ht="40" customHeight="1">
       <c r="A62" s="714" t="n">
@@ -4446,6 +4445,7 @@
           <t>Крупный = ещё и генератор трафика. Сейчас: 1 крупный, 8 средних.</t>
         </is>
       </c>
+      <c r="G62" s="718" t="n"/>
     </row>
     <row r="63" ht="40" customHeight="1">
       <c r="A63" s="714" t="n">
@@ -4476,6 +4476,7 @@
           <t>Цель: пользование сервисом + своевременное пополнение баланса; допродажа УАТ — по выгрузке ЦП.</t>
         </is>
       </c>
+      <c r="G63" s="718" t="n"/>
     </row>
     <row r="64" ht="40" customHeight="1">
       <c r="A64" s="714" t="n">
@@ -4506,6 +4507,7 @@
           <t>Определить, кто выхаживает: МПП, ЦКС или выделенный человек.</t>
         </is>
       </c>
+      <c r="G64" s="718" t="n"/>
     </row>
     <row r="65" ht="40" customHeight="1">
       <c r="A65" s="714" t="n">
@@ -4536,6 +4538,7 @@
           <t>Точечные запросы контента — Вике. Материалы для менеджеров на сентябрь.</t>
         </is>
       </c>
+      <c r="G65" s="718" t="n"/>
     </row>
     <row r="66" ht="40" customHeight="1">
       <c r="A66" s="714" t="n">
@@ -4566,6 +4569,7 @@
           <t>Соцсети + рассылка + менеджеры. Если к 01.09 — готовить сразу.</t>
         </is>
       </c>
+      <c r="G66" s="718" t="n"/>
     </row>
     <row r="67" ht="40" customHeight="1">
       <c r="A67" s="714" t="n">
@@ -4596,6 +4600,7 @@
           <t>Статус — инфоповод для контента.</t>
         </is>
       </c>
+      <c r="G67" s="718" t="n"/>
     </row>
     <row r="68" ht="48" customHeight="1">
       <c r="A68" s="589" t="inlineStr">
@@ -4605,7 +4610,7 @@
       </c>
       <c r="B68" s="717" t="n"/>
       <c r="C68" s="718" t="n"/>
-      <c r="D68" s="717" t="n"/>
+      <c r="D68" s="718" t="n"/>
       <c r="E68" s="717" t="n"/>
       <c r="F68" s="717" t="n"/>
       <c r="G68" s="718" t="n"/>
@@ -4636,8 +4641,8 @@
         </is>
       </c>
       <c r="B70" s="717" t="n"/>
-      <c r="C70" s="717" t="n"/>
-      <c r="D70" s="717" t="n"/>
+      <c r="C70" s="718" t="n"/>
+      <c r="D70" s="718" t="n"/>
       <c r="E70" s="717" t="n"/>
       <c r="F70" s="717" t="n"/>
       <c r="G70" s="718" t="n"/>
@@ -4651,12 +4656,8 @@
         </is>
       </c>
       <c r="B71" s="717" t="n"/>
-      <c r="C71" s="718" t="n"/>
-      <c r="D71" s="724" t="inlineStr">
-        <is>
-          <t>Оксана: уточнить адресата вопроса. Акцию продлили до 30.09.</t>
-        </is>
-      </c>
+      <c r="C71" s="717" t="n"/>
+      <c r="D71" s="717" t="n"/>
       <c r="E71" s="717" t="n"/>
       <c r="F71" s="717" t="n"/>
       <c r="G71" s="718" t="n"/>
@@ -4670,8 +4671,8 @@
         </is>
       </c>
       <c r="B72" s="717" t="n"/>
-      <c r="C72" s="717" t="n"/>
-      <c r="D72" s="717" t="n"/>
+      <c r="C72" s="718" t="n"/>
+      <c r="D72" s="718" t="n"/>
       <c r="E72" s="717" t="n"/>
       <c r="F72" s="717" t="n"/>
       <c r="G72" s="718" t="n"/>
@@ -4704,8 +4705,8 @@
         </is>
       </c>
       <c r="B74" s="717" t="n"/>
-      <c r="C74" s="717" t="n"/>
-      <c r="D74" s="717" t="n"/>
+      <c r="C74" s="718" t="n"/>
+      <c r="D74" s="718" t="n"/>
       <c r="E74" s="717" t="n"/>
       <c r="F74" s="717" t="n"/>
       <c r="G74" s="718" t="n"/>
@@ -4738,12 +4739,8 @@
         </is>
       </c>
       <c r="B76" s="717" t="n"/>
-      <c r="C76" s="718" t="n"/>
-      <c r="D76" s="724" t="inlineStr">
-        <is>
-          <t>По соотношению базы (крупные / средние / мелкие) пришли к соглашению по процентам.</t>
-        </is>
-      </c>
+      <c r="C76" s="717" t="n"/>
+      <c r="D76" s="717" t="n"/>
       <c r="E76" s="717" t="n"/>
       <c r="F76" s="717" t="n"/>
       <c r="G76" s="718" t="n"/>
@@ -4848,12 +4845,8 @@
         </is>
       </c>
       <c r="B82" s="717" t="n"/>
-      <c r="C82" s="718" t="n"/>
-      <c r="D82" s="724" t="inlineStr">
-        <is>
-          <t>Трафик не видим → не квалифицируем активность пользования пакетом. 1С обещают данные в сентябре.</t>
-        </is>
-      </c>
+      <c r="C82" s="717" t="n"/>
+      <c r="D82" s="717" t="n"/>
       <c r="E82" s="717" t="n"/>
       <c r="F82" s="717" t="n"/>
       <c r="G82" s="718" t="n"/>
@@ -4867,8 +4860,8 @@
         </is>
       </c>
       <c r="B83" s="717" t="n"/>
-      <c r="C83" s="717" t="n"/>
-      <c r="D83" s="717" t="n"/>
+      <c r="C83" s="718" t="n"/>
+      <c r="D83" s="718" t="n"/>
       <c r="E83" s="717" t="n"/>
       <c r="F83" s="717" t="n"/>
       <c r="G83" s="718" t="n"/>
@@ -4901,8 +4894,8 @@
         </is>
       </c>
       <c r="B85" s="717" t="n"/>
-      <c r="C85" s="717" t="n"/>
-      <c r="D85" s="717" t="n"/>
+      <c r="C85" s="718" t="n"/>
+      <c r="D85" s="718" t="n"/>
       <c r="E85" s="717" t="n"/>
       <c r="F85" s="717" t="n"/>
       <c r="G85" s="718" t="n"/>
@@ -4916,12 +4909,8 @@
         </is>
       </c>
       <c r="B86" s="717" t="n"/>
-      <c r="C86" s="718" t="n"/>
-      <c r="D86" s="724" t="inlineStr">
-        <is>
-          <t>Если есть ИТС — менеджер ЦКС смотрит динамику расхода ЭПД/Доки. Трафика пока нет; можно писать в Калугу с перечнем ИНН. Риск: кто выхаживает — текущие менеджеры или новый человек?</t>
-        </is>
-      </c>
+      <c r="C86" s="717" t="n"/>
+      <c r="D86" s="717" t="n"/>
       <c r="E86" s="717" t="n"/>
       <c r="F86" s="717" t="n"/>
       <c r="G86" s="718" t="n"/>
@@ -5026,12 +5015,8 @@
         </is>
       </c>
       <c r="B92" s="717" t="n"/>
-      <c r="C92" s="718" t="n"/>
-      <c r="D92" s="729" t="inlineStr">
-        <is>
-          <t>Задача на Сашу Дворяк / Лазарчук — клиенты ЦАС.</t>
-        </is>
-      </c>
+      <c r="C92" s="717" t="n"/>
+      <c r="D92" s="717" t="n"/>
       <c r="E92" s="717" t="n"/>
       <c r="F92" s="717" t="n"/>
       <c r="G92" s="718" t="n"/>
@@ -5045,8 +5030,8 @@
         </is>
       </c>
       <c r="B93" s="717" t="n"/>
-      <c r="C93" s="717" t="n"/>
-      <c r="D93" s="717" t="n"/>
+      <c r="C93" s="718" t="n"/>
+      <c r="D93" s="718" t="n"/>
       <c r="E93" s="717" t="n"/>
       <c r="F93" s="717" t="n"/>
       <c r="G93" s="718" t="n"/>
@@ -5060,12 +5045,8 @@
         </is>
       </c>
       <c r="B94" s="717" t="n"/>
-      <c r="C94" s="718" t="n"/>
-      <c r="D94" s="729" t="inlineStr">
-        <is>
-          <t>Взять неуспешные сделки ЭПД по корп. сегменту и предложить Доки в 1-ю неделю сентября (Юлиана).</t>
-        </is>
-      </c>
+      <c r="C94" s="717" t="n"/>
+      <c r="D94" s="717" t="n"/>
       <c r="E94" s="717" t="n"/>
       <c r="F94" s="717" t="n"/>
       <c r="G94" s="718" t="n"/>
@@ -5097,6 +5078,8 @@
           <t>Блок: Статистика продаж и расхождения</t>
         </is>
       </c>
+      <c r="B96" s="717" t="n"/>
+      <c r="C96" s="718" t="n"/>
     </row>
     <row r="97" ht="18" customHeight="1">
       <c r="A97" s="724" t="inlineStr">
@@ -5104,11 +5087,12 @@
           <t>Статистика 1С: оформленные тарифы (не клиенты). На текущий момент 143 тарифа; в августе уже ~87 подключений. УТ и 1С могут расходиться.</t>
         </is>
       </c>
-      <c r="D97" s="729" t="inlineStr">
-        <is>
-          <t>Фиксировать динамику тарифов. Разобрать расхождения УТ ↔ 1С и клиентов, не попавших в отчёты. По запросу — финансовая статистика помесячно.</t>
-        </is>
-      </c>
+      <c r="B97" s="717" t="n"/>
+      <c r="C97" s="717" t="n"/>
+      <c r="D97" s="717" t="n"/>
+      <c r="E97" s="717" t="n"/>
+      <c r="F97" s="717" t="n"/>
+      <c r="G97" s="718" t="n"/>
     </row>
     <row r="98" ht="52" customHeight="1">
       <c r="A98" s="724" t="inlineStr">
@@ -5116,11 +5100,16 @@
           <t>Дубли тарифов у одного клиента в одном периоде (пример «Пчёлы свободные»: две по 600 вместо одной 1000).</t>
         </is>
       </c>
+      <c r="B98" s="717" t="n"/>
+      <c r="C98" s="718" t="n"/>
       <c r="D98" s="729" t="inlineStr">
         <is>
           <t>Разобрать кейсы дублей: почему не предложили больший пакет; скорректировать скрипт продажи.</t>
         </is>
       </c>
+      <c r="E98" s="717" t="n"/>
+      <c r="F98" s="717" t="n"/>
+      <c r="G98" s="718" t="n"/>
     </row>
     <row r="99" ht="52" customHeight="1">
       <c r="A99" s="728" t="inlineStr">
@@ -5128,6 +5117,8 @@
           <t>Блок: Состав базы (крупные / средние / мелкие)</t>
         </is>
       </c>
+      <c r="B99" s="717" t="n"/>
+      <c r="C99" s="718" t="n"/>
     </row>
     <row r="100" ht="52" customHeight="1">
       <c r="A100" s="724" t="inlineStr">
@@ -5135,11 +5126,16 @@
           <t>Как сегментировать план 500: крупные ≥10 000 титулов, средние 2 000–10 000, мелкие &lt;2 000. Сейчас по факту: 1 крупный, 8 средних, остальное мелкие.</t>
         </is>
       </c>
+      <c r="B100" s="717" t="n"/>
+      <c r="C100" s="718" t="n"/>
       <c r="D100" s="729" t="inlineStr">
         <is>
           <t>Обсудили альтернативу: ~10% крупных / 30% средних / 60% мелких (более достижимо по количеству). Признак «генератор трафика» обязателен для крупных. Уточнить целевые % после анализа базы.</t>
         </is>
       </c>
+      <c r="E100" s="717" t="n"/>
+      <c r="F100" s="717" t="n"/>
+      <c r="G100" s="718" t="n"/>
     </row>
     <row r="101">
       <c r="A101" s="728" t="inlineStr">
@@ -6568,9 +6564,9 @@
     <mergeCell ref="A56:C56"/>
     <mergeCell ref="A20:G20"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D55:G55"/>
     <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A55:C55"/>
     <mergeCell ref="D51:G51"/>
     <mergeCell ref="F40:G40"/>
     <mergeCell ref="F7:G7"/>
